--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E201FA-4A48-4E1F-96EC-D462074BAC43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6A228B-F41E-48B7-8031-716B16248F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{7E05CBAD-F1D1-4BAA-84BF-89A5C137CB7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{7E05CBAD-F1D1-4BAA-84BF-89A5C137CB7C}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
   <si>
     <t>ID</t>
   </si>
@@ -58,15 +58,9 @@
     <t>Value</t>
   </si>
   <si>
-    <t>VCardOperationRelicCondition</t>
-  </si>
-  <si>
     <t>Equal</t>
   </si>
   <si>
-    <t>M</t>
-  </si>
-  <si>
     <t>Layer</t>
   </si>
   <si>
@@ -113,6 +107,24 @@
   </si>
   <si>
     <t>OnCardUsed</t>
+  </si>
+  <si>
+    <t>MyRelic1</t>
+  </si>
+  <si>
+    <t>VRaisingRelic</t>
+  </si>
+  <si>
+    <t>VRaisingEventCondition</t>
+  </si>
+  <si>
+    <t>stream event</t>
+  </si>
+  <si>
+    <t>Stream</t>
+  </si>
+  <si>
+    <t>OnDayEnd</t>
   </si>
 </sst>
 </file>
@@ -515,23 +527,20 @@
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
+      <c r="B2" t="s">
+        <v>27</v>
       </c>
       <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
         <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -541,14 +550,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B9C003-DCEA-4713-9280-8DA9989479B6}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.28515625" customWidth="1"/>
     <col min="3" max="3" width="18.85546875" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="5" width="9.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" customWidth="1"/>
     <col min="7" max="7" width="11.85546875" customWidth="1"/>
     <col min="8" max="8" width="10.28515625" customWidth="1"/>
     <col min="9" max="9" width="13.140625" customWidth="1"/>
@@ -575,43 +584,43 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" t="s">
         <v>16</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" t="s">
         <v>19</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>20</v>
-      </c>
-      <c r="P1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -619,19 +628,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E2">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G2">
         <v>9</v>
@@ -644,6 +653,38 @@
       </c>
       <c r="J2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3">
+        <v>-1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>22</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6A228B-F41E-48B7-8031-716B16248F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E201FA-4A48-4E1F-96EC-D462074BAC43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{7E05CBAD-F1D1-4BAA-84BF-89A5C137CB7C}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{7E05CBAD-F1D1-4BAA-84BF-89A5C137CB7C}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
   <si>
     <t>ID</t>
   </si>
@@ -58,9 +58,15 @@
     <t>Value</t>
   </si>
   <si>
+    <t>VCardOperationRelicCondition</t>
+  </si>
+  <si>
     <t>Equal</t>
   </si>
   <si>
+    <t>M</t>
+  </si>
+  <si>
     <t>Layer</t>
   </si>
   <si>
@@ -107,24 +113,6 @@
   </si>
   <si>
     <t>OnCardUsed</t>
-  </si>
-  <si>
-    <t>MyRelic1</t>
-  </si>
-  <si>
-    <t>VRaisingRelic</t>
-  </si>
-  <si>
-    <t>VRaisingEventCondition</t>
-  </si>
-  <si>
-    <t>stream event</t>
-  </si>
-  <si>
-    <t>Stream</t>
-  </si>
-  <si>
-    <t>OnDayEnd</t>
   </si>
 </sst>
 </file>
@@ -527,20 +515,23 @@
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>27</v>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -550,14 +541,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B9C003-DCEA-4713-9280-8DA9989479B6}">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.28515625" customWidth="1"/>
     <col min="3" max="3" width="18.85546875" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="5" width="9.42578125" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" customWidth="1"/>
     <col min="7" max="7" width="11.85546875" customWidth="1"/>
     <col min="8" max="8" width="10.28515625" customWidth="1"/>
     <col min="9" max="9" width="13.140625" customWidth="1"/>
@@ -584,43 +575,43 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -628,19 +619,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G2">
         <v>9</v>
@@ -653,38 +644,6 @@
       </c>
       <c r="J2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3">
-        <v>-1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>22</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6A228B-F41E-48B7-8031-716B16248F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A329E347-6472-401F-B06B-7ACC74494B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{7E05CBAD-F1D1-4BAA-84BF-89A5C137CB7C}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{7E05CBAD-F1D1-4BAA-84BF-89A5C137CB7C}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A329E347-6472-401F-B06B-7ACC74494B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1E2401-1246-4CC1-8603-9B1FC5B4D64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{7E05CBAD-F1D1-4BAA-84BF-89A5C137CB7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7E05CBAD-F1D1-4BAA-84BF-89A5C137CB7C}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -55,9 +55,6 @@
     <t>ConditionType</t>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
     <t>Equal</t>
   </si>
   <si>
@@ -125,6 +122,9 @@
   </si>
   <si>
     <t>OnDayEnd</t>
+  </si>
+  <si>
+    <t>TargetValue</t>
   </si>
 </sst>
 </file>
@@ -493,11 +493,12 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
     <col min="3" max="3" width="15.42578125" customWidth="1"/>
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="15.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -520,7 +521,7 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -528,19 +529,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -584,43 +585,43 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" t="s">
         <v>17</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>18</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>19</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -628,19 +629,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2">
         <v>9</v>
@@ -660,19 +661,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3">
         <v>-1</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3">
         <v>0</v>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -1,26 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1E2401-1246-4CC1-8603-9B1FC5B4D64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7E05CBAD-F1D1-4BAA-84BF-89A5C137CB7C}"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
     <sheet name="Relics" sheetId="2" r:id="rId2"/>
+    <sheet name="Consumables" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -28,6 +20,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
   <si>
     <t>ID</t>
   </si>
@@ -55,9 +49,21 @@
     <t>ConditionType</t>
   </si>
   <si>
+    <t>TargetValue</t>
+  </si>
+  <si>
+    <t>stream event</t>
+  </si>
+  <si>
+    <t>VRaisingEventCondition</t>
+  </si>
+  <si>
     <t>Equal</t>
   </si>
   <si>
+    <t>Stream</t>
+  </si>
+  <si>
     <t>Layer</t>
   </si>
   <si>
@@ -112,43 +118,398 @@
     <t>VRaisingRelic</t>
   </si>
   <si>
-    <t>VRaisingEventCondition</t>
-  </si>
-  <si>
-    <t>stream event</t>
-  </si>
-  <si>
-    <t>Stream</t>
-  </si>
-  <si>
     <t>OnDayEnd</t>
   </si>
   <si>
-    <t>TargetValue</t>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>Wasser</t>
+  </si>
+  <si>
+    <t>MineralWasser</t>
+  </si>
+  <si>
+    <t>VRaisingConsumable</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>Shield</t>
+  </si>
+  <si>
+    <t>20 Shields</t>
+  </si>
+  <si>
+    <t>VBattleConsumable</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -165,28 +526,316 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -235,7 +884,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -268,26 +917,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -320,23 +952,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -478,30 +1093,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDF99648-E133-47BD-9145-A5FCA01B6AD4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.1416666666667" customWidth="1"/>
+    <col min="2" max="2" width="11.7083333333333" customWidth="1"/>
+    <col min="3" max="3" width="15.425" customWidth="1"/>
+    <col min="4" max="4" width="28.7083333333333" customWidth="1"/>
+    <col min="5" max="5" width="14.7083333333333" customWidth="1"/>
+    <col min="6" max="6" width="15.425" customWidth="1"/>
+    <col min="7" max="7" width="10.425" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -521,57 +1131,59 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B9C003-DCEA-4713-9280-8DA9989479B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2"/>
   <cols>
-    <col min="2" max="2" width="10.28515625" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10.2833333333333" customWidth="1"/>
+    <col min="3" max="3" width="18.8583333333333" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" customWidth="1"/>
-    <col min="10" max="10" width="17.140625" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="9.425" customWidth="1"/>
+    <col min="6" max="6" width="20.1416666666667" customWidth="1"/>
+    <col min="7" max="7" width="11.8583333333333" customWidth="1"/>
+    <col min="8" max="8" width="10.2833333333333" customWidth="1"/>
+    <col min="9" max="9" width="13.1416666666667" customWidth="1"/>
+    <col min="10" max="10" width="17.1416666666667" customWidth="1"/>
+    <col min="11" max="11" width="14.1416666666667" customWidth="1"/>
+    <col min="12" max="12" width="12.425" customWidth="1"/>
     <col min="13" max="13" width="17" customWidth="1"/>
-    <col min="14" max="14" width="11.85546875" customWidth="1"/>
-    <col min="15" max="15" width="11.5703125" customWidth="1"/>
-    <col min="16" max="16" width="17.140625" customWidth="1"/>
+    <col min="14" max="14" width="11.8583333333333" customWidth="1"/>
+    <col min="15" max="15" width="11.5666666666667" customWidth="1"/>
+    <col min="16" max="16" width="17.1416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -585,63 +1197,63 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="G1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="I1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="L1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M1" t="s">
-        <v>15</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="O1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="P1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Q1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E2">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G2">
         <v>9</v>
@@ -656,24 +1268,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E3">
         <v>-1</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -690,5 +1302,111 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="2"/>
+  <cols>
+    <col min="1" max="2" width="8.66666666666667" style="1"/>
+    <col min="3" max="3" width="14.8583333333333" style="1" customWidth="1"/>
+    <col min="4" max="5" width="18.1416666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.8583333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.2833333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7083333333333" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.66666666666667" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:7">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="1">
+        <v>3</v>
+      </c>
+      <c r="G2" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:7">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="82">
   <si>
     <t>ID</t>
   </si>
@@ -103,46 +103,182 @@
     <t>Icon</t>
   </si>
   <si>
-    <t>MyRelic</t>
-  </si>
-  <si>
-    <t>VBattleRelic</t>
+    <t>小室的头绳</t>
+  </si>
+  <si>
+    <t>在外出结束后，粉丝+50</t>
+  </si>
+  <si>
+    <t>VRaisingRelic</t>
   </si>
   <si>
     <t>OnCardUsed</t>
   </si>
   <si>
-    <t>MyRelic1</t>
-  </si>
-  <si>
-    <t>VRaisingRelic</t>
+    <t>小室的玫瑰</t>
+  </si>
+  <si>
+    <t>在直播结束后，粉丝+100</t>
   </si>
   <si>
     <t>OnDayEnd</t>
   </si>
   <si>
+    <t>至尊啾咪的狗</t>
+  </si>
+  <si>
+    <t>进行杂谈练习后，杂谈力+6</t>
+  </si>
+  <si>
+    <t>至尊啾咪本体</t>
+  </si>
+  <si>
+    <t>获得A卡后，杂谈力+5</t>
+  </si>
+  <si>
+    <t>井井的话筒</t>
+  </si>
+  <si>
+    <t>进行歌力练习后，歌力+6</t>
+  </si>
+  <si>
+    <t>井井的光环</t>
+  </si>
+  <si>
+    <t>进行休息后，歌力+7</t>
+  </si>
+  <si>
+    <t>柚子的手柄</t>
+  </si>
+  <si>
+    <t>进行游戏练习后，游戏力+6</t>
+  </si>
+  <si>
+    <t>柚子的枕头</t>
+  </si>
+  <si>
+    <t>删除卡牌时，游戏力+10</t>
+  </si>
+  <si>
+    <t>画师麻麻的画笔</t>
+  </si>
+  <si>
+    <t>进行工作后，沪币+20</t>
+  </si>
+  <si>
+    <t>画师麻麻的画板</t>
+  </si>
+  <si>
+    <t>进行工作后，舰长+1</t>
+  </si>
+  <si>
+    <t>LiveType</t>
+  </si>
+  <si>
     <t>Rarity</t>
   </si>
   <si>
-    <t>Wasser</t>
-  </si>
-  <si>
-    <t>MineralWasser</t>
+    <t>水</t>
+  </si>
+  <si>
+    <t>神采+5</t>
+  </si>
+  <si>
+    <t>VBattleConsumable</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>千事可乐</t>
+  </si>
+  <si>
+    <t>红温+3</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>口口可乐</t>
+  </si>
+  <si>
+    <t>幽默+3</t>
+  </si>
+  <si>
+    <t>橙汁</t>
+  </si>
+  <si>
+    <t>参数+9</t>
+  </si>
+  <si>
+    <t>马卡龙</t>
+  </si>
+  <si>
+    <t>体力+6</t>
   </si>
   <si>
     <t>VRaisingConsumable</t>
   </si>
   <si>
-    <t>Common</t>
-  </si>
-  <si>
-    <t>Shield</t>
-  </si>
-  <si>
-    <t>20 Shields</t>
-  </si>
-  <si>
-    <t>VBattleConsumable</t>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>汉堡</t>
+  </si>
+  <si>
+    <t>参数获得量+30%三回合
+体力消耗减少50%+2回合
+体力消耗2</t>
+  </si>
+  <si>
+    <t>蓝莓汁</t>
+  </si>
+  <si>
+    <t>体力+3
+重抽手牌</t>
+  </si>
+  <si>
+    <t>冰淇淋</t>
+  </si>
+  <si>
+    <t>抽两张卡
+之后5回合开始时，抽一张牌</t>
+  </si>
+  <si>
+    <t>啤酒</t>
+  </si>
+  <si>
+    <t>下一张卡会使用两次，体力消耗增加50%+2回合</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>火锅汤</t>
+  </si>
+  <si>
+    <t>红温变为1.5倍，体力-2</t>
+  </si>
+  <si>
+    <t>菠萝披萨</t>
+  </si>
+  <si>
+    <t>回合结束时，幽默+1</t>
+  </si>
+  <si>
+    <t>神爪</t>
+  </si>
+  <si>
+    <t>卡牌使用次数+1</t>
+  </si>
+  <si>
+    <t>茶</t>
+  </si>
+  <si>
+    <t>压力-1，体力-4</t>
   </si>
 </sst>
 </file>
@@ -155,14 +291,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -627,159 +756,162 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1163,11 +1295,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2"/>
+  <dimension ref="A1:Q15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="10.2833333333333" customWidth="1"/>
-    <col min="3" max="3" width="18.8583333333333" customWidth="1"/>
+    <col min="2" max="2" width="13.5916666666667" customWidth="1"/>
+    <col min="3" max="3" width="25.5" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="5" width="9.425" customWidth="1"/>
     <col min="6" max="6" width="20.1416666666667" customWidth="1"/>
@@ -1199,13 +1331,13 @@
       <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>12</v>
       </c>
       <c r="G1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I1" t="s">
@@ -1214,7 +1346,7 @@
       <c r="J1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L1" t="s">
@@ -1223,7 +1355,7 @@
       <c r="M1" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O1" t="s">
@@ -1243,17 +1375,17 @@
       <c r="B2" t="s">
         <v>24</v>
       </c>
-      <c r="C2">
-        <v>2</v>
+      <c r="C2" t="s">
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2">
         <v>9</v>
@@ -1273,19 +1405,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E3">
         <v>-1</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1298,6 +1430,138 @@
       </c>
       <c r="J3">
         <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1309,22 +1573,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="2"/>
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="8.66666666666667" style="1"/>
-    <col min="3" max="3" width="14.8583333333333" style="1" customWidth="1"/>
-    <col min="4" max="5" width="18.1416666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5666666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.8583333333333" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.2833333333333" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7083333333333" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.66666666666667" style="1"/>
+    <col min="3" max="3" width="23.55" style="1" customWidth="1"/>
+    <col min="4" max="6" width="18.1416666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5666666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.8583333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.2833333333333" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7083333333333" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.66666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
+    <row r="1" s="1" customFormat="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1338,71 +1602,402 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:7">
+    <row r="2" s="1" customFormat="1" spans="1:8">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" s="1">
+        <v>52</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="1">
         <v>3</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:7">
+    <row r="3" s="1" customFormat="1" spans="1:8">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="1">
+        <v>56</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="1">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="G3" s="1">
-        <v>20</v>
+      <c r="B4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="1">
+        <v>45</v>
+      </c>
+      <c r="H4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="1">
+        <v>11</v>
+      </c>
+      <c r="H5" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" s="1">
+        <v>38</v>
+      </c>
+      <c r="H6" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" ht="42" spans="1:12">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="1">
+        <v>13</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="I7" s="1">
+        <v>38</v>
+      </c>
+      <c r="J7" s="1">
+        <v>-2</v>
+      </c>
+      <c r="K7" s="1">
+        <v>21</v>
+      </c>
+      <c r="L7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:9">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="1">
+        <v>38</v>
+      </c>
+      <c r="H8" s="1">
+        <v>3</v>
+      </c>
+      <c r="I8" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" ht="42" spans="1:10">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="1">
+        <v>9</v>
+      </c>
+      <c r="H9" s="1">
+        <v>2</v>
+      </c>
+      <c r="I9" s="1">
+        <v>62</v>
+      </c>
+      <c r="J9" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>26</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" s="1">
+        <v>63</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>3</v>
+      </c>
+      <c r="J11" s="1">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="1">
+        <v>65</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="1">
+        <v>14</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" s="1">
+        <v>4</v>
+      </c>
+      <c r="H14" s="1">
+        <v>-1</v>
+      </c>
+      <c r="I14" s="1">
+        <v>3</v>
+      </c>
+      <c r="J14" s="1">
+        <v>-4</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB638FE5-52EC-4599-B7DD-814EFF65A513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC910622-C857-43F4-BF5F-1C4A6829A0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="45">
   <si>
     <t>ID</t>
   </si>
@@ -156,6 +156,18 @@
   </si>
   <si>
     <t>Coke</t>
+  </si>
+  <si>
+    <t>LiveType</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>Epic</t>
   </si>
 </sst>
 </file>
@@ -687,20 +699,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="14.85546875" customWidth="1"/>
-    <col min="4" max="5" width="18.140625" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" customWidth="1"/>
+    <col min="4" max="6" width="18.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -714,28 +726,31 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2">
         <v>0</v>
       </c>
@@ -749,16 +764,19 @@
         <v>33</v>
       </c>
       <c r="E2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" t="s">
         <v>34</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>3</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:12">
       <c r="A3">
         <v>1</v>
       </c>
@@ -772,16 +790,19 @@
         <v>37</v>
       </c>
       <c r="E3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" t="s">
         <v>34</v>
       </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>2</v>
       </c>
@@ -795,16 +816,19 @@
         <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4">
+        <v>42</v>
+      </c>
+      <c r="F4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4">
         <v>3</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>3</v>
       </c>
@@ -818,12 +842,67 @@
         <v>37</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
+        <v>42</v>
+      </c>
+      <c r="F5" t="s">
+        <v>43</v>
       </c>
       <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
         <v>30</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="91">
   <si>
     <t>ID</t>
   </si>
@@ -52,7 +52,7 @@
     <t>TargetValue</t>
   </si>
   <si>
-    <t>stream event</t>
+    <t>外出事件</t>
   </si>
   <si>
     <t>VRaisingEventCondition</t>
@@ -61,9 +61,42 @@
     <t>Equal</t>
   </si>
   <si>
+    <t>Outside</t>
+  </si>
+  <si>
+    <t>直播事件</t>
+  </si>
+  <si>
     <t>Stream</t>
   </si>
   <si>
+    <t>社交事件</t>
+  </si>
+  <si>
+    <t>Coop</t>
+  </si>
+  <si>
+    <t>工作事件</t>
+  </si>
+  <si>
+    <t>Wrok</t>
+  </si>
+  <si>
+    <t>休息事件</t>
+  </si>
+  <si>
+    <t>Rest</t>
+  </si>
+  <si>
+    <t>杂谈练习事件</t>
+  </si>
+  <si>
+    <t>歌力练习事件</t>
+  </si>
+  <si>
+    <t>游戏练习事件</t>
+  </si>
+  <si>
     <t>Layer</t>
   </si>
   <si>
@@ -103,7 +136,7 @@
     <t>Icon</t>
   </si>
   <si>
-    <t>小室的头绳</t>
+    <t>墨镜</t>
   </si>
   <si>
     <t>在外出结束后，粉丝+50</t>
@@ -112,28 +145,25 @@
     <t>VRaisingRelic</t>
   </si>
   <si>
-    <t>OnCardUsed</t>
+    <t>OnEventEnd</t>
   </si>
   <si>
     <t>小室的玫瑰</t>
   </si>
   <si>
-    <t>在直播结束后，粉丝+100</t>
-  </si>
-  <si>
-    <t>OnDayEnd</t>
-  </si>
-  <si>
-    <t>至尊啾咪的狗</t>
+    <t>在直播结束后，粉丝+50</t>
+  </si>
+  <si>
+    <t>至尊雨王的狗</t>
   </si>
   <si>
     <t>进行杂谈练习后，杂谈力+6</t>
   </si>
   <si>
-    <t>至尊啾咪本体</t>
-  </si>
-  <si>
-    <t>获得A卡后，杂谈力+5</t>
+    <t>至尊雨王的心脏</t>
+  </si>
+  <si>
+    <t>进行社交后，杂谈力+3</t>
   </si>
   <si>
     <t>井井的话筒</t>
@@ -145,7 +175,7 @@
     <t>井井的光环</t>
   </si>
   <si>
-    <t>进行休息后，歌力+7</t>
+    <t>进行外出后，歌力+4</t>
   </si>
   <si>
     <t>柚子的手柄</t>
@@ -157,7 +187,7 @@
     <t>柚子的枕头</t>
   </si>
   <si>
-    <t>删除卡牌时，游戏力+10</t>
+    <t>进行休息后，游戏力+4</t>
   </si>
   <si>
     <t>画师麻麻的画笔</t>
@@ -248,9 +278,6 @@
 之后5回合开始时，抽一张牌</t>
   </si>
   <si>
-    <t>啤酒</t>
-  </si>
-  <si>
     <t>下一张卡会使用两次，体力消耗增加50%+2回合</t>
   </si>
   <si>
@@ -269,16 +296,16 @@
     <t>回合结束时，幽默+1</t>
   </si>
   <si>
-    <t>神爪</t>
+    <t>魔爪</t>
   </si>
   <si>
     <t>卡牌使用次数+1</t>
   </si>
   <si>
-    <t>茶</t>
-  </si>
-  <si>
-    <t>压力-1，体力-4</t>
+    <t>青岛啤酒</t>
+  </si>
+  <si>
+    <t>压力-1</t>
   </si>
 </sst>
 </file>
@@ -1231,15 +1258,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="12.1416666666667" customWidth="1"/>
+    <col min="1" max="1" width="3.08333333333333" customWidth="1"/>
     <col min="2" max="2" width="11.7083333333333" customWidth="1"/>
     <col min="3" max="3" width="15.425" customWidth="1"/>
     <col min="4" max="4" width="28.7083333333333" customWidth="1"/>
     <col min="5" max="5" width="14.7083333333333" customWidth="1"/>
-    <col min="6" max="6" width="15.425" customWidth="1"/>
+    <col min="6" max="6" width="13.4166666666667" customWidth="1"/>
     <col min="7" max="7" width="10.425" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1284,6 +1311,146 @@
       </c>
       <c r="G2" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1295,15 +1462,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="13.5916666666667" customWidth="1"/>
     <col min="3" max="3" width="25.5" customWidth="1"/>
-    <col min="4" max="4" width="23" customWidth="1"/>
-    <col min="5" max="5" width="9.425" customWidth="1"/>
+    <col min="4" max="4" width="12.0833333333333" customWidth="1"/>
+    <col min="5" max="5" width="5.5" customWidth="1"/>
     <col min="6" max="6" width="20.1416666666667" customWidth="1"/>
-    <col min="7" max="7" width="11.8583333333333" customWidth="1"/>
+    <col min="7" max="7" width="7.39166666666667" customWidth="1"/>
     <col min="8" max="8" width="10.2833333333333" customWidth="1"/>
     <col min="9" max="9" width="13.1416666666667" customWidth="1"/>
     <col min="10" max="10" width="17.1416666666667" customWidth="1"/>
@@ -1329,239 +1496,321 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="I1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="L1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="M1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="O1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="P1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="Q1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E3">
         <v>-1</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>37</v>
+      </c>
+      <c r="E4">
+        <v>-1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>30</v>
+      </c>
+      <c r="I4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>37</v>
+      </c>
+      <c r="E5">
+        <v>-1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>30</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>37</v>
+      </c>
+      <c r="E6">
+        <v>-1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6">
+        <v>28</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7">
+        <v>-1</v>
+      </c>
+      <c r="F7" t="s">
         <v>38</v>
       </c>
-      <c r="D7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>28</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>37</v>
+      </c>
+      <c r="E8">
+        <v>-1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+      <c r="H8">
+        <v>29</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>37</v>
+      </c>
+      <c r="E9">
+        <v>-1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9">
+        <v>29</v>
+      </c>
+      <c r="I9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>37</v>
+      </c>
+      <c r="E10">
+        <v>-1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15">
-        <v>13</v>
+        <v>37</v>
+      </c>
+      <c r="E11">
+        <v>-1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1602,28 +1851,28 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:8">
@@ -1631,19 +1880,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
@@ -1657,19 +1906,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G3" s="1">
         <v>15</v>
@@ -1683,19 +1932,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G4" s="1">
         <v>45</v>
@@ -1709,19 +1958,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G5" s="1">
         <v>11</v>
@@ -1735,19 +1984,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G6" s="1">
         <v>38</v>
@@ -1761,19 +2010,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G7" s="1">
         <v>13</v>
@@ -1799,19 +2048,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G8" s="1">
         <v>38</v>
@@ -1828,19 +2077,19 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
@@ -1859,20 +2108,18 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>71</v>
-      </c>
+      <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1889,19 +2136,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G11" s="1">
         <v>63</v>
@@ -1921,19 +2168,19 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G12" s="1">
         <v>65</v>
@@ -1947,19 +2194,19 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G13" s="1">
         <v>14</v>
@@ -1968,36 +2215,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G14" s="1">
         <v>4</v>
       </c>
       <c r="H14" s="1">
         <v>-1</v>
-      </c>
-      <c r="I14" s="1">
-        <v>3</v>
-      </c>
-      <c r="J14" s="1">
-        <v>-4</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FA4882-FC60-4301-BDEB-E564D4118CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -20,8 +26,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -311,361 +315,25 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -682,319 +350,28 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1252,22 +629,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.08333333333333" customWidth="1"/>
-    <col min="2" max="2" width="11.7083333333333" customWidth="1"/>
-    <col min="3" max="3" width="15.425" customWidth="1"/>
-    <col min="4" max="4" width="28.7083333333333" customWidth="1"/>
-    <col min="5" max="5" width="14.7083333333333" customWidth="1"/>
-    <col min="6" max="6" width="13.4166666666667" customWidth="1"/>
-    <col min="7" max="7" width="10.425" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1455,31 +832,29 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13.5916666666667" customWidth="1"/>
-    <col min="3" max="3" width="25.5" customWidth="1"/>
-    <col min="4" max="4" width="12.0833333333333" customWidth="1"/>
-    <col min="5" max="5" width="5.5" customWidth="1"/>
-    <col min="6" max="6" width="20.1416666666667" customWidth="1"/>
-    <col min="7" max="7" width="7.39166666666667" customWidth="1"/>
-    <col min="8" max="8" width="10.2833333333333" customWidth="1"/>
-    <col min="9" max="9" width="13.1416666666667" customWidth="1"/>
-    <col min="10" max="10" width="17.1416666666667" customWidth="1"/>
-    <col min="11" max="11" width="14.1416666666667" customWidth="1"/>
-    <col min="12" max="12" width="12.425" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="25.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" customWidth="1"/>
     <col min="13" max="13" width="17" customWidth="1"/>
-    <col min="14" max="14" width="11.8583333333333" customWidth="1"/>
-    <col min="15" max="15" width="11.5666666666667" customWidth="1"/>
-    <col min="16" max="16" width="17.1416666666667" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" customWidth="1"/>
+    <col min="15" max="15" width="11.5703125" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -1498,13 +873,13 @@
       <c r="E1" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G1" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="I1" t="s">
@@ -1513,7 +888,7 @@
       <c r="J1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="L1" t="s">
@@ -1522,7 +897,7 @@
       <c r="M1" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="1" t="s">
         <v>31</v>
       </c>
       <c r="O1" t="s">
@@ -1535,7 +910,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1564,7 +939,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1593,7 +968,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1622,7 +997,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:17">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1651,7 +1026,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1680,7 +1055,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1709,7 +1084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:17">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1738,7 +1113,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:17">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1767,7 +1142,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:17">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1790,7 +1165,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:17">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1815,434 +1190,428 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="8.66666666666667" style="1"/>
-    <col min="3" max="3" width="23.55" style="1" customWidth="1"/>
-    <col min="4" max="6" width="18.1416666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.8583333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.2833333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7083333333333" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.66666666666667" style="1"/>
+    <col min="3" max="3" width="23.5703125" customWidth="1"/>
+    <col min="4" max="6" width="18.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:8">
-      <c r="A2" s="1">
+    <row r="2" spans="1:12">
+      <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>62</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="1">
-        <v>3</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:8">
-      <c r="A3" s="1">
+    <row r="3" spans="1:12">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>61</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>66</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>63</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3">
         <v>15</v>
       </c>
-      <c r="H3" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1">
+      <c r="H3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>66</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4">
         <v>45</v>
       </c>
-      <c r="H4" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="H4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>61</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>63</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5">
         <v>11</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1">
+    <row r="6" spans="1:12">
+      <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>72</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>73</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6">
         <v>38</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6">
         <v>6</v>
       </c>
     </row>
-    <row r="7" ht="42" spans="1:12">
-      <c r="A7" s="1">
+    <row r="7" spans="1:12" ht="60">
+      <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>62</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7">
         <v>13</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7">
         <v>0.3</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7">
         <v>38</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7">
         <v>-2</v>
       </c>
-      <c r="K7" s="1">
+      <c r="K7">
         <v>21</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="28" spans="1:9">
-      <c r="A8" s="1">
+    <row r="8" spans="1:12" ht="30">
+      <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8">
         <v>38</v>
       </c>
-      <c r="H8" s="1">
-        <v>3</v>
-      </c>
-      <c r="I8" s="1">
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" ht="42" spans="1:10">
-      <c r="A9" s="1">
+    <row r="9" spans="1:12" ht="45">
+      <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>62</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9">
         <v>9</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9">
         <v>2</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9">
         <v>62</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="1">
+    <row r="10" spans="1:12">
+      <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>81</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10">
         <v>0</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10">
         <v>26</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="1">
+    <row r="11" spans="1:12">
+      <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>83</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11">
         <v>63</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11">
         <v>0.5</v>
       </c>
-      <c r="I11" s="1">
-        <v>3</v>
-      </c>
-      <c r="J11" s="1">
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11">
         <v>-2</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="1">
+    <row r="12" spans="1:12">
+      <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>85</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" t="s">
         <v>66</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12">
         <v>65</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="1">
+    <row r="13" spans="1:12">
+      <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>61</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13">
         <v>14</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="1">
+    <row r="14" spans="1:12">
+      <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14">
         <v>4</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="94">
   <si>
     <t>ID</t>
   </si>
@@ -193,13 +193,22 @@
     <t>画师麻麻的画笔</t>
   </si>
   <si>
-    <t>进行工作后，沪币+20</t>
+    <t>进行工作后，沪币+40</t>
   </si>
   <si>
     <t>画师麻麻的画板</t>
   </si>
   <si>
     <t>进行工作后，舰长+1</t>
+  </si>
+  <si>
+    <t>商店打折券</t>
+  </si>
+  <si>
+    <t>商店商品价格-25%</t>
+  </si>
+  <si>
+    <t>OnStoreLoadItems</t>
   </si>
   <si>
     <t>LiveType</t>
@@ -1462,7 +1471,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="13.5916666666667" customWidth="1"/>
@@ -1767,7 +1776,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1789,8 +1798,14 @@
       <c r="G10">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1811,6 +1826,38 @@
       </c>
       <c r="G11">
         <v>3</v>
+      </c>
+      <c r="H11">
+        <v>16</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12">
+        <v>-1</v>
+      </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12">
+        <v>45</v>
+      </c>
+      <c r="I12">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -1851,10 +1898,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>25</v>
@@ -1880,19 +1927,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
@@ -1906,19 +1953,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="E3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="G3" s="1">
         <v>15</v>
@@ -1932,19 +1979,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="G4" s="1">
         <v>45</v>
@@ -1958,19 +2005,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G5" s="1">
         <v>11</v>
@@ -1984,19 +2031,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G6" s="1">
         <v>38</v>
@@ -2010,19 +2057,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G7" s="1">
         <v>13</v>
@@ -2048,19 +2095,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="G8" s="1">
         <v>38</v>
@@ -2077,19 +2124,19 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
@@ -2108,18 +2155,17 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -2136,19 +2182,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G11" s="1">
         <v>63</v>
@@ -2168,19 +2214,19 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="G12" s="1">
         <v>65</v>
@@ -2194,19 +2240,19 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G13" s="1">
         <v>14</v>
@@ -2220,19 +2266,19 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G14" s="1">
         <v>4</v>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA12B664-6BC2-497B-8B0E-CE8A14A0F101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -320,361 +326,25 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -691,319 +361,28 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1261,22 +640,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.08333333333333" customWidth="1"/>
-    <col min="2" max="2" width="11.7083333333333" customWidth="1"/>
-    <col min="3" max="3" width="15.425" customWidth="1"/>
-    <col min="4" max="4" width="28.7083333333333" customWidth="1"/>
-    <col min="5" max="5" width="14.7083333333333" customWidth="1"/>
-    <col min="6" max="6" width="13.4166666666667" customWidth="1"/>
-    <col min="7" max="7" width="10.425" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1464,31 +843,29 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13.5916666666667" customWidth="1"/>
-    <col min="3" max="3" width="25.5" customWidth="1"/>
-    <col min="4" max="4" width="12.0833333333333" customWidth="1"/>
-    <col min="5" max="5" width="5.5" customWidth="1"/>
-    <col min="6" max="6" width="20.1416666666667" customWidth="1"/>
-    <col min="7" max="7" width="7.39166666666667" customWidth="1"/>
-    <col min="8" max="8" width="10.2833333333333" customWidth="1"/>
-    <col min="9" max="9" width="13.1416666666667" customWidth="1"/>
-    <col min="10" max="10" width="17.1416666666667" customWidth="1"/>
-    <col min="11" max="11" width="14.1416666666667" customWidth="1"/>
-    <col min="12" max="12" width="12.425" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="25.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" customWidth="1"/>
     <col min="13" max="13" width="17" customWidth="1"/>
-    <col min="14" max="14" width="11.8583333333333" customWidth="1"/>
-    <col min="15" max="15" width="11.5666666666667" customWidth="1"/>
-    <col min="16" max="16" width="17.1416666666667" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" customWidth="1"/>
+    <col min="15" max="15" width="11.5703125" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -1507,13 +884,13 @@
       <c r="E1" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G1" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="I1" t="s">
@@ -1522,7 +899,7 @@
       <c r="J1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="L1" t="s">
@@ -1531,7 +908,7 @@
       <c r="M1" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="1" t="s">
         <v>31</v>
       </c>
       <c r="O1" t="s">
@@ -1544,7 +921,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1573,7 +950,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1602,7 +979,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1631,7 +1008,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:17">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1660,7 +1037,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1689,7 +1066,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1718,7 +1095,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:17">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1747,7 +1124,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:17">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1776,7 +1153,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:17">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1805,7 +1182,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:17">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1834,7 +1211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:17">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1862,433 +1239,428 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="8.66666666666667" style="1"/>
-    <col min="3" max="3" width="23.55" style="1" customWidth="1"/>
-    <col min="4" max="6" width="18.1416666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.8583333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.2833333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7083333333333" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.66666666666667" style="1"/>
+    <col min="3" max="3" width="23.5703125" customWidth="1"/>
+    <col min="4" max="6" width="18.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:8">
-      <c r="A2" s="1">
+    <row r="2" spans="1:12">
+      <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="1">
-        <v>3</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:8">
-      <c r="A3" s="1">
+    <row r="3" spans="1:12">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>68</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>69</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3">
         <v>15</v>
       </c>
-      <c r="H3" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1">
+      <c r="H3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>71</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4">
         <v>45</v>
       </c>
-      <c r="H4" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="H4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>72</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>66</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5">
         <v>11</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1">
+    <row r="6" spans="1:12">
+      <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6">
         <v>38</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6">
         <v>6</v>
       </c>
     </row>
-    <row r="7" ht="42" spans="1:12">
-      <c r="A7" s="1">
+    <row r="7" spans="1:12" ht="60">
+      <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7">
         <v>13</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7">
         <v>0.3</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7">
         <v>38</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7">
         <v>-2</v>
       </c>
-      <c r="K7" s="1">
+      <c r="K7">
         <v>21</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="28" spans="1:9">
-      <c r="A8" s="1">
+    <row r="8" spans="1:12" ht="30">
+      <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8">
         <v>38</v>
       </c>
-      <c r="H8" s="1">
-        <v>3</v>
-      </c>
-      <c r="I8" s="1">
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" ht="42" spans="1:10">
-      <c r="A9" s="1">
+    <row r="9" spans="1:12" ht="45">
+      <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9">
         <v>9</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9">
         <v>2</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9">
         <v>62</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="1">
+    <row r="10" spans="1:12">
+      <c r="A10">
         <v>8</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>84</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10">
         <v>0</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10">
         <v>26</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="1">
+    <row r="11" spans="1:12">
+      <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" t="s">
         <v>69</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11">
         <v>63</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11">
         <v>0.5</v>
       </c>
-      <c r="I11" s="1">
-        <v>3</v>
-      </c>
-      <c r="J11" s="1">
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11">
         <v>-2</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="1">
+    <row r="12" spans="1:12">
+      <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>89</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" t="s">
         <v>69</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12">
         <v>65</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="1">
+    <row r="13" spans="1:12">
+      <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>91</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13">
         <v>14</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="1">
+    <row r="14" spans="1:12">
+      <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>93</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s">
         <v>76</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14">
         <v>4</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -136,7 +136,7 @@
     <t>Icon</t>
   </si>
   <si>
-    <t>墨镜</t>
+    <t>小室的头绳</t>
   </si>
   <si>
     <t>在外出结束后，粉丝+50</t>
@@ -166,7 +166,7 @@
     <t>进行社交后，杂谈力+3</t>
   </si>
   <si>
-    <t>井井的话筒</t>
+    <t>井井的麦克风</t>
   </si>
   <si>
     <t>进行歌力练习后，歌力+6</t>
@@ -202,7 +202,7 @@
     <t>进行工作后，舰长+1</t>
   </si>
   <si>
-    <t>商店打折券</t>
+    <t>商店会员卡</t>
   </si>
   <si>
     <t>商店商品价格-25%</t>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
+    <workbookView windowWidth="22190" windowHeight="9040" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="98">
   <si>
     <t>ID</t>
   </si>
@@ -209,6 +209,18 @@
   </si>
   <si>
     <t>OnStoreLoadItems</t>
+  </si>
+  <si>
+    <t>墨沫的龟壳</t>
+  </si>
+  <si>
+    <t>回合开始时，神采+2</t>
+  </si>
+  <si>
+    <t>VBattleRelic</t>
+  </si>
+  <si>
+    <t>OnTurnBeginBuffApply</t>
   </si>
   <si>
     <t>LiveType</t>
@@ -1471,7 +1483,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="13.5916666666667" customWidth="1"/>
@@ -1544,7 +1556,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1572,8 +1584,11 @@
       <c r="I2">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1601,8 +1616,11 @@
       <c r="I3">
         <v>50</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1630,8 +1648,11 @@
       <c r="I4">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1659,8 +1680,11 @@
       <c r="I5">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1688,8 +1712,11 @@
       <c r="I6">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1717,8 +1744,11 @@
       <c r="I7">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1746,8 +1776,11 @@
       <c r="I8">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1775,8 +1808,11 @@
       <c r="I9">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1804,8 +1840,11 @@
       <c r="I10">
         <v>40</v>
       </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1833,8 +1872,11 @@
       <c r="I11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1858,6 +1900,38 @@
       </c>
       <c r="I12">
         <v>0.25</v>
+      </c>
+      <c r="J12">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1898,10 +1972,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>25</v>
@@ -1927,19 +2001,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
@@ -1953,19 +2027,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G3" s="1">
         <v>15</v>
@@ -1979,19 +2053,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="G4" s="1">
         <v>45</v>
@@ -2005,19 +2079,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G5" s="1">
         <v>11</v>
@@ -2031,19 +2105,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G6" s="1">
         <v>38</v>
@@ -2057,19 +2131,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G7" s="1">
         <v>13</v>
@@ -2095,19 +2169,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="G8" s="1">
         <v>38</v>
@@ -2124,19 +2198,19 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
@@ -2156,16 +2230,16 @@
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -2182,19 +2256,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G11" s="1">
         <v>63</v>
@@ -2214,19 +2288,19 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="G12" s="1">
         <v>65</v>
@@ -2240,19 +2314,19 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G13" s="1">
         <v>14</v>
@@ -2266,19 +2340,19 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G14" s="1">
         <v>4</v>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F6AAB57-9312-41C2-A101-2839E87C591A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22190" windowHeight="9040" activeTab="1"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -20,8 +26,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -320,361 +324,25 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -691,319 +359,28 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1261,22 +638,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.08333333333333" customWidth="1"/>
-    <col min="2" max="2" width="11.7083333333333" customWidth="1"/>
-    <col min="3" max="3" width="15.425" customWidth="1"/>
-    <col min="4" max="4" width="28.7083333333333" customWidth="1"/>
-    <col min="5" max="5" width="14.7083333333333" customWidth="1"/>
-    <col min="6" max="6" width="13.4166666666667" customWidth="1"/>
-    <col min="7" max="7" width="10.425" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1464,31 +841,29 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13.5916666666667" customWidth="1"/>
-    <col min="3" max="3" width="25.5" customWidth="1"/>
-    <col min="4" max="4" width="12.0833333333333" customWidth="1"/>
-    <col min="5" max="5" width="5.5" customWidth="1"/>
-    <col min="6" max="6" width="20.1416666666667" customWidth="1"/>
-    <col min="7" max="7" width="7.39166666666667" customWidth="1"/>
-    <col min="8" max="8" width="10.2833333333333" customWidth="1"/>
-    <col min="9" max="9" width="13.1416666666667" customWidth="1"/>
-    <col min="10" max="10" width="17.1416666666667" customWidth="1"/>
-    <col min="11" max="11" width="14.1416666666667" customWidth="1"/>
-    <col min="12" max="12" width="12.425" customWidth="1"/>
-    <col min="13" max="13" width="17" customWidth="1"/>
-    <col min="14" max="14" width="11.8583333333333" customWidth="1"/>
-    <col min="15" max="15" width="11.5666666666667" customWidth="1"/>
-    <col min="16" max="16" width="17.1416666666667" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="25.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" customWidth="1"/>
+    <col min="6" max="7" width="20.140625" customWidth="1"/>
+    <col min="8" max="8" width="7.42578125" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="11" max="11" width="17.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
+    <col min="15" max="15" width="11.85546875" customWidth="1"/>
+    <col min="16" max="16" width="11.5703125" customWidth="1"/>
+    <col min="17" max="17" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -1507,44 +882,44 @@
       <c r="E1" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>26</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>29</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>32</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1563,17 +938,17 @@
       <c r="F2" t="s">
         <v>38</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>0</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>15</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1592,17 +967,17 @@
       <c r="F3" t="s">
         <v>38</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>1</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>15</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1621,17 +996,17 @@
       <c r="F4" t="s">
         <v>38</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>5</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>30</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:17">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1650,17 +1025,17 @@
       <c r="F5" t="s">
         <v>38</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>2</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>30</v>
       </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1679,17 +1054,17 @@
       <c r="F6" t="s">
         <v>38</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>6</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>28</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1708,17 +1083,17 @@
       <c r="F7" t="s">
         <v>38</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>28</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:17">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1737,17 +1112,17 @@
       <c r="F8" t="s">
         <v>38</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>7</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>29</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:17">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1766,17 +1141,17 @@
       <c r="F9" t="s">
         <v>38</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>4</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>29</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:17">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1795,17 +1170,17 @@
       <c r="F10" t="s">
         <v>38</v>
       </c>
-      <c r="G10">
-        <v>3</v>
-      </c>
       <c r="H10">
+        <v>3</v>
+      </c>
+      <c r="I10">
         <v>5</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:17">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1824,17 +1199,17 @@
       <c r="F11" t="s">
         <v>38</v>
       </c>
-      <c r="G11">
-        <v>3</v>
-      </c>
       <c r="H11">
+        <v>3</v>
+      </c>
+      <c r="I11">
         <v>16</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:17">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1853,442 +1228,438 @@
       <c r="F12" t="s">
         <v>59</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>45</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>0.25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="8.66666666666667" style="1"/>
-    <col min="3" max="3" width="23.55" style="1" customWidth="1"/>
-    <col min="4" max="6" width="18.1416666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.8583333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.2833333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7083333333333" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.66666666666667" style="1"/>
+    <col min="3" max="3" width="23.5703125" customWidth="1"/>
+    <col min="4" max="6" width="18.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:8">
-      <c r="A2" s="1">
+    <row r="2" spans="1:12">
+      <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="1">
-        <v>3</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:8">
-      <c r="A3" s="1">
+    <row r="3" spans="1:12">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>68</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>69</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3">
         <v>15</v>
       </c>
-      <c r="H3" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1">
+      <c r="H3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>71</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4">
         <v>45</v>
       </c>
-      <c r="H4" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="H4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>72</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>66</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5">
         <v>11</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1">
+    <row r="6" spans="1:12">
+      <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6">
         <v>38</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6">
         <v>6</v>
       </c>
     </row>
-    <row r="7" ht="42" spans="1:12">
-      <c r="A7" s="1">
+    <row r="7" spans="1:12" ht="60">
+      <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7">
         <v>13</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7">
         <v>0.3</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7">
         <v>38</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7">
         <v>-2</v>
       </c>
-      <c r="K7" s="1">
+      <c r="K7">
         <v>21</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="28" spans="1:9">
-      <c r="A8" s="1">
+    <row r="8" spans="1:12" ht="30">
+      <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8">
         <v>38</v>
       </c>
-      <c r="H8" s="1">
-        <v>3</v>
-      </c>
-      <c r="I8" s="1">
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" ht="42" spans="1:10">
-      <c r="A9" s="1">
+    <row r="9" spans="1:12" ht="45">
+      <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9">
         <v>9</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9">
         <v>2</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9">
         <v>62</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="1">
+    <row r="10" spans="1:12">
+      <c r="A10">
         <v>8</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>84</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10">
         <v>0</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10">
         <v>26</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="1">
+    <row r="11" spans="1:12">
+      <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" t="s">
         <v>69</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11">
         <v>63</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11">
         <v>0.5</v>
       </c>
-      <c r="I11" s="1">
-        <v>3</v>
-      </c>
-      <c r="J11" s="1">
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11">
         <v>-2</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="1">
+    <row r="12" spans="1:12">
+      <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>89</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" t="s">
         <v>69</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12">
         <v>65</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="1">
+    <row r="13" spans="1:12">
+      <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>91</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13">
         <v>14</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="1">
+    <row r="14" spans="1:12">
+      <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>93</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s">
         <v>76</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14">
         <v>4</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22190" windowHeight="9040" activeTab="1"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="99">
   <si>
     <t>ID</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>WhenToApply</t>
+  </si>
+  <si>
+    <t>icon</t>
   </si>
   <si>
     <t>Condition</t>
@@ -1483,7 +1486,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="13.5916666666667" customWidth="1"/>
@@ -1491,19 +1494,20 @@
     <col min="4" max="4" width="12.0833333333333" customWidth="1"/>
     <col min="5" max="5" width="5.5" customWidth="1"/>
     <col min="6" max="6" width="20.1416666666667" customWidth="1"/>
-    <col min="7" max="7" width="7.39166666666667" customWidth="1"/>
-    <col min="8" max="8" width="10.2833333333333" customWidth="1"/>
-    <col min="9" max="9" width="13.1416666666667" customWidth="1"/>
-    <col min="10" max="10" width="17.1416666666667" customWidth="1"/>
-    <col min="11" max="11" width="14.1416666666667" customWidth="1"/>
-    <col min="12" max="12" width="12.425" customWidth="1"/>
-    <col min="13" max="13" width="17" customWidth="1"/>
-    <col min="14" max="14" width="11.8583333333333" customWidth="1"/>
-    <col min="15" max="15" width="11.5666666666667" customWidth="1"/>
-    <col min="16" max="16" width="17.1416666666667" customWidth="1"/>
+    <col min="7" max="7" width="3.91666666666667" customWidth="1"/>
+    <col min="8" max="8" width="7.39166666666667" customWidth="1"/>
+    <col min="9" max="9" width="10.2833333333333" customWidth="1"/>
+    <col min="10" max="10" width="13.1416666666667" customWidth="1"/>
+    <col min="11" max="11" width="17.1416666666667" customWidth="1"/>
+    <col min="12" max="12" width="14.1416666666667" customWidth="1"/>
+    <col min="13" max="13" width="12.425" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
+    <col min="15" max="15" width="11.8583333333333" customWidth="1"/>
+    <col min="16" max="16" width="11.5666666666667" customWidth="1"/>
+    <col min="17" max="17" width="17.1416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1522,31 +1526,31 @@
       <c r="F1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="3" t="s">
         <v>26</v>
       </c>
       <c r="J1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" t="s">
         <v>28</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="3" t="s">
         <v>29</v>
       </c>
       <c r="M1" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="3" t="s">
         <v>32</v>
       </c>
       <c r="P1" t="s">
@@ -1555,382 +1559,385 @@
       <c r="Q1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="R1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2">
         <v>-1</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2">
+        <v>39</v>
+      </c>
+      <c r="H2">
         <v>0</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>15</v>
-      </c>
-      <c r="I2">
-        <v>50</v>
       </c>
       <c r="J2">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E3">
         <v>-1</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3">
+        <v>39</v>
+      </c>
+      <c r="H3">
         <v>1</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>15</v>
-      </c>
-      <c r="I3">
-        <v>50</v>
       </c>
       <c r="J3">
         <v>50</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4">
         <v>-1</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4">
+        <v>39</v>
+      </c>
+      <c r="H4">
         <v>5</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>30</v>
-      </c>
-      <c r="I4">
-        <v>6</v>
       </c>
       <c r="J4">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5">
         <v>-1</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5">
+        <v>39</v>
+      </c>
+      <c r="H5">
         <v>2</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>30</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
       </c>
       <c r="J5">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6">
         <v>-1</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6">
+        <v>39</v>
+      </c>
+      <c r="H6">
         <v>6</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>28</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
       </c>
       <c r="J6">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="K6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <v>-1</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7">
+        <v>39</v>
+      </c>
+      <c r="H7">
         <v>0</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>28</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
       </c>
       <c r="J7">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="K7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8">
         <v>-1</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8">
+        <v>39</v>
+      </c>
+      <c r="H8">
         <v>7</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>29</v>
-      </c>
-      <c r="I8">
-        <v>6</v>
       </c>
       <c r="J8">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E9">
         <v>-1</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9">
+        <v>39</v>
+      </c>
+      <c r="H9">
         <v>4</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>29</v>
-      </c>
-      <c r="I9">
-        <v>4</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="K9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E10">
         <v>-1</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10">
+        <v>39</v>
+      </c>
+      <c r="H10">
         <v>3</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>5</v>
-      </c>
-      <c r="I10">
-        <v>40</v>
       </c>
       <c r="J10">
         <v>40</v>
       </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="K10">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E11">
         <v>-1</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11">
+        <v>39</v>
+      </c>
+      <c r="H11">
         <v>3</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>16</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="K11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E12">
         <v>-1</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
-      </c>
-      <c r="H12">
+        <v>60</v>
+      </c>
+      <c r="I12">
         <v>45</v>
-      </c>
-      <c r="I12">
-        <v>0.25</v>
       </c>
       <c r="J12">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="K12">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
-      </c>
-      <c r="H13">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="I13">
         <v>2</v>
       </c>
       <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13">
         <v>2</v>
       </c>
     </row>
@@ -1972,28 +1979,28 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:8">
@@ -2001,19 +2008,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
@@ -2027,19 +2034,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="G3" s="1">
         <v>15</v>
@@ -2053,19 +2060,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G4" s="1">
         <v>45</v>
@@ -2079,19 +2086,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G5" s="1">
         <v>11</v>
@@ -2105,19 +2112,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G6" s="1">
         <v>38</v>
@@ -2131,19 +2138,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="G7" s="1">
         <v>13</v>
@@ -2169,19 +2176,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G8" s="1">
         <v>38</v>
@@ -2198,19 +2205,19 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G9" s="1">
         <v>9</v>
@@ -2230,16 +2237,16 @@
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -2256,19 +2263,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="G11" s="1">
         <v>63</v>
@@ -2288,19 +2295,19 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G12" s="1">
         <v>65</v>
@@ -2314,19 +2321,19 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G13" s="1">
         <v>14</v>
@@ -2340,19 +2347,19 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G14" s="1">
         <v>4</v>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
+    <workbookView windowWidth="22190" windowHeight="9040" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -181,13 +181,13 @@
     <t>进行外出后，歌力+4</t>
   </si>
   <si>
-    <t>柚子的手柄</t>
+    <t>柚子茶的手柄</t>
   </si>
   <si>
     <t>进行游戏练习后，游戏力+6</t>
   </si>
   <si>
-    <t>柚子的枕头</t>
+    <t>柚子茶的枕头</t>
   </si>
   <si>
     <t>进行休息后，游戏力+4</t>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F4E41E-5D89-4DDC-9E7E-BF51ABEBD723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="22190" windowHeight="9040" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -26,6 +20,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="106">
   <si>
     <t>ID</t>
   </si>
@@ -83,6 +79,9 @@
     <t>工作事件</t>
   </si>
   <si>
+    <t>Work</t>
+  </si>
+  <si>
     <t>休息事件</t>
   </si>
   <si>
@@ -225,6 +224,27 @@
   </si>
   <si>
     <t>OnTurnBeginBuffApply</t>
+  </si>
+  <si>
+    <t>唱歌的心得</t>
+  </si>
+  <si>
+    <t>删除卡牌时歌力+12</t>
+  </si>
+  <si>
+    <t>游戏的心得</t>
+  </si>
+  <si>
+    <t>删除卡牌时游戏力+12</t>
+  </si>
+  <si>
+    <t>杂谈的心得</t>
+  </si>
+  <si>
+    <t>删除卡牌时杂谈力+12</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>LiveType</t>
@@ -331,33 +351,366 @@
   </si>
   <si>
     <t>压力-1</t>
-  </si>
-  <si>
-    <t>Work</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -374,9 +727,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -385,17 +980,61 @@
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -653,22 +1292,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="3.140625" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="3.14166666666667" customWidth="1"/>
+    <col min="2" max="2" width="11.7083333333333" customWidth="1"/>
+    <col min="3" max="3" width="15.425" customWidth="1"/>
+    <col min="4" max="4" width="28.7083333333333" customWidth="1"/>
+    <col min="5" max="5" width="14.7083333333333" customWidth="1"/>
+    <col min="6" max="6" width="13.425" customWidth="1"/>
+    <col min="7" max="7" width="10.425" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -771,7 +1410,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -779,7 +1418,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
@@ -791,7 +1430,7 @@
         <v>3</v>
       </c>
       <c r="G6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -799,7 +1438,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
@@ -819,7 +1458,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
@@ -839,7 +1478,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
@@ -856,33 +1495,35 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:R19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="13.5703125" customWidth="1"/>
-    <col min="3" max="3" width="25.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" customWidth="1"/>
-    <col min="5" max="5" width="5.42578125" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" customWidth="1"/>
-    <col min="7" max="7" width="3.85546875" customWidth="1"/>
-    <col min="8" max="8" width="7.42578125" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" customWidth="1"/>
-    <col min="11" max="11" width="17.140625" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.5666666666667" customWidth="1"/>
+    <col min="3" max="3" width="25.425" customWidth="1"/>
+    <col min="4" max="4" width="12.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="5.425" customWidth="1"/>
+    <col min="6" max="6" width="20.1416666666667" customWidth="1"/>
+    <col min="7" max="7" width="3.85833333333333" customWidth="1"/>
+    <col min="8" max="8" width="7.425" customWidth="1"/>
+    <col min="9" max="9" width="10.2833333333333" customWidth="1"/>
+    <col min="10" max="10" width="13.1416666666667" customWidth="1"/>
+    <col min="11" max="11" width="17.1416666666667" customWidth="1"/>
+    <col min="12" max="12" width="14.1416666666667" customWidth="1"/>
+    <col min="13" max="13" width="12.425" customWidth="1"/>
     <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="11.85546875" customWidth="1"/>
-    <col min="16" max="16" width="11.5703125" customWidth="1"/>
-    <col min="17" max="17" width="17.140625" customWidth="1"/>
+    <col min="15" max="15" width="11.8583333333333" customWidth="1"/>
+    <col min="16" max="16" width="11.5666666666667" customWidth="1"/>
+    <col min="17" max="17" width="17.1416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="30">
+    <row r="1" ht="28" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -896,66 +1537,66 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2">
         <v>-1</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -970,24 +1611,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E3">
         <v>-1</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -1002,24 +1643,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4">
         <v>-1</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -1034,24 +1675,24 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5">
         <v>-1</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -1066,24 +1707,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6">
         <v>-1</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -1098,24 +1739,24 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <v>-1</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1130,24 +1771,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8">
         <v>-1</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H8">
         <v>7</v>
@@ -1162,24 +1803,24 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E9">
         <v>-1</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H9">
         <v>4</v>
@@ -1194,24 +1835,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E10">
         <v>-1</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H10">
         <v>3</v>
@@ -1226,24 +1867,24 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E11">
         <v>-1</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -1258,24 +1899,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E12">
         <v>-1</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I12">
         <v>45</v>
@@ -1287,24 +1928,24 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I13">
         <v>2</v>
@@ -1316,24 +1957,82 @@
         <v>2</v>
       </c>
     </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" t="s">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.70833333333333" defaultRowHeight="14"/>
   <cols>
-    <col min="3" max="3" width="23.5703125" customWidth="1"/>
-    <col min="4" max="6" width="18.140625" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="3" max="3" width="23.5666666666667" customWidth="1"/>
+    <col min="4" max="6" width="18.1416666666667" customWidth="1"/>
+    <col min="7" max="7" width="10.5666666666667" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" customWidth="1"/>
+    <col min="9" max="9" width="12.8583333333333" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="11.28515625" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.2833333333333" customWidth="1"/>
+    <col min="12" max="12" width="10.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1350,48 +2049,48 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G2">
         <v>3</v>
@@ -1400,24 +2099,24 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G3">
         <v>15</v>
@@ -1426,24 +2125,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F4" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G4">
         <v>45</v>
@@ -1452,24 +2151,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" t="s">
         <v>76</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>77</v>
       </c>
-      <c r="D5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" t="s">
-        <v>69</v>
-      </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G5">
         <v>11</v>
@@ -1478,24 +2177,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G6">
         <v>38</v>
@@ -1504,24 +2203,24 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="60">
+    <row r="7" ht="42" spans="1:12">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G7">
         <v>13</v>
@@ -1542,24 +2241,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="30">
+    <row r="8" ht="28" spans="1:9">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G8">
         <v>38</v>
@@ -1571,24 +2270,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="45">
+    <row r="9" ht="42" spans="1:10">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G9">
         <v>9</v>
@@ -1603,21 +2302,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1629,24 +2328,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G11">
         <v>63</v>
@@ -1661,24 +2360,24 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E12" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G12">
         <v>65</v>
@@ -1687,24 +2386,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G13">
         <v>14</v>
@@ -1713,24 +2412,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="D14" t="s">
-        <v>80</v>
-      </c>
-      <c r="E14" t="s">
-        <v>69</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="G14">
         <v>4</v>
@@ -1741,5 +2440,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22190" windowHeight="9040" activeTab="1"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="107">
   <si>
     <t>ID</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>删除卡牌时歌力+12</t>
+  </si>
+  <si>
+    <t>OnCardRemoved</t>
   </si>
   <si>
     <t>游戏的心得</t>
@@ -1957,7 +1960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1973,16 +1976,25 @@
       <c r="E14">
         <v>-1</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14">
+        <v>28</v>
+      </c>
+      <c r="J14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
         <v>38</v>
@@ -1990,16 +2002,25 @@
       <c r="E15">
         <v>-1</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15">
+        <v>29</v>
+      </c>
+      <c r="J15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
         <v>38</v>
@@ -2007,10 +2028,19 @@
       <c r="E16">
         <v>-1</v>
       </c>
+      <c r="F16" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16">
+        <v>30</v>
+      </c>
+      <c r="J16">
+        <v>12</v>
+      </c>
     </row>
     <row r="19" spans="3:3">
       <c r="C19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2049,10 +2079,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>26</v>
@@ -2078,19 +2108,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G2">
         <v>3</v>
@@ -2104,19 +2134,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3" t="s">
         <v>79</v>
-      </c>
-      <c r="C3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F3" t="s">
-        <v>78</v>
       </c>
       <c r="G3">
         <v>15</v>
@@ -2130,19 +2160,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" t="s">
         <v>82</v>
       </c>
-      <c r="C4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" t="s">
-        <v>81</v>
-      </c>
       <c r="F4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G4">
         <v>45</v>
@@ -2156,19 +2186,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G5">
         <v>11</v>
@@ -2182,19 +2212,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G6">
         <v>38</v>
@@ -2208,19 +2238,19 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="G7">
         <v>13</v>
@@ -2246,19 +2276,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G8">
         <v>38</v>
@@ -2275,19 +2305,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9">
         <v>9</v>
@@ -2307,16 +2337,16 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2333,19 +2363,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="C11" t="s">
-        <v>99</v>
-      </c>
-      <c r="D11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="G11">
         <v>63</v>
@@ -2365,19 +2395,19 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G12">
         <v>65</v>
@@ -2391,19 +2421,19 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G13">
         <v>14</v>
@@ -2417,19 +2447,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G14">
         <v>4</v>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
+    <workbookView windowWidth="22190" windowHeight="9040" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="106">
   <si>
     <t>ID</t>
   </si>
@@ -326,6 +326,9 @@
 之后5回合开始时，抽一张牌</t>
   </si>
   <si>
+    <t>神秘饮品</t>
+  </si>
+  <si>
     <t>下一张卡会使用两次，体力消耗增加50%+2回合</t>
   </si>
   <si>
@@ -348,12 +351,6 @@
   </si>
   <si>
     <t>卡牌使用次数+1</t>
-  </si>
-  <si>
-    <t>青岛啤酒</t>
-  </si>
-  <si>
-    <t>压力-1</t>
   </si>
 </sst>
 </file>
@@ -2336,8 +2333,11 @@
       <c r="A10">
         <v>8</v>
       </c>
+      <c r="B10" t="s">
+        <v>97</v>
+      </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
         <v>77</v>
@@ -2346,7 +2346,7 @@
         <v>78</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2363,10 +2363,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
         <v>77</v>
@@ -2375,7 +2375,7 @@
         <v>82</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G11">
         <v>63</v>
@@ -2395,10 +2395,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
         <v>77</v>
@@ -2407,7 +2407,7 @@
         <v>82</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G12">
         <v>65</v>
@@ -2421,10 +2421,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
         <v>77</v>
@@ -2433,7 +2433,7 @@
         <v>78</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G13">
         <v>14</v>
@@ -2442,31 +2442,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>105</v>
-      </c>
-      <c r="C14" t="s">
-        <v>106</v>
-      </c>
-      <c r="D14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="G14">
-        <v>4</v>
-      </c>
-      <c r="H14">
-        <v>-1</v>
-      </c>
+    <row r="14" spans="6:6">
+      <c r="F14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC1CA57-2F2B-4B45-822E-64918E6D2E94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22190" windowHeight="9040" activeTab="2"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -20,8 +26,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -29,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="106">
   <si>
     <t>ID</t>
   </si>
@@ -356,361 +360,25 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -727,314 +395,29 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1292,22 +675,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="3.14166666666667" customWidth="1"/>
-    <col min="2" max="2" width="11.7083333333333" customWidth="1"/>
-    <col min="3" max="3" width="15.425" customWidth="1"/>
-    <col min="4" max="4" width="28.7083333333333" customWidth="1"/>
-    <col min="5" max="5" width="14.7083333333333" customWidth="1"/>
-    <col min="6" max="6" width="13.425" customWidth="1"/>
-    <col min="7" max="7" width="10.425" customWidth="1"/>
+    <col min="1" max="1" width="3.1796875" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="4" max="4" width="28.7265625" customWidth="1"/>
+    <col min="5" max="5" width="14.7265625" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" customWidth="1"/>
+    <col min="7" max="7" width="10.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1495,35 +878,33 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="13.5666666666667" customWidth="1"/>
-    <col min="3" max="3" width="25.425" customWidth="1"/>
-    <col min="4" max="4" width="12.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="5.425" customWidth="1"/>
-    <col min="6" max="6" width="20.1416666666667" customWidth="1"/>
-    <col min="7" max="7" width="3.85833333333333" customWidth="1"/>
-    <col min="8" max="8" width="7.425" customWidth="1"/>
-    <col min="9" max="9" width="10.2833333333333" customWidth="1"/>
-    <col min="10" max="10" width="13.1416666666667" customWidth="1"/>
-    <col min="11" max="11" width="17.1416666666667" customWidth="1"/>
-    <col min="12" max="12" width="14.1416666666667" customWidth="1"/>
-    <col min="13" max="13" width="12.425" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" customWidth="1"/>
+    <col min="3" max="3" width="25.453125" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" customWidth="1"/>
+    <col min="5" max="5" width="5.453125" customWidth="1"/>
+    <col min="6" max="6" width="20.1796875" customWidth="1"/>
+    <col min="7" max="7" width="3.81640625" customWidth="1"/>
+    <col min="8" max="8" width="7.453125" customWidth="1"/>
+    <col min="9" max="9" width="10.26953125" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
+    <col min="11" max="11" width="17.1796875" customWidth="1"/>
+    <col min="12" max="12" width="14.1796875" customWidth="1"/>
+    <col min="13" max="13" width="12.453125" customWidth="1"/>
     <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="11.8583333333333" customWidth="1"/>
-    <col min="16" max="16" width="11.5666666666667" customWidth="1"/>
-    <col min="17" max="17" width="17.1416666666667" customWidth="1"/>
+    <col min="15" max="15" width="11.81640625" customWidth="1"/>
+    <col min="16" max="16" width="11.54296875" customWidth="1"/>
+    <col min="17" max="17" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" spans="1:18">
+    <row r="1" spans="1:18" ht="29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1579,7 +960,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1611,7 +992,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1643,7 +1024,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1675,7 +1056,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1707,7 +1088,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1739,7 +1120,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1771,7 +1152,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1803,7 +1184,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1835,7 +1216,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1867,7 +1248,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1899,7 +1280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1928,7 +1309,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:18">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1957,7 +1338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:18">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1983,7 +1364,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2009,7 +1390,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:18">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2042,27 +1423,25 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultColWidth="8.70833333333333" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:M14"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="23.5666666666667" customWidth="1"/>
-    <col min="4" max="6" width="18.1416666666667" customWidth="1"/>
-    <col min="7" max="7" width="10.5666666666667" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="12.8583333333333" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="11.2833333333333" customWidth="1"/>
-    <col min="12" max="12" width="10.7083333333333" customWidth="1"/>
+    <col min="3" max="3" width="23.54296875" customWidth="1"/>
+    <col min="4" max="7" width="18.1796875" customWidth="1"/>
+    <col min="8" max="8" width="10.54296875" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="12.81640625" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="11.26953125" customWidth="1"/>
+    <col min="13" max="13" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2081,26 +1460,29 @@
       <c r="F1" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2119,14 +1501,14 @@
       <c r="F2" t="s">
         <v>79</v>
       </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
       <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2145,14 +1527,14 @@
       <c r="F3" t="s">
         <v>79</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>15</v>
       </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2171,14 +1553,14 @@
       <c r="F4" t="s">
         <v>79</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>45</v>
       </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2197,14 +1579,14 @@
       <c r="F5" t="s">
         <v>79</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>11</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2223,14 +1605,15 @@
       <c r="F6" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="3"/>
+      <c r="H6">
         <v>38</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>6</v>
       </c>
     </row>
-    <row r="7" ht="42" spans="1:12">
+    <row r="7" spans="1:13" ht="43.5">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2249,26 +1632,27 @@
       <c r="F7" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="3"/>
+      <c r="H7">
         <v>13</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>0.3</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>38</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>-2</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>21</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="28" spans="1:9">
+    <row r="8" spans="1:13" ht="29">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2287,17 +1671,18 @@
       <c r="F8" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="3"/>
+      <c r="H8">
         <v>38</v>
       </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
       <c r="I8">
+        <v>3</v>
+      </c>
+      <c r="J8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" ht="42" spans="1:10">
+    <row r="9" spans="1:13" ht="43.5">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2316,20 +1701,21 @@
       <c r="F9" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="3"/>
+      <c r="H9">
         <v>9</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>2</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>62</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2348,17 +1734,18 @@
       <c r="F10" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="3"/>
+      <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>26</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2377,20 +1764,21 @@
       <c r="F11" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="3"/>
+      <c r="H11">
         <v>63</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>0.5</v>
       </c>
-      <c r="I11">
-        <v>3</v>
-      </c>
       <c r="J11">
+        <v>3</v>
+      </c>
+      <c r="K11">
         <v>-2</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:13">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2409,14 +1797,15 @@
       <c r="F12" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="3"/>
+      <c r="H12">
         <v>65</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:13">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2435,18 +1824,19 @@
       <c r="F13" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="3"/>
+      <c r="H13">
         <v>14</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="6:6">
+    <row r="14" spans="1:13">
       <c r="F14" s="1"/>
+      <c r="G14" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC1CA57-2F2B-4B45-822E-64918E6D2E94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E68404-F6D8-494B-9F46-D016D755E1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -399,13 +399,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -682,15 +681,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.1796875" customWidth="1"/>
-    <col min="2" max="2" width="11.7265625" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
-    <col min="4" max="4" width="28.7265625" customWidth="1"/>
-    <col min="5" max="5" width="14.7265625" customWidth="1"/>
-    <col min="6" max="6" width="13.453125" customWidth="1"/>
-    <col min="7" max="7" width="10.453125" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -884,27 +883,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13.54296875" customWidth="1"/>
-    <col min="3" max="3" width="25.453125" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" customWidth="1"/>
-    <col min="5" max="5" width="5.453125" customWidth="1"/>
-    <col min="6" max="6" width="20.1796875" customWidth="1"/>
-    <col min="7" max="7" width="3.81640625" customWidth="1"/>
-    <col min="8" max="8" width="7.453125" customWidth="1"/>
-    <col min="9" max="9" width="10.26953125" customWidth="1"/>
-    <col min="10" max="10" width="13.1796875" customWidth="1"/>
-    <col min="11" max="11" width="17.1796875" customWidth="1"/>
-    <col min="12" max="12" width="14.1796875" customWidth="1"/>
-    <col min="13" max="13" width="12.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="25.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" customWidth="1"/>
+    <col min="7" max="7" width="3.85546875" customWidth="1"/>
+    <col min="8" max="8" width="7.42578125" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="11" max="11" width="17.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
     <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="11.81640625" customWidth="1"/>
-    <col min="16" max="16" width="11.54296875" customWidth="1"/>
-    <col min="17" max="17" width="17.1796875" customWidth="1"/>
+    <col min="15" max="15" width="11.85546875" customWidth="1"/>
+    <col min="16" max="16" width="11.5703125" customWidth="1"/>
+    <col min="17" max="17" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="29">
+    <row r="1" spans="1:18" ht="30">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1429,16 +1428,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="23.54296875" customWidth="1"/>
-    <col min="4" max="7" width="18.1796875" customWidth="1"/>
-    <col min="8" max="8" width="10.54296875" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" customWidth="1"/>
+    <col min="4" max="7" width="18.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="12.81640625" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="11.26953125" customWidth="1"/>
-    <col min="13" max="13" width="10.7265625" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -1605,7 +1604,6 @@
       <c r="F6" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G6" s="3"/>
       <c r="H6">
         <v>38</v>
       </c>
@@ -1613,7 +1611,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="43.5">
+    <row r="7" spans="1:13" ht="60">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1632,7 +1630,6 @@
       <c r="F7" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G7" s="3"/>
       <c r="H7">
         <v>13</v>
       </c>
@@ -1652,7 +1649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="29">
+    <row r="8" spans="1:13" ht="30">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1671,7 +1668,6 @@
       <c r="F8" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G8" s="3"/>
       <c r="H8">
         <v>38</v>
       </c>
@@ -1682,7 +1678,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="43.5">
+    <row r="9" spans="1:13" ht="45">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1701,7 +1697,6 @@
       <c r="F9" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G9" s="3"/>
       <c r="H9">
         <v>9</v>
       </c>
@@ -1734,7 +1729,6 @@
       <c r="F10" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G10" s="3"/>
       <c r="H10">
         <v>0</v>
       </c>
@@ -1764,7 +1758,6 @@
       <c r="F11" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G11" s="3"/>
       <c r="H11">
         <v>63</v>
       </c>
@@ -1797,7 +1790,6 @@
       <c r="F12" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G12" s="3"/>
       <c r="H12">
         <v>65</v>
       </c>
@@ -1824,7 +1816,6 @@
       <c r="F13" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G13" s="3"/>
       <c r="H13">
         <v>14</v>
       </c>
@@ -1834,7 +1825,6 @@
     </row>
     <row r="14" spans="1:13">
       <c r="F14" s="1"/>
-      <c r="G14" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC1CA57-2F2B-4B45-822E-64918E6D2E94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -26,6 +20,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="190">
   <si>
     <t>ID</t>
   </si>
@@ -101,6 +97,42 @@
     <t>游戏练习事件</t>
   </si>
   <si>
+    <t>唱歌回合</t>
+  </si>
+  <si>
+    <t>VAttributeTurnGainRateModifierEffect</t>
+  </si>
+  <si>
+    <t>游戏回合</t>
+  </si>
+  <si>
+    <t>杂谈回合</t>
+  </si>
+  <si>
+    <t>每使用两张卡牌时</t>
+  </si>
+  <si>
+    <t>VCardTypeUsedCountCondition</t>
+  </si>
+  <si>
+    <t>属性减少时</t>
+  </si>
+  <si>
+    <t>VRaisingRelicAttributeCondition</t>
+  </si>
+  <si>
+    <t>LessThan</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>属性增加时</t>
+  </si>
+  <si>
+    <t>GreaterThan</t>
+  </si>
+  <si>
     <t>Layer</t>
   </si>
   <si>
@@ -230,28 +262,208 @@
     <t>OnTurnBeginBuffApply</t>
   </si>
   <si>
+    <t>唱歌的技巧</t>
+  </si>
+  <si>
+    <t>删除卡牌时歌力+8</t>
+  </si>
+  <si>
+    <t>OnCardRemoved</t>
+  </si>
+  <si>
+    <t>游戏的技巧</t>
+  </si>
+  <si>
+    <t>删除卡牌时游戏力+8</t>
+  </si>
+  <si>
+    <t>杂谈的技巧</t>
+  </si>
+  <si>
+    <t>删除卡牌时杂谈力+8</t>
+  </si>
+  <si>
     <t>唱歌的心得</t>
   </si>
   <si>
-    <t>删除卡牌时歌力+12</t>
-  </si>
-  <si>
-    <t>OnCardRemoved</t>
+    <t>直播开始时，神采+8</t>
+  </si>
+  <si>
+    <t>OnBattleBegin</t>
   </si>
   <si>
     <t>游戏的心得</t>
   </si>
   <si>
-    <t>删除卡牌时游戏力+12</t>
+    <t>直播开始时，红温+4</t>
   </si>
   <si>
     <t>杂谈的心得</t>
   </si>
   <si>
-    <t>删除卡牌时杂谈力+12</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
+    <t>直播开始时，幽默+4</t>
+  </si>
+  <si>
+    <t>唱歌的理论</t>
+  </si>
+  <si>
+    <t>获得卡牌时，歌力+4</t>
+  </si>
+  <si>
+    <t>OnCardAdded</t>
+  </si>
+  <si>
+    <t>游戏的理论</t>
+  </si>
+  <si>
+    <t>获得卡牌时，游戏力+4</t>
+  </si>
+  <si>
+    <t>杂谈的理论</t>
+  </si>
+  <si>
+    <t>获得卡牌时，杂谈力+4</t>
+  </si>
+  <si>
+    <t>饭撒的理论</t>
+  </si>
+  <si>
+    <t>获得卡牌时，粉丝数+25</t>
+  </si>
+  <si>
+    <t>唱歌的理解</t>
+  </si>
+  <si>
+    <t>每使用两张卡，神采+2</t>
+  </si>
+  <si>
+    <t>OnCardUsed</t>
+  </si>
+  <si>
+    <t>游戏的理解</t>
+  </si>
+  <si>
+    <t>每使用两张卡，参数+4</t>
+  </si>
+  <si>
+    <t>杂谈的理解</t>
+  </si>
+  <si>
+    <t>每使用两张卡，红温+3</t>
+  </si>
+  <si>
+    <t>饭撒的理解</t>
+  </si>
+  <si>
+    <t>每使用两张卡，同接+20</t>
+  </si>
+  <si>
+    <t>爱墨生的投稿</t>
+  </si>
+  <si>
+    <t>每当获得粉丝时，歌力+5</t>
+  </si>
+  <si>
+    <t>OnFollowerCountChanged</t>
+  </si>
+  <si>
+    <t>爱墨生的祝福</t>
+  </si>
+  <si>
+    <t>每当获得舰长时，游戏力+5</t>
+  </si>
+  <si>
+    <t>OnMemberCountChanged</t>
+  </si>
+  <si>
+    <t>爱墨生的礼物</t>
+  </si>
+  <si>
+    <t>每当消耗沪币时，杂谈力+5</t>
+  </si>
+  <si>
+    <t>OnMoneyChanged</t>
+  </si>
+  <si>
+    <t>爱墨生的精气</t>
+  </si>
+  <si>
+    <t>每当体力减少时，体力+1</t>
+  </si>
+  <si>
+    <t>OnStaminaChanged</t>
+  </si>
+  <si>
+    <t>润喉糖</t>
+  </si>
+  <si>
+    <t>当处于唱歌回合时，参数获得量+50%，直播中触发3次</t>
+  </si>
+  <si>
+    <t>人体工学椅</t>
+  </si>
+  <si>
+    <t>当处于游戏回合时，参数获得量+50%，直播中触发3次</t>
+  </si>
+  <si>
+    <t>一只猫</t>
+  </si>
+  <si>
+    <t>当处于杂谈回合时，参数获得量+50%，直播中触发3次</t>
+  </si>
+  <si>
+    <t>百舰徽章-音乐区</t>
+  </si>
+  <si>
+    <t>每周结束时，获得舰长数50%的歌力</t>
+  </si>
+  <si>
+    <t>百舰徽章-游戏区</t>
+  </si>
+  <si>
+    <t>每周结束时，获得舰长数50%的游戏力</t>
+  </si>
+  <si>
+    <t>百舰徽章-电台区</t>
+  </si>
+  <si>
+    <t>每周结束时，获得舰长数50%的杂谈力</t>
+  </si>
+  <si>
+    <t>粉丝勋章-音乐区</t>
+  </si>
+  <si>
+    <t>每阶段结束时，获得粉丝数1%的歌力</t>
+  </si>
+  <si>
+    <t>粉丝勋章-游戏区</t>
+  </si>
+  <si>
+    <t>每阶段结束时，获得粉丝数1%的游戏力</t>
+  </si>
+  <si>
+    <t>粉丝勋章-电台区</t>
+  </si>
+  <si>
+    <t>每阶段结束时，获得粉丝数1%的杂谈力</t>
+  </si>
+  <si>
+    <t>歌势的领悟</t>
+  </si>
+  <si>
+    <t>当歌力大于1500时，在唱歌直播结束时，歌力+15</t>
+  </si>
+  <si>
+    <t>游戏势的领悟</t>
+  </si>
+  <si>
+    <t>当游戏力大于1500时，在游戏直播结束时，游戏力+15</t>
+  </si>
+  <si>
+    <t>杂谈势的领悟</t>
+  </si>
+  <si>
+    <t>当杂谈力大于1500时，在杂谈直播结束时，杂谈力+15</t>
   </si>
   <si>
     <t>LiveType</t>
@@ -275,6 +487,9 @@
     <t>Common</t>
   </si>
   <si>
+    <t>drink1</t>
+  </si>
+  <si>
     <t>千事可乐</t>
   </si>
   <si>
@@ -284,18 +499,27 @@
     <t>C</t>
   </si>
   <si>
+    <t>drink2</t>
+  </si>
+  <si>
     <t>口口可乐</t>
   </si>
   <si>
     <t>幽默+3</t>
   </si>
   <si>
+    <t>drink3</t>
+  </si>
+  <si>
     <t>橙汁</t>
   </si>
   <si>
     <t>参数+9</t>
   </si>
   <si>
+    <t>drink4</t>
+  </si>
+  <si>
     <t>马卡龙</t>
   </si>
   <si>
@@ -306,6 +530,9 @@
   </si>
   <si>
     <t>Rare</t>
+  </si>
+  <si>
+    <t>drink5</t>
   </si>
   <si>
     <t>汉堡</t>
@@ -316,6 +543,9 @@
 体力消耗2</t>
   </si>
   <si>
+    <t>drink</t>
+  </si>
+  <si>
     <t>蓝莓汁</t>
   </si>
   <si>
@@ -323,6 +553,9 @@
 重抽手牌</t>
   </si>
   <si>
+    <t>drink6</t>
+  </si>
+  <si>
     <t>冰淇淋</t>
   </si>
   <si>
@@ -330,6 +563,9 @@
 之后5回合开始时，抽一张牌</t>
   </si>
   <si>
+    <t>drink7</t>
+  </si>
+  <si>
     <t>神秘饮品</t>
   </si>
   <si>
@@ -339,46 +575,394 @@
     <t>Epic</t>
   </si>
   <si>
+    <t>drink8</t>
+  </si>
+  <si>
     <t>火锅汤</t>
   </si>
   <si>
     <t>红温变为1.5倍，体力-2</t>
   </si>
   <si>
+    <t>drink9</t>
+  </si>
+  <si>
     <t>菠萝披萨</t>
   </si>
   <si>
     <t>回合结束时，幽默+1</t>
   </si>
   <si>
+    <t>drink10</t>
+  </si>
+  <si>
     <t>魔爪</t>
   </si>
   <si>
     <t>卡牌使用次数+1</t>
+  </si>
+  <si>
+    <t>drink11</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -395,9 +979,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -407,17 +1233,61 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -675,22 +1545,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="3.1796875" customWidth="1"/>
-    <col min="2" max="2" width="11.7265625" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
-    <col min="4" max="4" width="28.7265625" customWidth="1"/>
-    <col min="5" max="5" width="14.7265625" customWidth="1"/>
-    <col min="6" max="6" width="13.453125" customWidth="1"/>
-    <col min="7" max="7" width="10.453125" customWidth="1"/>
+    <col min="1" max="1" width="3.18333333333333" customWidth="1"/>
+    <col min="2" max="2" width="11.725" customWidth="1"/>
+    <col min="3" max="3" width="15.45" customWidth="1"/>
+    <col min="4" max="4" width="28.725" customWidth="1"/>
+    <col min="5" max="5" width="14.725" customWidth="1"/>
+    <col min="6" max="6" width="13.45" customWidth="1"/>
+    <col min="7" max="7" width="10.45" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -876,35 +1746,138 @@
         <v>1</v>
       </c>
     </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13"/>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:R43"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="13.54296875" customWidth="1"/>
-    <col min="3" max="3" width="25.453125" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" customWidth="1"/>
-    <col min="5" max="5" width="5.453125" customWidth="1"/>
-    <col min="6" max="6" width="20.1796875" customWidth="1"/>
-    <col min="7" max="7" width="3.81640625" customWidth="1"/>
-    <col min="8" max="8" width="7.453125" customWidth="1"/>
-    <col min="9" max="9" width="10.26953125" customWidth="1"/>
-    <col min="10" max="10" width="13.1796875" customWidth="1"/>
-    <col min="11" max="11" width="17.1796875" customWidth="1"/>
-    <col min="12" max="12" width="14.1796875" customWidth="1"/>
-    <col min="13" max="13" width="12.453125" customWidth="1"/>
+    <col min="1" max="1" width="3.41666666666667" customWidth="1"/>
+    <col min="2" max="2" width="13.5416666666667" customWidth="1"/>
+    <col min="3" max="3" width="25.45" customWidth="1"/>
+    <col min="4" max="4" width="12.1833333333333" customWidth="1"/>
+    <col min="5" max="5" width="5.45" customWidth="1"/>
+    <col min="6" max="6" width="20.1833333333333" customWidth="1"/>
+    <col min="7" max="7" width="3.81666666666667" customWidth="1"/>
+    <col min="8" max="8" width="7.45" customWidth="1"/>
+    <col min="9" max="9" width="10.2666666666667" customWidth="1"/>
+    <col min="10" max="10" width="13.1833333333333" customWidth="1"/>
+    <col min="11" max="11" width="17.1833333333333" customWidth="1"/>
+    <col min="12" max="12" width="14.1833333333333" customWidth="1"/>
+    <col min="13" max="13" width="12.45" customWidth="1"/>
     <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="11.81640625" customWidth="1"/>
-    <col min="16" max="16" width="11.54296875" customWidth="1"/>
-    <col min="17" max="17" width="17.1796875" customWidth="1"/>
+    <col min="15" max="15" width="11.8166666666667" customWidth="1"/>
+    <col min="16" max="16" width="11.5416666666667" customWidth="1"/>
+    <col min="17" max="17" width="17.1833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="29">
+    <row r="1" ht="28" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -918,66 +1891,66 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="J1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="K1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="M1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="P1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E2">
         <v>-1</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -992,24 +1965,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E3">
         <v>-1</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -1024,24 +1997,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E4">
         <v>-1</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -1056,24 +2029,24 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E5">
         <v>-1</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -1088,24 +2061,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E6">
         <v>-1</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -1120,24 +2093,24 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E7">
         <v>-1</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1152,24 +2125,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" t="s">
         <v>50</v>
-      </c>
-      <c r="C8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" t="s">
-        <v>38</v>
       </c>
       <c r="E8">
         <v>-1</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H8">
         <v>7</v>
@@ -1184,24 +2157,24 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E9">
         <v>-1</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H9">
         <v>4</v>
@@ -1216,24 +2189,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E10">
         <v>-1</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H10">
         <v>3</v>
@@ -1248,24 +2221,24 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E11">
         <v>-1</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -1280,24 +2253,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E12">
         <v>-1</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="I12">
         <v>45</v>
@@ -1309,24 +2282,24 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="I13">
         <v>2</v>
@@ -1338,107 +2311,722 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E14">
         <v>-1</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="I14">
         <v>28</v>
       </c>
       <c r="J14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E15">
         <v>-1</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="I15">
         <v>29</v>
       </c>
       <c r="J15">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E16">
         <v>-1</v>
       </c>
       <c r="F16" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="I16">
         <v>30</v>
       </c>
       <c r="J16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17">
+        <v>-1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>86</v>
+      </c>
+      <c r="I17">
+        <v>2</v>
+      </c>
+      <c r="J17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18">
+        <v>-1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>86</v>
+      </c>
+      <c r="I18">
+        <v>15</v>
+      </c>
+      <c r="J18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19">
+        <v>-1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>86</v>
+      </c>
+      <c r="I19">
+        <v>45</v>
+      </c>
+      <c r="J19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20">
+        <v>-1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20">
+        <v>28</v>
+      </c>
+      <c r="J20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21">
+        <v>-1</v>
+      </c>
+      <c r="F21" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21">
+        <v>29</v>
+      </c>
+      <c r="J21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22">
+        <v>-1</v>
+      </c>
+      <c r="F22" t="s">
+        <v>93</v>
+      </c>
+      <c r="I22">
+        <v>30</v>
+      </c>
+      <c r="J22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23">
+        <v>-1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>93</v>
+      </c>
+      <c r="I23">
+        <v>15</v>
+      </c>
+      <c r="J23">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24" t="s">
+        <v>102</v>
+      </c>
+      <c r="H24">
+        <v>11</v>
+      </c>
+      <c r="I24">
+        <v>2</v>
+      </c>
+      <c r="J24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25" t="s">
+        <v>102</v>
+      </c>
+      <c r="H25">
+        <v>11</v>
+      </c>
+      <c r="I25">
+        <v>11</v>
+      </c>
+      <c r="J25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26">
+        <v>3</v>
+      </c>
+      <c r="F26" t="s">
+        <v>102</v>
+      </c>
+      <c r="H26">
+        <v>11</v>
+      </c>
+      <c r="I26">
+        <v>15</v>
+      </c>
+      <c r="J26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27">
+        <v>3</v>
+      </c>
+      <c r="F27" t="s">
+        <v>102</v>
+      </c>
+      <c r="H27">
+        <v>11</v>
+      </c>
+      <c r="I27">
+        <v>33</v>
+      </c>
+      <c r="J27">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28">
+        <v>-1</v>
+      </c>
+      <c r="F28" t="s">
+        <v>111</v>
+      </c>
+      <c r="H28">
+        <v>13</v>
+      </c>
+      <c r="I28">
+        <v>28</v>
+      </c>
+      <c r="J28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29">
+        <v>-1</v>
+      </c>
+      <c r="F29" t="s">
+        <v>114</v>
+      </c>
+      <c r="H29">
+        <v>13</v>
+      </c>
+      <c r="I29">
+        <v>29</v>
+      </c>
+      <c r="J29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>115</v>
+      </c>
+      <c r="C30" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30">
+        <v>-1</v>
+      </c>
+      <c r="F30" t="s">
+        <v>117</v>
+      </c>
+      <c r="H30">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="3:3">
-      <c r="C19" t="s">
-        <v>72</v>
+      <c r="I30">
+        <v>30</v>
+      </c>
+      <c r="J30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31">
+        <v>-1</v>
+      </c>
+      <c r="F31" t="s">
+        <v>120</v>
+      </c>
+      <c r="H31">
+        <v>12</v>
+      </c>
+      <c r="I31">
+        <v>3</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>121</v>
+      </c>
+      <c r="C32" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" t="s">
+        <v>75</v>
+      </c>
+      <c r="E32">
+        <v>3</v>
+      </c>
+      <c r="F32" t="s">
+        <v>76</v>
+      </c>
+      <c r="H32">
+        <v>10</v>
+      </c>
+      <c r="I32">
+        <v>75</v>
+      </c>
+      <c r="J32">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33" t="s">
+        <v>75</v>
+      </c>
+      <c r="E33">
+        <v>3</v>
+      </c>
+      <c r="F33" t="s">
+        <v>76</v>
+      </c>
+      <c r="H33">
+        <v>11</v>
+      </c>
+      <c r="I33">
+        <v>75</v>
+      </c>
+      <c r="J33">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>125</v>
+      </c>
+      <c r="C34" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E34">
+        <v>3</v>
+      </c>
+      <c r="F34" t="s">
+        <v>76</v>
+      </c>
+      <c r="H34">
+        <v>12</v>
+      </c>
+      <c r="I34">
+        <v>75</v>
+      </c>
+      <c r="J34">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>127</v>
+      </c>
+      <c r="C35" t="s">
+        <v>128</v>
+      </c>
+      <c r="D35" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>131</v>
+      </c>
+      <c r="C37" t="s">
+        <v>132</v>
+      </c>
+      <c r="D37" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
+        <v>133</v>
+      </c>
+      <c r="C38" t="s">
+        <v>134</v>
+      </c>
+      <c r="D38" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>135</v>
+      </c>
+      <c r="C39" t="s">
+        <v>136</v>
+      </c>
+      <c r="D39" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>137</v>
+      </c>
+      <c r="C40" t="s">
+        <v>138</v>
+      </c>
+      <c r="D40" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>139</v>
+      </c>
+      <c r="C41" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s">
+        <v>141</v>
+      </c>
+      <c r="C42" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>143</v>
+      </c>
+      <c r="C43" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:M14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="14"/>
   <cols>
-    <col min="3" max="3" width="23.54296875" customWidth="1"/>
-    <col min="4" max="7" width="18.1796875" customWidth="1"/>
-    <col min="8" max="8" width="10.54296875" customWidth="1"/>
+    <col min="3" max="3" width="23.5416666666667" customWidth="1"/>
+    <col min="4" max="7" width="18.1833333333333" customWidth="1"/>
+    <col min="8" max="8" width="10.5416666666667" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="12.81640625" customWidth="1"/>
+    <col min="10" max="10" width="12.8166666666667" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="11.26953125" customWidth="1"/>
-    <col min="13" max="13" width="10.7265625" customWidth="1"/>
+    <col min="12" max="12" width="11.2666666666667" customWidth="1"/>
+    <col min="13" max="13" width="10.725" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -1455,51 +3043,54 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="F1" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="G1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="I1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="M1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>148</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="E2" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="F2" t="s">
-        <v>79</v>
+        <v>151</v>
+      </c>
+      <c r="G2" t="s">
+        <v>152</v>
       </c>
       <c r="H2">
         <v>3</v>
@@ -1508,24 +3099,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="E3" t="s">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="F3" t="s">
-        <v>79</v>
+        <v>151</v>
+      </c>
+      <c r="G3" t="s">
+        <v>156</v>
       </c>
       <c r="H3">
         <v>15</v>
@@ -1534,24 +3128,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>158</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="E4" t="s">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="F4" t="s">
-        <v>79</v>
+        <v>151</v>
+      </c>
+      <c r="G4" t="s">
+        <v>159</v>
       </c>
       <c r="H4">
         <v>45</v>
@@ -1560,24 +3157,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>161</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="F5" t="s">
-        <v>79</v>
+        <v>151</v>
+      </c>
+      <c r="G5" t="s">
+        <v>162</v>
       </c>
       <c r="H5">
         <v>11</v>
@@ -1586,26 +3186,28 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>163</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>165</v>
       </c>
       <c r="E6" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" s="3"/>
+        <v>166</v>
+      </c>
+      <c r="G6" t="s">
+        <v>167</v>
+      </c>
       <c r="H6">
         <v>38</v>
       </c>
@@ -1613,26 +3215,28 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="43.5">
+    <row r="7" ht="42" spans="1:13">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>168</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>92</v>
+        <v>169</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="E7" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G7" s="3"/>
+        <v>166</v>
+      </c>
+      <c r="G7" t="s">
+        <v>170</v>
+      </c>
       <c r="H7">
         <v>13</v>
       </c>
@@ -1652,26 +3256,28 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="29">
+    <row r="8" ht="28" spans="1:10">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>94</v>
+        <v>172</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" s="3"/>
+        <v>166</v>
+      </c>
+      <c r="G8" t="s">
+        <v>173</v>
+      </c>
       <c r="H8">
         <v>38</v>
       </c>
@@ -1682,26 +3288,28 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="43.5">
+    <row r="9" ht="42" spans="1:11">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>174</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>96</v>
+        <v>175</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="E9" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G9" s="3"/>
+        <v>166</v>
+      </c>
+      <c r="G9" t="s">
+        <v>176</v>
+      </c>
       <c r="H9">
         <v>9</v>
       </c>
@@ -1715,26 +3323,28 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>178</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="E10" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G10" s="3"/>
+        <v>179</v>
+      </c>
+      <c r="G10" t="s">
+        <v>180</v>
+      </c>
       <c r="H10">
         <v>0</v>
       </c>
@@ -1745,26 +3355,28 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>100</v>
+        <v>181</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>182</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="E11" t="s">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G11" s="3"/>
+        <v>179</v>
+      </c>
+      <c r="G11" t="s">
+        <v>183</v>
+      </c>
       <c r="H11">
         <v>63</v>
       </c>
@@ -1778,26 +3390,28 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>184</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>185</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="E12" t="s">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G12" s="3"/>
+        <v>179</v>
+      </c>
+      <c r="G12" t="s">
+        <v>186</v>
+      </c>
       <c r="H12">
         <v>65</v>
       </c>
@@ -1805,26 +3419,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>187</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>188</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G13" s="3"/>
+        <v>179</v>
+      </c>
+      <c r="G13" t="s">
+        <v>189</v>
+      </c>
       <c r="H13">
         <v>14</v>
       </c>
@@ -1832,11 +3448,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="6:7">
       <c r="F14" s="1"/>
       <c r="G14" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="201">
   <si>
     <t>ID</t>
   </si>
@@ -352,118 +352,151 @@
     <t>每使用两张卡，红温+3</t>
   </si>
   <si>
-    <t>饭撒的理解</t>
-  </si>
-  <si>
-    <t>每使用两张卡，同接+20</t>
+    <t>饭撒的精通</t>
+  </si>
+  <si>
+    <t>每使用两张卡，获得</t>
   </si>
   <si>
     <t>爱墨生的投稿</t>
   </si>
   <si>
-    <t>每当获得粉丝时，歌力+5</t>
-  </si>
-  <si>
-    <t>OnFollowerCountChanged</t>
+    <t>每当获得消耗品时，歌力+5</t>
+  </si>
+  <si>
+    <t>OnAddConsumable</t>
   </si>
   <si>
     <t>爱墨生的祝福</t>
   </si>
   <si>
-    <t>每当获得舰长时，游戏力+5</t>
-  </si>
-  <si>
-    <t>OnMemberCountChanged</t>
+    <t>每当获得消耗品时，游戏力+5</t>
   </si>
   <si>
     <t>爱墨生的礼物</t>
   </si>
   <si>
+    <t>每当获得消耗品时，杂谈力+5</t>
+  </si>
+  <si>
+    <t>爱墨生的精气</t>
+  </si>
+  <si>
+    <t>每当体力减少时，体力+1</t>
+  </si>
+  <si>
+    <t>OnStaminaChanged</t>
+  </si>
+  <si>
+    <t>唱歌的精通</t>
+  </si>
+  <si>
+    <t>当处于唱歌回合时，参数获得量+50%，直播中触发3次</t>
+  </si>
+  <si>
+    <t>游戏的精通</t>
+  </si>
+  <si>
+    <t>当处于游戏回合时，参数获得量+50%，直播中触发3次</t>
+  </si>
+  <si>
+    <t>杂谈的精通</t>
+  </si>
+  <si>
+    <t>当处于杂谈回合时，参数获得量+50%，直播中触发3次</t>
+  </si>
+  <si>
+    <t>百舰徽章-音乐区</t>
+  </si>
+  <si>
+    <t>每周结束时，获得舰长数50%的歌力</t>
+  </si>
+  <si>
+    <t>OnWeekEnd</t>
+  </si>
+  <si>
+    <t>百舰徽章-游戏区</t>
+  </si>
+  <si>
+    <t>每周结束时，获得舰长数50%的游戏力</t>
+  </si>
+  <si>
+    <t>百舰徽章-电台区</t>
+  </si>
+  <si>
+    <t>每周结束时，获得舰长数50%的杂谈力</t>
+  </si>
+  <si>
+    <t>粉丝徽章-音乐区</t>
+  </si>
+  <si>
+    <t>每阶段结束时，获得粉丝数1%的歌力</t>
+  </si>
+  <si>
+    <t>OnPhaseEndingSelected</t>
+  </si>
+  <si>
+    <t>粉丝徽章-游戏区</t>
+  </si>
+  <si>
+    <t>每阶段结束时，获得粉丝数1%的游戏力</t>
+  </si>
+  <si>
+    <t>粉丝徽章-电台区</t>
+  </si>
+  <si>
+    <t>每阶段结束时，获得粉丝数1%的杂谈力</t>
+  </si>
+  <si>
+    <t>收益徽章-音乐区</t>
+  </si>
+  <si>
+    <t>每当消耗沪币时，歌力+5</t>
+  </si>
+  <si>
+    <t>OnMoneyChanged</t>
+  </si>
+  <si>
+    <t>收益徽章-游戏区</t>
+  </si>
+  <si>
+    <t>每当消耗沪币时，游戏力+5</t>
+  </si>
+  <si>
+    <t>收益徽章-电台区</t>
+  </si>
+  <si>
     <t>每当消耗沪币时，杂谈力+5</t>
   </si>
   <si>
-    <t>OnMoneyChanged</t>
-  </si>
-  <si>
-    <t>爱墨生的精气</t>
-  </si>
-  <si>
-    <t>每当体力减少时，体力+1</t>
-  </si>
-  <si>
-    <t>OnStaminaChanged</t>
-  </si>
-  <si>
-    <t>润喉糖</t>
-  </si>
-  <si>
-    <t>当处于唱歌回合时，参数获得量+50%，直播中触发3次</t>
-  </si>
-  <si>
-    <t>人体工学椅</t>
-  </si>
-  <si>
-    <t>当处于游戏回合时，参数获得量+50%，直播中触发3次</t>
-  </si>
-  <si>
-    <t>一只猫</t>
-  </si>
-  <si>
-    <t>当处于杂谈回合时，参数获得量+50%，直播中触发3次</t>
-  </si>
-  <si>
-    <t>百舰徽章-音乐区</t>
-  </si>
-  <si>
-    <t>每周结束时，获得舰长数50%的歌力</t>
-  </si>
-  <si>
-    <t>百舰徽章-游戏区</t>
-  </si>
-  <si>
-    <t>每周结束时，获得舰长数50%的游戏力</t>
-  </si>
-  <si>
-    <t>百舰徽章-电台区</t>
-  </si>
-  <si>
-    <t>每周结束时，获得舰长数50%的杂谈力</t>
-  </si>
-  <si>
-    <t>粉丝勋章-音乐区</t>
-  </si>
-  <si>
-    <t>每阶段结束时，获得粉丝数1%的歌力</t>
-  </si>
-  <si>
-    <t>粉丝勋章-游戏区</t>
-  </si>
-  <si>
-    <t>每阶段结束时，获得粉丝数1%的游戏力</t>
-  </si>
-  <si>
-    <t>粉丝勋章-电台区</t>
-  </si>
-  <si>
-    <t>每阶段结束时，获得粉丝数1%的杂谈力</t>
-  </si>
-  <si>
     <t>歌势的领悟</t>
   </si>
   <si>
-    <t>当歌力大于1500时，在唱歌直播结束时，歌力+15</t>
+    <t>每当升级卡牌时，歌力+5</t>
+  </si>
+  <si>
+    <t>OnCardUpgraded</t>
   </si>
   <si>
     <t>游戏势的领悟</t>
   </si>
   <si>
-    <t>当游戏力大于1500时，在游戏直播结束时，游戏力+15</t>
+    <t>每当升级卡牌时，游戏力+5</t>
   </si>
   <si>
     <t>杂谈势的领悟</t>
   </si>
   <si>
-    <t>当杂谈力大于1500时，在杂谈直播结束时，杂谈力+15</t>
+    <t>每当升级卡牌时，杂谈力+5</t>
+  </si>
+  <si>
+    <t>社交的领悟</t>
+  </si>
+  <si>
+    <t>和协助者关系升级时，粉丝+500，舰长+1</t>
+  </si>
+  <si>
+    <t>OnSetCoopUpgradeEvent</t>
   </si>
   <si>
     <t>LiveType</t>
@@ -1801,7 +1834,6 @@
       <c r="E13" t="s">
         <v>9</v>
       </c>
-      <c r="F13"/>
       <c r="G13">
         <v>2</v>
       </c>
@@ -1855,7 +1887,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R43"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.41666666666667" customWidth="1"/>
@@ -2733,7 +2765,7 @@
         <v>-1</v>
       </c>
       <c r="F29" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H29">
         <v>13</v>
@@ -2750,10 +2782,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" t="s">
         <v>115</v>
-      </c>
-      <c r="C30" t="s">
-        <v>116</v>
       </c>
       <c r="D30" t="s">
         <v>50</v>
@@ -2762,7 +2794,7 @@
         <v>-1</v>
       </c>
       <c r="F30" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="H30">
         <v>12</v>
@@ -2779,10 +2811,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D31" t="s">
         <v>50</v>
@@ -2791,7 +2823,7 @@
         <v>-1</v>
       </c>
       <c r="F31" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H31">
         <v>12</v>
@@ -2808,10 +2840,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s">
         <v>75</v>
@@ -2837,10 +2869,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D33" t="s">
         <v>75</v>
@@ -2866,10 +2898,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D34" t="s">
         <v>75</v>
@@ -2890,63 +2922,111 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:10">
       <c r="A35">
         <v>33</v>
       </c>
       <c r="B35" t="s">
+        <v>125</v>
+      </c>
+      <c r="C35" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35">
+        <v>-1</v>
+      </c>
+      <c r="F35" t="s">
         <v>127</v>
       </c>
-      <c r="C35" t="s">
-        <v>128</v>
-      </c>
-      <c r="D35" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="I35">
+        <v>57</v>
+      </c>
+      <c r="J35">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36" t="s">
+        <v>128</v>
+      </c>
+      <c r="C36" t="s">
         <v>129</v>
       </c>
-      <c r="C36" t="s">
-        <v>130</v>
-      </c>
       <c r="D36" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="E36">
+        <v>-1</v>
+      </c>
+      <c r="F36" t="s">
+        <v>127</v>
+      </c>
+      <c r="I36">
+        <v>58</v>
+      </c>
+      <c r="J36">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37" t="s">
+        <v>130</v>
+      </c>
+      <c r="C37" t="s">
         <v>131</v>
       </c>
-      <c r="C37" t="s">
-        <v>132</v>
-      </c>
       <c r="D37" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="E37">
+        <v>-1</v>
+      </c>
+      <c r="F37" t="s">
+        <v>127</v>
+      </c>
+      <c r="I37">
+        <v>59</v>
+      </c>
+      <c r="J37">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" t="s">
+        <v>132</v>
+      </c>
+      <c r="C38" t="s">
         <v>133</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
+        <v>50</v>
+      </c>
+      <c r="E38">
+        <v>-1</v>
+      </c>
+      <c r="F38" t="s">
         <v>134</v>
       </c>
-      <c r="D38" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="I38">
+        <v>60</v>
+      </c>
+      <c r="J38">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39">
         <v>37</v>
       </c>
@@ -2959,8 +3039,20 @@
       <c r="D39" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="40" spans="1:4">
+      <c r="E39">
+        <v>-1</v>
+      </c>
+      <c r="F39" t="s">
+        <v>134</v>
+      </c>
+      <c r="I39">
+        <v>61</v>
+      </c>
+      <c r="J39">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40">
         <v>38</v>
       </c>
@@ -2973,8 +3065,20 @@
       <c r="D40" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
+      <c r="E40">
+        <v>-1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>134</v>
+      </c>
+      <c r="I40">
+        <v>62</v>
+      </c>
+      <c r="J40">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41">
         <v>39</v>
       </c>
@@ -2984,27 +3088,194 @@
       <c r="C41" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="D41" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41">
+        <v>-1</v>
+      </c>
+      <c r="F41" t="s">
+        <v>141</v>
+      </c>
+      <c r="H41">
+        <v>12</v>
+      </c>
+      <c r="I41">
+        <v>28</v>
+      </c>
+      <c r="J41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42">
         <v>40</v>
       </c>
       <c r="B42" t="s">
+        <v>142</v>
+      </c>
+      <c r="C42" t="s">
+        <v>143</v>
+      </c>
+      <c r="D42" t="s">
+        <v>50</v>
+      </c>
+      <c r="E42">
+        <v>-1</v>
+      </c>
+      <c r="F42" t="s">
         <v>141</v>
       </c>
-      <c r="C42" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
+      <c r="H42">
+        <v>12</v>
+      </c>
+      <c r="I42">
+        <v>29</v>
+      </c>
+      <c r="J42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43">
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C43" t="s">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="D43" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43">
+        <v>-1</v>
+      </c>
+      <c r="F43" t="s">
+        <v>141</v>
+      </c>
+      <c r="H43">
+        <v>12</v>
+      </c>
+      <c r="I43">
+        <v>30</v>
+      </c>
+      <c r="J43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>146</v>
+      </c>
+      <c r="C44" t="s">
+        <v>147</v>
+      </c>
+      <c r="D44" t="s">
+        <v>50</v>
+      </c>
+      <c r="E44">
+        <v>-1</v>
+      </c>
+      <c r="F44" t="s">
+        <v>148</v>
+      </c>
+      <c r="I44">
+        <v>28</v>
+      </c>
+      <c r="J44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>149</v>
+      </c>
+      <c r="C45" t="s">
+        <v>150</v>
+      </c>
+      <c r="D45" t="s">
+        <v>50</v>
+      </c>
+      <c r="E45">
+        <v>-1</v>
+      </c>
+      <c r="F45" t="s">
+        <v>148</v>
+      </c>
+      <c r="I45">
+        <v>29</v>
+      </c>
+      <c r="J45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>151</v>
+      </c>
+      <c r="C46" t="s">
+        <v>152</v>
+      </c>
+      <c r="D46" t="s">
+        <v>50</v>
+      </c>
+      <c r="E46">
+        <v>-1</v>
+      </c>
+      <c r="F46" t="s">
+        <v>148</v>
+      </c>
+      <c r="I46">
+        <v>30</v>
+      </c>
+      <c r="J46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>153</v>
+      </c>
+      <c r="C47" t="s">
+        <v>154</v>
+      </c>
+      <c r="D47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E47">
+        <v>-1</v>
+      </c>
+      <c r="F47" t="s">
+        <v>155</v>
+      </c>
+      <c r="I47">
+        <v>15</v>
+      </c>
+      <c r="J47">
+        <v>500</v>
+      </c>
+      <c r="L47">
+        <v>16</v>
+      </c>
+      <c r="M47">
+        <v>1</v>
+      </c>
+      <c r="N47">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3043,10 +3314,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="G1" t="s">
         <v>47</v>
@@ -3075,22 +3346,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C2" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="F2" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="G2" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="H2">
         <v>3</v>
@@ -3104,22 +3375,22 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C3" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="D3" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E3" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="F3" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="G3" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="H3">
         <v>15</v>
@@ -3133,22 +3404,22 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E4" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="F4" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="G4" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="H4">
         <v>45</v>
@@ -3162,22 +3433,22 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D5" t="s">
         <v>160</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>161</v>
       </c>
-      <c r="D5" t="s">
-        <v>149</v>
-      </c>
-      <c r="E5" t="s">
-        <v>150</v>
-      </c>
       <c r="F5" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="G5" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="H5">
         <v>11</v>
@@ -3191,22 +3462,22 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="C6" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="D6" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="E6" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="G6" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="H6">
         <v>38</v>
@@ -3220,22 +3491,22 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="D7" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E7" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="G7" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="H7">
         <v>13</v>
@@ -3261,22 +3532,22 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E8" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="G8" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="H8">
         <v>38</v>
@@ -3293,22 +3564,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="D9" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E9" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="G9" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="H9">
         <v>9</v>
@@ -3328,22 +3599,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C10" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="D10" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E10" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="G10" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -3360,22 +3631,22 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="C11" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E11" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="G11" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="H11">
         <v>63</v>
@@ -3395,22 +3666,22 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="C12" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E12" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="G12" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="H12">
         <v>65</v>
@@ -3424,22 +3695,22 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="C13" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E13" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="G13" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="H13">
         <v>14</v>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C56DC2-1CD0-409C-B5F4-B29F5063EBDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -20,8 +26,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -29,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="196">
   <si>
     <t>ID</t>
   </si>
@@ -95,24 +99,6 @@
   </si>
   <si>
     <t>游戏练习事件</t>
-  </si>
-  <si>
-    <t>唱歌回合</t>
-  </si>
-  <si>
-    <t>VAttributeTurnGainRateModifierEffect</t>
-  </si>
-  <si>
-    <t>游戏回合</t>
-  </si>
-  <si>
-    <t>杂谈回合</t>
-  </si>
-  <si>
-    <t>每使用两张卡牌时</t>
-  </si>
-  <si>
-    <t>VCardTypeUsedCountCondition</t>
   </si>
   <si>
     <t>属性减少时</t>
@@ -636,366 +622,33 @@
   </si>
   <si>
     <t>drink11</t>
+  </si>
+  <si>
+    <t>占位</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1012,315 +665,28 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1578,25 +944,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.18333333333333" customWidth="1"/>
-    <col min="2" max="2" width="11.725" customWidth="1"/>
-    <col min="3" max="3" width="15.45" customWidth="1"/>
-    <col min="4" max="4" width="28.725" customWidth="1"/>
-    <col min="5" max="5" width="14.725" customWidth="1"/>
-    <col min="6" max="6" width="13.45" customWidth="1"/>
-    <col min="7" max="7" width="10.45" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1619,7 +985,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1639,7 +1005,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1659,7 +1025,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1679,7 +1045,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1699,7 +1065,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1719,7 +1085,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1739,7 +1105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1759,7 +1125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1779,100 +1145,133 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>195</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" t="s">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>195</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11" t="s">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>195</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="F12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>195</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
+      <c r="F13" t="s">
+        <v>0</v>
+      </c>
       <c r="G13">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="H13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F14" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:8">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1880,36 +1279,35 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.41666666666667" customWidth="1"/>
-    <col min="2" max="2" width="13.5416666666667" customWidth="1"/>
-    <col min="3" max="3" width="25.45" customWidth="1"/>
-    <col min="4" max="4" width="12.1833333333333" customWidth="1"/>
-    <col min="5" max="5" width="5.45" customWidth="1"/>
-    <col min="6" max="6" width="20.1833333333333" customWidth="1"/>
-    <col min="7" max="7" width="3.81666666666667" customWidth="1"/>
-    <col min="8" max="8" width="7.45" customWidth="1"/>
-    <col min="9" max="9" width="10.2666666666667" customWidth="1"/>
-    <col min="10" max="10" width="13.1833333333333" customWidth="1"/>
-    <col min="11" max="11" width="17.1833333333333" customWidth="1"/>
-    <col min="12" max="12" width="14.1833333333333" customWidth="1"/>
-    <col min="13" max="13" width="12.45" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="25.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" customWidth="1"/>
+    <col min="7" max="7" width="3.85546875" customWidth="1"/>
+    <col min="8" max="8" width="7.42578125" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="11" max="11" width="17.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
     <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="11.8166666666667" customWidth="1"/>
-    <col min="16" max="16" width="11.5416666666667" customWidth="1"/>
-    <col min="17" max="17" width="17.1833333333333" customWidth="1"/>
+    <col min="15" max="15" width="11.85546875" customWidth="1"/>
+    <col min="16" max="16" width="11.5703125" customWidth="1"/>
+    <col min="17" max="17" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" spans="1:18">
+    <row r="1" spans="1:18" ht="30">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1923,66 +1321,66 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="M1" t="s">
         <v>36</v>
       </c>
-      <c r="H1" t="s">
+      <c r="N1" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J1" t="s">
+      <c r="P1" t="s">
         <v>39</v>
       </c>
-      <c r="K1" t="s">
+      <c r="Q1" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="R1" t="s">
         <v>41</v>
       </c>
-      <c r="M1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N1" t="s">
-        <v>43</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="P1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>46</v>
-      </c>
-      <c r="R1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E2">
         <v>-1</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1997,24 +1395,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E3">
         <v>-1</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -2029,24 +1427,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E4">
         <v>-1</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -2061,24 +1459,24 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E5">
         <v>-1</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -2093,24 +1491,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E6">
         <v>-1</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -2125,24 +1523,24 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E7">
         <v>-1</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -2157,24 +1555,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E8">
         <v>-1</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H8">
         <v>7</v>
@@ -2189,24 +1587,24 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E9">
         <v>-1</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H9">
         <v>4</v>
@@ -2221,24 +1619,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E10">
         <v>-1</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H10">
         <v>3</v>
@@ -2253,24 +1651,24 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E11">
         <v>-1</v>
       </c>
       <c r="F11" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -2285,24 +1683,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E12">
         <v>-1</v>
       </c>
       <c r="F12" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="I12">
         <v>45</v>
@@ -2314,24 +1712,24 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:18">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="I13">
         <v>2</v>
@@ -2343,24 +1741,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:18">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E14">
         <v>-1</v>
       </c>
       <c r="F14" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I14">
         <v>28</v>
@@ -2369,24 +1767,24 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E15">
         <v>-1</v>
       </c>
       <c r="F15" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I15">
         <v>29</v>
@@ -2395,24 +1793,24 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:18">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E16">
         <v>-1</v>
       </c>
       <c r="F16" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I16">
         <v>30</v>
@@ -2426,19 +1824,19 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E17">
         <v>-1</v>
       </c>
       <c r="F17" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I17">
         <v>2</v>
@@ -2452,19 +1850,19 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E18">
         <v>-1</v>
       </c>
       <c r="F18" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I18">
         <v>15</v>
@@ -2478,19 +1876,19 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E19">
         <v>-1</v>
       </c>
       <c r="F19" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I19">
         <v>45</v>
@@ -2504,19 +1902,19 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D20" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E20">
         <v>-1</v>
       </c>
       <c r="F20" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="I20">
         <v>28</v>
@@ -2530,19 +1928,19 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E21">
         <v>-1</v>
       </c>
       <c r="F21" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="I21">
         <v>29</v>
@@ -2556,19 +1954,19 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E22">
         <v>-1</v>
       </c>
       <c r="F22" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="I22">
         <v>30</v>
@@ -2582,19 +1980,19 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E23">
         <v>-1</v>
       </c>
       <c r="F23" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="I23">
         <v>15</v>
@@ -2608,19 +2006,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E24">
         <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="H24">
         <v>11</v>
@@ -2637,19 +2035,19 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D25" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E25">
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="H25">
         <v>11</v>
@@ -2666,19 +2064,19 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="H26">
         <v>11</v>
@@ -2695,19 +2093,19 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D27" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E27">
         <v>3</v>
       </c>
       <c r="F27" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="H27">
         <v>11</v>
@@ -2724,19 +2122,19 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D28" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E28">
         <v>-1</v>
       </c>
       <c r="F28" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H28">
         <v>13</v>
@@ -2753,19 +2151,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C29" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E29">
         <v>-1</v>
       </c>
       <c r="F29" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H29">
         <v>13</v>
@@ -2782,19 +2180,19 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E30">
         <v>-1</v>
       </c>
       <c r="F30" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H30">
         <v>12</v>
@@ -2811,19 +2209,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C31" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E31">
         <v>-1</v>
       </c>
       <c r="F31" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="H31">
         <v>12</v>
@@ -2840,19 +2238,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E32">
         <v>3</v>
       </c>
       <c r="F32" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H32">
         <v>10</v>
@@ -2864,24 +2262,24 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:14">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C33" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D33" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E33">
         <v>3</v>
       </c>
       <c r="F33" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H33">
         <v>11</v>
@@ -2893,24 +2291,24 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:14">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C34" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D34" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E34">
         <v>3</v>
       </c>
       <c r="F34" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H34">
         <v>12</v>
@@ -2922,24 +2320,24 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:14">
       <c r="A35">
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D35" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E35">
         <v>-1</v>
       </c>
       <c r="F35" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="I35">
         <v>57</v>
@@ -2948,24 +2346,24 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:14">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C36" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D36" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E36">
         <v>-1</v>
       </c>
       <c r="F36" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="I36">
         <v>58</v>
@@ -2974,24 +2372,24 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:14">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C37" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D37" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E37">
         <v>-1</v>
       </c>
       <c r="F37" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="I37">
         <v>59</v>
@@ -3000,24 +2398,24 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:14">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C38" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E38">
         <v>-1</v>
       </c>
       <c r="F38" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I38">
         <v>60</v>
@@ -3026,24 +2424,24 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:14">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C39" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D39" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E39">
         <v>-1</v>
       </c>
       <c r="F39" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I39">
         <v>61</v>
@@ -3052,24 +2450,24 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:14">
       <c r="A40">
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E40">
         <v>-1</v>
       </c>
       <c r="F40" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I40">
         <v>62</v>
@@ -3078,24 +2476,24 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:14">
       <c r="A41">
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C41" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E41">
         <v>-1</v>
       </c>
       <c r="F41" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="H41">
         <v>12</v>
@@ -3107,24 +2505,24 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:14">
       <c r="A42">
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C42" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D42" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E42">
         <v>-1</v>
       </c>
       <c r="F42" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="H42">
         <v>12</v>
@@ -3136,24 +2534,24 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:14">
       <c r="A43">
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C43" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D43" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E43">
         <v>-1</v>
       </c>
       <c r="F43" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="H43">
         <v>12</v>
@@ -3165,24 +2563,24 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:14">
       <c r="A44">
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C44" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E44">
         <v>-1</v>
       </c>
       <c r="F44" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I44">
         <v>28</v>
@@ -3191,24 +2589,24 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:14">
       <c r="A45">
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C45" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D45" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E45">
         <v>-1</v>
       </c>
       <c r="F45" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I45">
         <v>29</v>
@@ -3217,24 +2615,24 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:14">
       <c r="A46">
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C46" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D46" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E46">
         <v>-1</v>
       </c>
       <c r="F46" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I46">
         <v>30</v>
@@ -3248,19 +2646,19 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C47" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D47" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E47">
         <v>-1</v>
       </c>
       <c r="F47" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="I47">
         <v>15</v>
@@ -3280,24 +2678,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M14"/>
-  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="23.5416666666667" customWidth="1"/>
-    <col min="4" max="7" width="18.1833333333333" customWidth="1"/>
-    <col min="8" max="8" width="10.5416666666667" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" customWidth="1"/>
+    <col min="4" max="7" width="18.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="12.8166666666667" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="11.2666666666667" customWidth="1"/>
-    <col min="13" max="13" width="10.725" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -3314,54 +2710,54 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>39</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="M1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G2" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="H2">
         <v>3</v>
@@ -3370,27 +2766,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E3" t="s">
         <v>160</v>
       </c>
-      <c r="E3" t="s">
-        <v>166</v>
-      </c>
       <c r="F3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="H3">
         <v>15</v>
@@ -3399,27 +2795,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C4" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E4" t="s">
         <v>160</v>
       </c>
-      <c r="E4" t="s">
-        <v>166</v>
-      </c>
       <c r="F4" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G4" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H4">
         <v>45</v>
@@ -3428,27 +2824,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F5" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H5">
         <v>11</v>
@@ -3457,27 +2853,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D6" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E6" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G6" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="H6">
         <v>38</v>
@@ -3486,27 +2882,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" ht="42" spans="1:13">
+    <row r="7" spans="1:13" ht="60">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D7" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E7" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G7" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="H7">
         <v>13</v>
@@ -3527,27 +2923,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="28" spans="1:10">
+    <row r="8" spans="1:13" ht="30">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D8" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E8" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G8" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="H8">
         <v>38</v>
@@ -3559,27 +2955,27 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" ht="42" spans="1:11">
+    <row r="9" spans="1:13" ht="45">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E9" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G9" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H9">
         <v>9</v>
@@ -3594,27 +2990,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C10" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D10" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E10" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="G10" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -3626,27 +3022,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C11" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D11" t="s">
+        <v>154</v>
+      </c>
+      <c r="E11" t="s">
         <v>160</v>
       </c>
-      <c r="E11" t="s">
-        <v>166</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="G11" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="H11">
         <v>63</v>
@@ -3661,27 +3057,27 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:13">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C12" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D12" t="s">
+        <v>154</v>
+      </c>
+      <c r="E12" t="s">
         <v>160</v>
       </c>
-      <c r="E12" t="s">
-        <v>166</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="G12" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H12">
         <v>65</v>
@@ -3690,27 +3086,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:13">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D13" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E13" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="G13" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="H13">
         <v>14</v>
@@ -3719,12 +3115,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="6:7">
+    <row r="14" spans="1:13">
       <c r="F14" s="1"/>
-      <c r="G14" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
+    <workbookView windowWidth="22190" windowHeight="9040" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="196">
   <si>
     <t>ID</t>
   </si>
@@ -97,22 +97,7 @@
     <t>游戏练习事件</t>
   </si>
   <si>
-    <t>唱歌回合</t>
-  </si>
-  <si>
-    <t>VAttributeTurnGainRateModifierEffect</t>
-  </si>
-  <si>
-    <t>游戏回合</t>
-  </si>
-  <si>
-    <t>杂谈回合</t>
-  </si>
-  <si>
-    <t>每使用两张卡牌时</t>
-  </si>
-  <si>
-    <t>VCardTypeUsedCountCondition</t>
+    <t>空事件</t>
   </si>
   <si>
     <t>属性减少时</t>
@@ -1779,7 +1764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" customFormat="1" spans="1:7">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1787,55 +1772,76 @@
         <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" t="s">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:7">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11" t="s">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:7">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="F12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:7">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
+      <c r="F13" t="s">
+        <v>0</v>
+      </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1843,16 +1849,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F14" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1863,16 +1869,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1923,46 +1929,46 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="K1" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H1" t="s">
+      <c r="M1" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="N1" t="s">
         <v>38</v>
       </c>
-      <c r="J1" t="s">
+      <c r="O1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K1" t="s">
+      <c r="P1" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>41</v>
       </c>
-      <c r="M1" t="s">
+      <c r="R1" t="s">
         <v>42</v>
-      </c>
-      <c r="N1" t="s">
-        <v>43</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="P1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>46</v>
-      </c>
-      <c r="R1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1970,19 +1976,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E2">
         <v>-1</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -2002,19 +2008,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E3">
         <v>-1</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -2034,19 +2040,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E4">
         <v>-1</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -2066,19 +2072,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E5">
         <v>-1</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -2098,19 +2104,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E6">
         <v>-1</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -2130,19 +2136,19 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E7">
         <v>-1</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -2162,19 +2168,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E8">
         <v>-1</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H8">
         <v>7</v>
@@ -2194,19 +2200,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E9">
         <v>-1</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H9">
         <v>4</v>
@@ -2226,19 +2232,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E10">
         <v>-1</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H10">
         <v>3</v>
@@ -2258,19 +2264,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E11">
         <v>-1</v>
       </c>
       <c r="F11" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -2290,19 +2296,19 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E12">
         <v>-1</v>
       </c>
       <c r="F12" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="I12">
         <v>45</v>
@@ -2319,19 +2325,19 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="I13">
         <v>2</v>
@@ -2348,19 +2354,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E14">
         <v>-1</v>
       </c>
       <c r="F14" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="I14">
         <v>28</v>
@@ -2374,19 +2380,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E15">
         <v>-1</v>
       </c>
       <c r="F15" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="I15">
         <v>29</v>
@@ -2400,19 +2406,19 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E16">
         <v>-1</v>
       </c>
       <c r="F16" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="I16">
         <v>30</v>
@@ -2426,19 +2432,19 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E17">
         <v>-1</v>
       </c>
       <c r="F17" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I17">
         <v>2</v>
@@ -2452,19 +2458,19 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E18">
         <v>-1</v>
       </c>
       <c r="F18" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I18">
         <v>15</v>
@@ -2478,19 +2484,19 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E19">
         <v>-1</v>
       </c>
       <c r="F19" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I19">
         <v>45</v>
@@ -2504,19 +2510,19 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E20">
         <v>-1</v>
       </c>
       <c r="F20" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I20">
         <v>28</v>
@@ -2530,19 +2536,19 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E21">
         <v>-1</v>
       </c>
       <c r="F21" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I21">
         <v>29</v>
@@ -2556,19 +2562,19 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E22">
         <v>-1</v>
       </c>
       <c r="F22" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I22">
         <v>30</v>
@@ -2582,19 +2588,19 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E23">
         <v>-1</v>
       </c>
       <c r="F23" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I23">
         <v>15</v>
@@ -2608,22 +2614,22 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E24">
         <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H24">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I24">
         <v>2</v>
@@ -2637,22 +2643,22 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E25">
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H25">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I25">
         <v>11</v>
@@ -2666,22 +2672,22 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D26" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H26">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I26">
         <v>15</v>
@@ -2695,22 +2701,22 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D27" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E27">
         <v>3</v>
       </c>
       <c r="F27" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H27">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I27">
         <v>33</v>
@@ -2724,19 +2730,19 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E28">
         <v>-1</v>
       </c>
       <c r="F28" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H28">
         <v>13</v>
@@ -2753,19 +2759,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C29" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D29" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E29">
         <v>-1</v>
       </c>
       <c r="F29" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H29">
         <v>13</v>
@@ -2782,19 +2788,19 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E30">
         <v>-1</v>
       </c>
       <c r="F30" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H30">
         <v>12</v>
@@ -2811,19 +2817,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E31">
         <v>-1</v>
       </c>
       <c r="F31" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H31">
         <v>12</v>
@@ -2840,19 +2846,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D32" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E32">
         <v>3</v>
       </c>
       <c r="F32" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H32">
         <v>10</v>
@@ -2869,19 +2875,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C33" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D33" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E33">
         <v>3</v>
       </c>
       <c r="F33" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H33">
         <v>11</v>
@@ -2898,19 +2904,19 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C34" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D34" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E34">
         <v>3</v>
       </c>
       <c r="F34" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H34">
         <v>12</v>
@@ -2927,19 +2933,19 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E35">
         <v>-1</v>
       </c>
       <c r="F35" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I35">
         <v>57</v>
@@ -2953,19 +2959,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C36" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D36" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E36">
         <v>-1</v>
       </c>
       <c r="F36" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I36">
         <v>58</v>
@@ -2979,19 +2985,19 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C37" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D37" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E37">
         <v>-1</v>
       </c>
       <c r="F37" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I37">
         <v>59</v>
@@ -3005,19 +3011,19 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C38" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E38">
         <v>-1</v>
       </c>
       <c r="F38" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I38">
         <v>60</v>
@@ -3031,19 +3037,19 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C39" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D39" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E39">
         <v>-1</v>
       </c>
       <c r="F39" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I39">
         <v>61</v>
@@ -3057,19 +3063,19 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E40">
         <v>-1</v>
       </c>
       <c r="F40" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I40">
         <v>62</v>
@@ -3083,19 +3089,19 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C41" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E41">
         <v>-1</v>
       </c>
       <c r="F41" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H41">
         <v>12</v>
@@ -3112,19 +3118,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C42" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D42" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E42">
         <v>-1</v>
       </c>
       <c r="F42" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H42">
         <v>12</v>
@@ -3141,19 +3147,19 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C43" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D43" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E43">
         <v>-1</v>
       </c>
       <c r="F43" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H43">
         <v>12</v>
@@ -3170,19 +3176,19 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C44" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E44">
         <v>-1</v>
       </c>
       <c r="F44" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I44">
         <v>28</v>
@@ -3196,19 +3202,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C45" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D45" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E45">
         <v>-1</v>
       </c>
       <c r="F45" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I45">
         <v>29</v>
@@ -3222,19 +3228,19 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C46" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D46" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E46">
         <v>-1</v>
       </c>
       <c r="F46" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I46">
         <v>30</v>
@@ -3248,19 +3254,19 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C47" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D47" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E47">
         <v>-1</v>
       </c>
       <c r="F47" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="I47">
         <v>15</v>
@@ -3314,31 +3320,31 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="M1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3346,22 +3352,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F2" t="s">
+        <v>157</v>
+      </c>
+      <c r="G2" t="s">
         <v>158</v>
-      </c>
-      <c r="C2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G2" t="s">
-        <v>163</v>
       </c>
       <c r="H2">
         <v>3</v>
@@ -3375,22 +3381,22 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G3" t="s">
         <v>162</v>
-      </c>
-      <c r="G3" t="s">
-        <v>167</v>
       </c>
       <c r="H3">
         <v>15</v>
@@ -3404,22 +3410,22 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F4" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G4" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="H4">
         <v>45</v>
@@ -3433,22 +3439,22 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E5" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G5" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H5">
         <v>11</v>
@@ -3462,22 +3468,22 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D6" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E6" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G6" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H6">
         <v>38</v>
@@ -3491,22 +3497,22 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D7" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E7" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G7" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="H7">
         <v>13</v>
@@ -3532,22 +3538,22 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D8" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G8" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H8">
         <v>38</v>
@@ -3564,22 +3570,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E9" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G9" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H9">
         <v>9</v>
@@ -3599,22 +3605,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C10" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D10" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E10" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G10" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -3631,22 +3637,22 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C11" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E11" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G11" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="H11">
         <v>63</v>
@@ -3666,22 +3672,22 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C12" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D12" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E12" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G12" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="H12">
         <v>65</v>
@@ -3695,22 +3701,22 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C13" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D13" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E13" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G13" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="H13">
         <v>14</v>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22190" windowHeight="9040" activeTab="1"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -214,13 +214,13 @@
     <t>进行休息后，游戏力+4</t>
   </si>
   <si>
-    <t>画师麻麻的画笔</t>
+    <t>糯糯的画笔</t>
   </si>
   <si>
     <t>进行工作后，沪币+40</t>
   </si>
   <si>
-    <t>画师麻麻的画板</t>
+    <t>糯糯的画板</t>
   </si>
   <si>
     <t>进行工作后，舰长+1</t>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -3370,7 +3370,7 @@
         <v>158</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>10</v>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
+    <workbookView windowWidth="21990" windowHeight="8940" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -3373,7 +3373,7 @@
         <v>2</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:9">

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21990" windowHeight="8940" activeTab="2"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -3533,7 +3533,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="28" spans="1:10">
+    <row r="8" ht="28" spans="1:11">
       <c r="A8">
         <v>6</v>
       </c>
@@ -3556,13 +3556,13 @@
         <v>179</v>
       </c>
       <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="J8">
         <v>38</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>3</v>
-      </c>
-      <c r="J8">
-        <v>4</v>
       </c>
     </row>
     <row r="9" ht="42" spans="1:11">

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E5A6B2-A815-4D9F-A547-72FAC12E4D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
+    <workbookView xWindow="11985" yWindow="5430" windowWidth="25575" windowHeight="13665" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -626,361 +632,25 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -997,315 +667,28 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1563,22 +946,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.18333333333333" customWidth="1"/>
-    <col min="2" max="2" width="11.725" customWidth="1"/>
-    <col min="3" max="3" width="15.45" customWidth="1"/>
-    <col min="4" max="4" width="28.725" customWidth="1"/>
-    <col min="5" max="5" width="14.725" customWidth="1"/>
-    <col min="6" max="6" width="13.45" customWidth="1"/>
-    <col min="7" max="7" width="10.45" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1764,7 +1147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" customFormat="1" spans="1:7">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1784,7 +1167,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" customFormat="1" spans="1:7">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1804,7 +1187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="1" spans="1:7">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1824,7 +1207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" customFormat="1" spans="1:7">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1886,36 +1269,34 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.41666666666667" customWidth="1"/>
-    <col min="2" max="2" width="13.5416666666667" customWidth="1"/>
-    <col min="3" max="3" width="25.45" customWidth="1"/>
-    <col min="4" max="4" width="12.1833333333333" customWidth="1"/>
-    <col min="5" max="5" width="5.45" customWidth="1"/>
-    <col min="6" max="6" width="20.1833333333333" customWidth="1"/>
-    <col min="7" max="7" width="3.81666666666667" customWidth="1"/>
-    <col min="8" max="8" width="7.45" customWidth="1"/>
-    <col min="9" max="9" width="10.2666666666667" customWidth="1"/>
-    <col min="10" max="10" width="13.1833333333333" customWidth="1"/>
-    <col min="11" max="11" width="17.1833333333333" customWidth="1"/>
-    <col min="12" max="12" width="14.1833333333333" customWidth="1"/>
-    <col min="13" max="13" width="12.45" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="39.140625" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" customWidth="1"/>
+    <col min="7" max="7" width="3.85546875" customWidth="1"/>
+    <col min="8" max="8" width="7.42578125" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="11" max="11" width="17.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
     <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="11.8166666666667" customWidth="1"/>
-    <col min="16" max="16" width="11.5416666666667" customWidth="1"/>
-    <col min="17" max="17" width="17.1833333333333" customWidth="1"/>
+    <col min="15" max="15" width="11.85546875" customWidth="1"/>
+    <col min="16" max="16" width="11.5703125" customWidth="1"/>
+    <col min="17" max="17" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" spans="1:18">
+    <row r="1" spans="1:18" ht="30">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1971,7 +1352,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2003,7 +1384,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2035,7 +1416,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2067,7 +1448,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2099,7 +1480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2131,7 +1512,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2163,7 +1544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2195,7 +1576,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2227,7 +1608,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2259,7 +1640,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2291,7 +1672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2320,7 +1701,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:18">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2349,7 +1730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:18">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2374,8 +1755,11 @@
       <c r="J14">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="K14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2400,8 +1784,11 @@
       <c r="J15">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="K15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2426,8 +1813,11 @@
       <c r="J16">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="K16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2452,8 +1842,11 @@
       <c r="J17">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="K17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2478,8 +1871,11 @@
       <c r="J18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="K18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2504,8 +1900,11 @@
       <c r="J19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="K19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20">
         <v>18</v>
       </c>
@@ -2530,8 +1929,11 @@
       <c r="J20">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="K20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2556,8 +1958,11 @@
       <c r="J21">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="K21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2582,8 +1987,11 @@
       <c r="J22">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:10">
+      <c r="K22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2608,8 +2016,11 @@
       <c r="J23">
         <v>25</v>
       </c>
-    </row>
-    <row r="24" spans="1:10">
+      <c r="K23">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2637,8 +2048,11 @@
       <c r="J24">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" spans="1:10">
+      <c r="K24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2666,8 +2080,11 @@
       <c r="J25">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="K25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2695,8 +2112,11 @@
       <c r="J26">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:10">
+      <c r="K26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2724,8 +2144,11 @@
       <c r="J27">
         <v>20</v>
       </c>
-    </row>
-    <row r="28" spans="1:10">
+      <c r="K27">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28">
         <v>26</v>
       </c>
@@ -2753,8 +2176,11 @@
       <c r="J28">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:10">
+      <c r="K28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29">
         <v>27</v>
       </c>
@@ -2782,8 +2208,11 @@
       <c r="J29">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:10">
+      <c r="K29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30">
         <v>28</v>
       </c>
@@ -2811,8 +2240,11 @@
       <c r="J30">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:10">
+      <c r="K30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31">
         <v>29</v>
       </c>
@@ -2840,8 +2272,11 @@
       <c r="J31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:10">
+      <c r="K31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32">
         <v>30</v>
       </c>
@@ -2869,8 +2304,11 @@
       <c r="J32">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="33" spans="1:10">
+      <c r="K32">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33">
         <v>31</v>
       </c>
@@ -2898,8 +2336,11 @@
       <c r="J33">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="34" spans="1:10">
+      <c r="K33">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34">
         <v>32</v>
       </c>
@@ -2927,8 +2368,11 @@
       <c r="J34">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="35" spans="1:10">
+      <c r="K34">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35">
         <v>33</v>
       </c>
@@ -2953,8 +2397,11 @@
       <c r="J35">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="36" spans="1:10">
+      <c r="K35">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36">
         <v>34</v>
       </c>
@@ -2979,8 +2426,11 @@
       <c r="J36">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="37" spans="1:10">
+      <c r="K36">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37">
         <v>35</v>
       </c>
@@ -3005,8 +2455,11 @@
       <c r="J37">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="38" spans="1:10">
+      <c r="K37">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38">
         <v>36</v>
       </c>
@@ -3031,8 +2484,11 @@
       <c r="J38">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="39" spans="1:10">
+      <c r="K38">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39">
         <v>37</v>
       </c>
@@ -3057,8 +2513,11 @@
       <c r="J39">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="40" spans="1:10">
+      <c r="K39">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40">
         <v>38</v>
       </c>
@@ -3083,8 +2542,11 @@
       <c r="J40">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="41" spans="1:10">
+      <c r="K40">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41">
         <v>39</v>
       </c>
@@ -3112,8 +2574,11 @@
       <c r="J41">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="1:10">
+      <c r="K41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42">
         <v>40</v>
       </c>
@@ -3141,8 +2606,11 @@
       <c r="J42">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="1:10">
+      <c r="K42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43">
         <v>41</v>
       </c>
@@ -3170,8 +2638,11 @@
       <c r="J43">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="1:10">
+      <c r="K43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44">
         <v>42</v>
       </c>
@@ -3196,8 +2667,11 @@
       <c r="J44">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="1:10">
+      <c r="K44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45">
         <v>43</v>
       </c>
@@ -3222,8 +2696,11 @@
       <c r="J45">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="1:10">
+      <c r="K45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46">
         <v>44</v>
       </c>
@@ -3248,6 +2725,9 @@
       <c r="J46">
         <v>5</v>
       </c>
+      <c r="K46">
+        <v>5</v>
+      </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47">
@@ -3274,6 +2754,9 @@
       <c r="J47">
         <v>500</v>
       </c>
+      <c r="K47">
+        <v>500</v>
+      </c>
       <c r="L47">
         <v>16</v>
       </c>
@@ -3286,24 +2769,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M14"/>
-  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="23.5416666666667" customWidth="1"/>
-    <col min="4" max="7" width="18.1833333333333" customWidth="1"/>
-    <col min="8" max="8" width="10.5416666666667" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" customWidth="1"/>
+    <col min="4" max="7" width="18.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="12.8166666666667" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="11.2666666666667" customWidth="1"/>
-    <col min="13" max="13" width="10.725" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -3347,7 +2828,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>0</v>
       </c>
@@ -3376,7 +2857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3405,7 +2886,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>2</v>
       </c>
@@ -3434,7 +2915,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>3</v>
       </c>
@@ -3463,7 +2944,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>4</v>
       </c>
@@ -3492,7 +2973,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" ht="42" spans="1:13">
+    <row r="7" spans="1:13" ht="60">
       <c r="A7">
         <v>5</v>
       </c>
@@ -3533,7 +3014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="28" spans="1:11">
+    <row r="8" spans="1:13" ht="30">
       <c r="A8">
         <v>6</v>
       </c>
@@ -3565,7 +3046,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="42" spans="1:11">
+    <row r="9" spans="1:13" ht="45">
       <c r="A9">
         <v>7</v>
       </c>
@@ -3600,7 +3081,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>8</v>
       </c>
@@ -3632,7 +3113,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3667,7 +3148,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:13">
       <c r="A12">
         <v>10</v>
       </c>
@@ -3696,7 +3177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:13">
       <c r="A13">
         <v>11</v>
       </c>
@@ -3725,12 +3206,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="6:7">
+    <row r="14" spans="1:13">
       <c r="F14" s="1"/>
-      <c r="G14" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E5A6B2-A815-4D9F-A547-72FAC12E4D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11985" yWindow="5430" windowWidth="25575" windowHeight="13665" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="30720" windowHeight="13380" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -35,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="198">
   <si>
     <t>ID</t>
   </si>
@@ -178,19 +172,22 @@
     <t>OnEventEnd</t>
   </si>
   <si>
+    <t>小室的发圈</t>
+  </si>
+  <si>
     <t>小室的玫瑰</t>
   </si>
   <si>
     <t>在直播结束后，粉丝+50</t>
   </si>
   <si>
-    <t>至尊雨王的狗</t>
+    <t>至尊血王的狗</t>
   </si>
   <si>
     <t>进行杂谈练习后，杂谈力+6</t>
   </si>
   <si>
-    <t>至尊雨王的心脏</t>
+    <t>至尊血王的心脏</t>
   </si>
   <si>
     <t>进行社交后，杂谈力+3</t>
@@ -202,19 +199,22 @@
     <t>进行歌力练习后，歌力+6</t>
   </si>
   <si>
+    <t>井井的话筒</t>
+  </si>
+  <si>
     <t>井井的光环</t>
   </si>
   <si>
     <t>进行外出后，歌力+4</t>
   </si>
   <si>
-    <t>柚子的手柄</t>
+    <t>柚茶的手柄</t>
   </si>
   <si>
     <t>进行游戏练习后，游戏力+6</t>
   </si>
   <si>
-    <t>柚子的枕头</t>
+    <t>柚茶的枕头</t>
   </si>
   <si>
     <t>进行休息后，游戏力+4</t>
@@ -632,25 +632,361 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -667,9 +1003,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -678,17 +1256,61 @@
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -946,22 +1568,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="3.140625" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="3.13888888888889" customWidth="1"/>
+    <col min="2" max="2" width="11.712962962963" customWidth="1"/>
+    <col min="3" max="3" width="15.4259259259259" customWidth="1"/>
+    <col min="4" max="4" width="28.712962962963" customWidth="1"/>
+    <col min="5" max="5" width="14.712962962963" customWidth="1"/>
+    <col min="6" max="6" width="13.4259259259259" customWidth="1"/>
+    <col min="7" max="7" width="10.4259259259259" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1269,34 +1891,36 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:R47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" customWidth="1"/>
-    <col min="3" max="3" width="39.140625" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" customWidth="1"/>
-    <col min="5" max="5" width="5.42578125" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" customWidth="1"/>
-    <col min="7" max="7" width="3.85546875" customWidth="1"/>
-    <col min="8" max="8" width="7.42578125" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" customWidth="1"/>
-    <col min="11" max="11" width="17.140625" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="1" max="1" width="3.42592592592593" customWidth="1"/>
+    <col min="2" max="2" width="13.5740740740741" customWidth="1"/>
+    <col min="3" max="3" width="39.1388888888889" customWidth="1"/>
+    <col min="4" max="4" width="12.1388888888889" customWidth="1"/>
+    <col min="5" max="5" width="5.42592592592593" customWidth="1"/>
+    <col min="6" max="6" width="20.1388888888889" customWidth="1"/>
+    <col min="7" max="7" width="3.85185185185185" customWidth="1"/>
+    <col min="8" max="8" width="7.42592592592593" customWidth="1"/>
+    <col min="9" max="9" width="10.287037037037" customWidth="1"/>
+    <col min="10" max="10" width="13.1388888888889" customWidth="1"/>
+    <col min="11" max="11" width="17.1388888888889" customWidth="1"/>
+    <col min="12" max="12" width="14.1388888888889" customWidth="1"/>
+    <col min="13" max="13" width="12.4259259259259" customWidth="1"/>
     <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="11.85546875" customWidth="1"/>
-    <col min="16" max="16" width="11.5703125" customWidth="1"/>
-    <col min="17" max="17" width="17.140625" customWidth="1"/>
+    <col min="15" max="15" width="11.8518518518519" customWidth="1"/>
+    <col min="16" max="16" width="11.5740740740741" customWidth="1"/>
+    <col min="17" max="17" width="17.1388888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="30">
+    <row r="1" ht="27.6" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1352,7 +1976,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1371,6 +1995,9 @@
       <c r="F2" t="s">
         <v>46</v>
       </c>
+      <c r="G2" t="s">
+        <v>47</v>
+      </c>
       <c r="H2">
         <v>0</v>
       </c>
@@ -1384,15 +2011,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
         <v>45</v>
@@ -1403,6 +2030,9 @@
       <c r="F3" t="s">
         <v>46</v>
       </c>
+      <c r="G3" t="s">
+        <v>48</v>
+      </c>
       <c r="H3">
         <v>1</v>
       </c>
@@ -1416,15 +2046,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
         <v>45</v>
@@ -1435,6 +2065,9 @@
       <c r="F4" t="s">
         <v>46</v>
       </c>
+      <c r="G4" t="s">
+        <v>50</v>
+      </c>
       <c r="H4">
         <v>5</v>
       </c>
@@ -1448,15 +2081,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
         <v>45</v>
@@ -1467,6 +2100,9 @@
       <c r="F5" t="s">
         <v>46</v>
       </c>
+      <c r="G5" t="s">
+        <v>52</v>
+      </c>
       <c r="H5">
         <v>2</v>
       </c>
@@ -1480,15 +2116,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
         <v>45</v>
@@ -1499,6 +2135,9 @@
       <c r="F6" t="s">
         <v>46</v>
       </c>
+      <c r="G6" t="s">
+        <v>56</v>
+      </c>
       <c r="H6">
         <v>6</v>
       </c>
@@ -1512,15 +2151,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
         <v>45</v>
@@ -1531,6 +2170,9 @@
       <c r="F7" t="s">
         <v>46</v>
       </c>
+      <c r="G7" t="s">
+        <v>57</v>
+      </c>
       <c r="H7">
         <v>0</v>
       </c>
@@ -1544,15 +2186,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
         <v>45</v>
@@ -1563,6 +2205,9 @@
       <c r="F8" t="s">
         <v>46</v>
       </c>
+      <c r="G8" t="s">
+        <v>59</v>
+      </c>
       <c r="H8">
         <v>7</v>
       </c>
@@ -1576,15 +2221,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
         <v>45</v>
@@ -1595,6 +2240,9 @@
       <c r="F9" t="s">
         <v>46</v>
       </c>
+      <c r="G9" t="s">
+        <v>61</v>
+      </c>
       <c r="H9">
         <v>4</v>
       </c>
@@ -1608,15 +2256,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
         <v>45</v>
@@ -1627,6 +2275,9 @@
       <c r="F10" t="s">
         <v>46</v>
       </c>
+      <c r="G10" t="s">
+        <v>63</v>
+      </c>
       <c r="H10">
         <v>3</v>
       </c>
@@ -1640,15 +2291,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
         <v>45</v>
@@ -1659,6 +2310,9 @@
       <c r="F11" t="s">
         <v>46</v>
       </c>
+      <c r="G11" t="s">
+        <v>65</v>
+      </c>
       <c r="H11">
         <v>3</v>
       </c>
@@ -1672,15 +2326,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
         <v>45</v>
@@ -1689,6 +2343,9 @@
         <v>-1</v>
       </c>
       <c r="F12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" t="s">
         <v>67</v>
       </c>
       <c r="I12">
@@ -1701,24 +2358,27 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>71</v>
+        <v>73</v>
+      </c>
+      <c r="G13" t="s">
+        <v>70</v>
       </c>
       <c r="I13">
         <v>2</v>
@@ -1730,15 +2390,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
         <v>45</v>
@@ -1747,7 +2407,7 @@
         <v>-1</v>
       </c>
       <c r="F14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I14">
         <v>28</v>
@@ -1759,15 +2419,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
         <v>45</v>
@@ -1776,7 +2436,7 @@
         <v>-1</v>
       </c>
       <c r="F15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I15">
         <v>29</v>
@@ -1788,15 +2448,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
         <v>45</v>
@@ -1805,7 +2465,7 @@
         <v>-1</v>
       </c>
       <c r="F16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I16">
         <v>30</v>
@@ -1822,19 +2482,19 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E17">
         <v>-1</v>
       </c>
       <c r="F17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I17">
         <v>2</v>
@@ -1851,19 +2511,19 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E18">
         <v>-1</v>
       </c>
       <c r="F18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I18">
         <v>15</v>
@@ -1880,19 +2540,19 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E19">
         <v>-1</v>
       </c>
       <c r="F19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I19">
         <v>45</v>
@@ -1909,10 +2569,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
         <v>45</v>
@@ -1921,7 +2581,7 @@
         <v>-1</v>
       </c>
       <c r="F20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I20">
         <v>28</v>
@@ -1938,10 +2598,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
         <v>45</v>
@@ -1950,7 +2610,7 @@
         <v>-1</v>
       </c>
       <c r="F21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I21">
         <v>29</v>
@@ -1967,10 +2627,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D22" t="s">
         <v>45</v>
@@ -1979,7 +2639,7 @@
         <v>-1</v>
       </c>
       <c r="F22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I22">
         <v>30</v>
@@ -1996,10 +2656,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
         <v>45</v>
@@ -2008,7 +2668,7 @@
         <v>-1</v>
       </c>
       <c r="F23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I23">
         <v>15</v>
@@ -2025,19 +2685,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E24">
         <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H24">
         <v>13</v>
@@ -2057,19 +2717,19 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D25" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E25">
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H25">
         <v>13</v>
@@ -2089,19 +2749,19 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H26">
         <v>13</v>
@@ -2121,19 +2781,19 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E27">
         <v>3</v>
       </c>
       <c r="F27" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H27">
         <v>13</v>
@@ -2153,10 +2813,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
         <v>45</v>
@@ -2165,7 +2825,7 @@
         <v>-1</v>
       </c>
       <c r="F28" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H28">
         <v>13</v>
@@ -2185,10 +2845,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D29" t="s">
         <v>45</v>
@@ -2197,7 +2857,7 @@
         <v>-1</v>
       </c>
       <c r="F29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H29">
         <v>13</v>
@@ -2217,10 +2877,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D30" t="s">
         <v>45</v>
@@ -2229,7 +2889,7 @@
         <v>-1</v>
       </c>
       <c r="F30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H30">
         <v>12</v>
@@ -2249,10 +2909,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D31" t="s">
         <v>45</v>
@@ -2261,7 +2921,7 @@
         <v>-1</v>
       </c>
       <c r="F31" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H31">
         <v>12</v>
@@ -2281,19 +2941,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D32" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E32">
         <v>3</v>
       </c>
       <c r="F32" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H32">
         <v>10</v>
@@ -2308,24 +2968,24 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:11">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E33">
         <v>3</v>
       </c>
       <c r="F33" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H33">
         <v>11</v>
@@ -2340,24 +3000,24 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:11">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C34" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E34">
         <v>3</v>
       </c>
       <c r="F34" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H34">
         <v>12</v>
@@ -2372,15 +3032,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:11">
       <c r="A35">
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D35" t="s">
         <v>45</v>
@@ -2389,7 +3049,7 @@
         <v>-1</v>
       </c>
       <c r="F35" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I35">
         <v>57</v>
@@ -2401,15 +3061,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:11">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C36" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D36" t="s">
         <v>45</v>
@@ -2418,7 +3078,7 @@
         <v>-1</v>
       </c>
       <c r="F36" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I36">
         <v>58</v>
@@ -2430,15 +3090,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:11">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C37" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D37" t="s">
         <v>45</v>
@@ -2447,7 +3107,7 @@
         <v>-1</v>
       </c>
       <c r="F37" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I37">
         <v>59</v>
@@ -2459,15 +3119,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:11">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C38" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D38" t="s">
         <v>45</v>
@@ -2476,7 +3136,7 @@
         <v>-1</v>
       </c>
       <c r="F38" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I38">
         <v>60</v>
@@ -2488,15 +3148,15 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:11">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D39" t="s">
         <v>45</v>
@@ -2505,7 +3165,7 @@
         <v>-1</v>
       </c>
       <c r="F39" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I39">
         <v>61</v>
@@ -2517,15 +3177,15 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:11">
       <c r="A40">
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C40" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D40" t="s">
         <v>45</v>
@@ -2534,7 +3194,7 @@
         <v>-1</v>
       </c>
       <c r="F40" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I40">
         <v>62</v>
@@ -2546,15 +3206,15 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:11">
       <c r="A41">
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C41" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D41" t="s">
         <v>45</v>
@@ -2563,7 +3223,7 @@
         <v>-1</v>
       </c>
       <c r="F41" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H41">
         <v>12</v>
@@ -2578,15 +3238,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:11">
       <c r="A42">
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D42" t="s">
         <v>45</v>
@@ -2595,7 +3255,7 @@
         <v>-1</v>
       </c>
       <c r="F42" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H42">
         <v>12</v>
@@ -2610,15 +3270,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:11">
       <c r="A43">
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C43" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D43" t="s">
         <v>45</v>
@@ -2627,7 +3287,7 @@
         <v>-1</v>
       </c>
       <c r="F43" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H43">
         <v>12</v>
@@ -2642,15 +3302,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:11">
       <c r="A44">
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C44" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D44" t="s">
         <v>45</v>
@@ -2659,7 +3319,7 @@
         <v>-1</v>
       </c>
       <c r="F44" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I44">
         <v>28</v>
@@ -2671,15 +3331,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:11">
       <c r="A45">
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C45" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D45" t="s">
         <v>45</v>
@@ -2688,7 +3348,7 @@
         <v>-1</v>
       </c>
       <c r="F45" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I45">
         <v>29</v>
@@ -2700,15 +3360,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:11">
       <c r="A46">
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C46" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D46" t="s">
         <v>45</v>
@@ -2717,7 +3377,7 @@
         <v>-1</v>
       </c>
       <c r="F46" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I46">
         <v>30</v>
@@ -2734,10 +3394,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C47" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D47" t="s">
         <v>45</v>
@@ -2746,7 +3406,7 @@
         <v>-1</v>
       </c>
       <c r="F47" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I47">
         <v>15</v>
@@ -2769,22 +3429,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:M14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.71296296296296" defaultRowHeight="13.8"/>
   <cols>
-    <col min="3" max="3" width="23.5703125" customWidth="1"/>
-    <col min="4" max="7" width="18.140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="3" max="3" width="23.5740740740741" customWidth="1"/>
+    <col min="4" max="7" width="18.1388888888889" customWidth="1"/>
+    <col min="8" max="8" width="10.5740740740741" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="12.85546875" customWidth="1"/>
+    <col min="10" max="10" width="12.8518518518519" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="11.28515625" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.287037037037" customWidth="1"/>
+    <col min="13" max="13" width="10.712962962963" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -2801,10 +3463,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G1" t="s">
         <v>42</v>
@@ -2828,27 +3490,27 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -2857,27 +3519,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F3" t="s">
         <v>159</v>
       </c>
-      <c r="C3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E3" t="s">
-        <v>161</v>
-      </c>
-      <c r="F3" t="s">
-        <v>157</v>
-      </c>
       <c r="G3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H3">
         <v>15</v>
@@ -2886,27 +3548,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E4" t="s">
         <v>163</v>
       </c>
-      <c r="C4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D4" t="s">
-        <v>155</v>
-      </c>
-      <c r="E4" t="s">
-        <v>161</v>
-      </c>
       <c r="F4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H4">
         <v>45</v>
@@ -2915,27 +3577,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H5">
         <v>11</v>
@@ -2944,27 +3606,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H6">
         <v>38</v>
@@ -2973,27 +3635,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="60">
+    <row r="7" ht="41.4" spans="1:13">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D7" t="s">
-        <v>155</v>
-      </c>
-      <c r="E7" t="s">
-        <v>156</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>172</v>
-      </c>
       <c r="G7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H7">
         <v>13</v>
@@ -3014,27 +3676,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="30">
+    <row r="8" ht="27.6" spans="1:11">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H8">
         <v>4</v>
@@ -3046,27 +3708,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="45">
+    <row r="9" ht="41.4" spans="1:11">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H9">
         <v>9</v>
@@ -3081,27 +3743,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -3113,27 +3775,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>189</v>
+      </c>
+      <c r="C11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D11" t="s">
+        <v>157</v>
+      </c>
+      <c r="E11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C11" t="s">
-        <v>188</v>
-      </c>
-      <c r="D11" t="s">
-        <v>155</v>
-      </c>
-      <c r="E11" t="s">
-        <v>161</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="G11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H11">
         <v>63</v>
@@ -3148,27 +3810,27 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H12">
         <v>65</v>
@@ -3177,27 +3839,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E13" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G13" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H13">
         <v>14</v>
@@ -3206,10 +3868,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="6:6">
       <c r="F14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -253,7 +253,7 @@
     <t>OnTurnBeginBuffApply</t>
   </si>
   <si>
-    <t>唱歌的技巧</t>
+    <t>音乐饼干</t>
   </si>
   <si>
     <t>删除卡牌时歌力+8</t>
@@ -262,19 +262,19 @@
     <t>OnCardRemoved</t>
   </si>
   <si>
-    <t>游戏的技巧</t>
+    <t>游戏饼干</t>
   </si>
   <si>
     <t>删除卡牌时游戏力+8</t>
   </si>
   <si>
-    <t>杂谈的技巧</t>
+    <t>杂谈饼干</t>
   </si>
   <si>
     <t>删除卡牌时杂谈力+8</t>
   </si>
   <si>
-    <t>唱歌的心得</t>
+    <t>音乐区水杯</t>
   </si>
   <si>
     <t>直播开始时，神采+8</t>
@@ -283,19 +283,19 @@
     <t>OnBattleBegin</t>
   </si>
   <si>
-    <t>游戏的心得</t>
+    <t>游戏区心得</t>
   </si>
   <si>
     <t>直播开始时，红温+4</t>
   </si>
   <si>
-    <t>杂谈的心得</t>
+    <t>杂谈区心得</t>
   </si>
   <si>
     <t>直播开始时，幽默+4</t>
   </si>
   <si>
-    <t>唱歌的理论</t>
+    <t>唱歌笔记</t>
   </si>
   <si>
     <t>获得卡牌时，歌力+4</t>
@@ -304,13 +304,13 @@
     <t>OnCardAdded</t>
   </si>
   <si>
-    <t>游戏的理论</t>
+    <t>游戏笔记</t>
   </si>
   <si>
     <t>获得卡牌时，游戏力+4</t>
   </si>
   <si>
-    <t>杂谈的理论</t>
+    <t>杂谈笔记</t>
   </si>
   <si>
     <t>获得卡牌时，杂谈力+4</t>
@@ -1907,7 +1907,7 @@
     <col min="4" max="4" width="12.1388888888889" customWidth="1"/>
     <col min="5" max="5" width="5.42592592592593" customWidth="1"/>
     <col min="6" max="6" width="20.1388888888889" customWidth="1"/>
-    <col min="7" max="7" width="3.85185185185185" customWidth="1"/>
+    <col min="7" max="7" width="15.2962962962963" customWidth="1"/>
     <col min="8" max="8" width="7.42592592592593" customWidth="1"/>
     <col min="9" max="9" width="10.287037037037" customWidth="1"/>
     <col min="10" max="10" width="13.1388888888889" customWidth="1"/>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380" activeTab="1"/>
+    <workbookView windowWidth="15215" windowHeight="11748" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="208">
   <si>
     <t>ID</t>
   </si>
@@ -262,18 +262,27 @@
     <t>OnCardRemoved</t>
   </si>
   <si>
+    <t>cookie3</t>
+  </si>
+  <si>
     <t>游戏饼干</t>
   </si>
   <si>
     <t>删除卡牌时游戏力+8</t>
   </si>
   <si>
+    <t>cookie1</t>
+  </si>
+  <si>
     <t>杂谈饼干</t>
   </si>
   <si>
     <t>删除卡牌时杂谈力+8</t>
   </si>
   <si>
+    <t>cookie2</t>
+  </si>
+  <si>
     <t>音乐区水杯</t>
   </si>
   <si>
@@ -283,18 +292,27 @@
     <t>OnBattleBegin</t>
   </si>
   <si>
+    <t>cup1</t>
+  </si>
+  <si>
     <t>游戏区心得</t>
   </si>
   <si>
     <t>直播开始时，红温+4</t>
   </si>
   <si>
+    <t>cup2</t>
+  </si>
+  <si>
     <t>杂谈区心得</t>
   </si>
   <si>
     <t>直播开始时，幽默+4</t>
   </si>
   <si>
+    <t>cup3</t>
+  </si>
+  <si>
     <t>唱歌笔记</t>
   </si>
   <si>
@@ -304,22 +322,34 @@
     <t>OnCardAdded</t>
   </si>
   <si>
+    <t>note1</t>
+  </si>
+  <si>
     <t>游戏笔记</t>
   </si>
   <si>
     <t>获得卡牌时，游戏力+4</t>
   </si>
   <si>
+    <t>note2</t>
+  </si>
+  <si>
     <t>杂谈笔记</t>
   </si>
   <si>
     <t>获得卡牌时，杂谈力+4</t>
   </si>
   <si>
+    <t>note3</t>
+  </si>
+  <si>
     <t>饭撒的理论</t>
   </si>
   <si>
     <t>获得卡牌时，粉丝数+25</t>
+  </si>
+  <si>
+    <t>note4</t>
   </si>
   <si>
     <t>唱歌的理解</t>
@@ -1920,7 +1950,7 @@
     <col min="17" max="17" width="17.1388888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.6" spans="1:18">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2409,6 +2439,9 @@
       <c r="F14" t="s">
         <v>76</v>
       </c>
+      <c r="G14" t="s">
+        <v>77</v>
+      </c>
       <c r="I14">
         <v>28</v>
       </c>
@@ -2424,10 +2457,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
         <v>45</v>
@@ -2437,6 +2470,9 @@
       </c>
       <c r="F15" t="s">
         <v>76</v>
+      </c>
+      <c r="G15" t="s">
+        <v>80</v>
       </c>
       <c r="I15">
         <v>29</v>
@@ -2453,10 +2489,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
         <v>45</v>
@@ -2466,6 +2502,9 @@
       </c>
       <c r="F16" t="s">
         <v>76</v>
+      </c>
+      <c r="G16" t="s">
+        <v>83</v>
       </c>
       <c r="I16">
         <v>30</v>
@@ -2482,10 +2521,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
         <v>72</v>
@@ -2494,7 +2533,10 @@
         <v>-1</v>
       </c>
       <c r="F17" t="s">
-        <v>83</v>
+        <v>86</v>
+      </c>
+      <c r="G17" t="s">
+        <v>87</v>
       </c>
       <c r="I17">
         <v>2</v>
@@ -2511,10 +2553,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
         <v>72</v>
@@ -2523,7 +2565,10 @@
         <v>-1</v>
       </c>
       <c r="F18" t="s">
-        <v>83</v>
+        <v>86</v>
+      </c>
+      <c r="G18" t="s">
+        <v>90</v>
       </c>
       <c r="I18">
         <v>15</v>
@@ -2540,10 +2585,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
         <v>72</v>
@@ -2552,7 +2597,10 @@
         <v>-1</v>
       </c>
       <c r="F19" t="s">
-        <v>83</v>
+        <v>86</v>
+      </c>
+      <c r="G19" t="s">
+        <v>93</v>
       </c>
       <c r="I19">
         <v>45</v>
@@ -2569,10 +2617,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D20" t="s">
         <v>45</v>
@@ -2581,7 +2629,10 @@
         <v>-1</v>
       </c>
       <c r="F20" t="s">
-        <v>90</v>
+        <v>96</v>
+      </c>
+      <c r="G20" t="s">
+        <v>97</v>
       </c>
       <c r="I20">
         <v>28</v>
@@ -2598,10 +2649,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
         <v>45</v>
@@ -2610,7 +2661,10 @@
         <v>-1</v>
       </c>
       <c r="F21" t="s">
-        <v>90</v>
+        <v>96</v>
+      </c>
+      <c r="G21" t="s">
+        <v>100</v>
       </c>
       <c r="I21">
         <v>29</v>
@@ -2627,10 +2681,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s">
         <v>45</v>
@@ -2639,7 +2693,10 @@
         <v>-1</v>
       </c>
       <c r="F22" t="s">
-        <v>90</v>
+        <v>96</v>
+      </c>
+      <c r="G22" t="s">
+        <v>103</v>
       </c>
       <c r="I22">
         <v>30</v>
@@ -2656,10 +2713,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
         <v>45</v>
@@ -2668,7 +2725,10 @@
         <v>-1</v>
       </c>
       <c r="F23" t="s">
-        <v>90</v>
+        <v>96</v>
+      </c>
+      <c r="G23" t="s">
+        <v>106</v>
       </c>
       <c r="I23">
         <v>15</v>
@@ -2685,10 +2745,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
         <v>72</v>
@@ -2697,7 +2757,7 @@
         <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="H24">
         <v>13</v>
@@ -2717,10 +2777,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D25" t="s">
         <v>72</v>
@@ -2729,7 +2789,7 @@
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="H25">
         <v>13</v>
@@ -2749,10 +2809,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s">
         <v>72</v>
@@ -2761,7 +2821,7 @@
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="H26">
         <v>13</v>
@@ -2781,10 +2841,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s">
         <v>72</v>
@@ -2793,7 +2853,7 @@
         <v>3</v>
       </c>
       <c r="F27" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="H27">
         <v>13</v>
@@ -2813,10 +2873,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
         <v>45</v>
@@ -2825,7 +2885,7 @@
         <v>-1</v>
       </c>
       <c r="F28" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H28">
         <v>13</v>
@@ -2845,10 +2905,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C29" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
         <v>45</v>
@@ -2857,7 +2917,7 @@
         <v>-1</v>
       </c>
       <c r="F29" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H29">
         <v>13</v>
@@ -2877,10 +2937,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D30" t="s">
         <v>45</v>
@@ -2889,7 +2949,7 @@
         <v>-1</v>
       </c>
       <c r="F30" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H30">
         <v>12</v>
@@ -2909,10 +2969,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D31" t="s">
         <v>45</v>
@@ -2921,7 +2981,7 @@
         <v>-1</v>
       </c>
       <c r="F31" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="H31">
         <v>12</v>
@@ -2941,10 +3001,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C32" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D32" t="s">
         <v>72</v>
@@ -2973,10 +3033,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D33" t="s">
         <v>72</v>
@@ -3005,10 +3065,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D34" t="s">
         <v>72</v>
@@ -3037,10 +3097,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="C35" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="D35" t="s">
         <v>45</v>
@@ -3049,7 +3109,7 @@
         <v>-1</v>
       </c>
       <c r="F35" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="I35">
         <v>57</v>
@@ -3066,10 +3126,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C36" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D36" t="s">
         <v>45</v>
@@ -3078,7 +3138,7 @@
         <v>-1</v>
       </c>
       <c r="F36" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="I36">
         <v>58</v>
@@ -3095,10 +3155,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C37" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D37" t="s">
         <v>45</v>
@@ -3107,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="F37" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="I37">
         <v>59</v>
@@ -3124,10 +3184,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C38" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D38" t="s">
         <v>45</v>
@@ -3136,7 +3196,7 @@
         <v>-1</v>
       </c>
       <c r="F38" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="I38">
         <v>60</v>
@@ -3153,10 +3213,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C39" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="D39" t="s">
         <v>45</v>
@@ -3165,7 +3225,7 @@
         <v>-1</v>
       </c>
       <c r="F39" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="I39">
         <v>61</v>
@@ -3182,10 +3242,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="C40" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D40" t="s">
         <v>45</v>
@@ -3194,7 +3254,7 @@
         <v>-1</v>
       </c>
       <c r="F40" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="I40">
         <v>62</v>
@@ -3211,10 +3271,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C41" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="D41" t="s">
         <v>45</v>
@@ -3223,7 +3283,7 @@
         <v>-1</v>
       </c>
       <c r="F41" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="H41">
         <v>12</v>
@@ -3243,10 +3303,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C42" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D42" t="s">
         <v>45</v>
@@ -3255,7 +3315,7 @@
         <v>-1</v>
       </c>
       <c r="F42" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="H42">
         <v>12</v>
@@ -3275,10 +3335,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C43" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D43" t="s">
         <v>45</v>
@@ -3287,7 +3347,7 @@
         <v>-1</v>
       </c>
       <c r="F43" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="H43">
         <v>12</v>
@@ -3307,10 +3367,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C44" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="D44" t="s">
         <v>45</v>
@@ -3319,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="F44" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="I44">
         <v>28</v>
@@ -3336,10 +3396,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C45" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D45" t="s">
         <v>45</v>
@@ -3348,7 +3408,7 @@
         <v>-1</v>
       </c>
       <c r="F45" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="I45">
         <v>29</v>
@@ -3365,10 +3425,10 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C46" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D46" t="s">
         <v>45</v>
@@ -3377,7 +3437,7 @@
         <v>-1</v>
       </c>
       <c r="F46" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="I46">
         <v>30</v>
@@ -3394,10 +3454,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="C47" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="D47" t="s">
         <v>45</v>
@@ -3406,7 +3466,7 @@
         <v>-1</v>
       </c>
       <c r="F47" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="I47">
         <v>15</v>
@@ -3463,10 +3523,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F1" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="G1" t="s">
         <v>42</v>
@@ -3495,22 +3555,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="C2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="D2" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E2" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="F2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="G2" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -3524,22 +3584,22 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="C3" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="D3" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="F3" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="G3" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H3">
         <v>15</v>
@@ -3553,22 +3613,22 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="C4" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E4" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="F4" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="G4" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="H4">
         <v>45</v>
@@ -3582,22 +3642,22 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E5" t="s">
         <v>168</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
         <v>169</v>
       </c>
-      <c r="D5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E5" t="s">
-        <v>158</v>
-      </c>
-      <c r="F5" t="s">
-        <v>159</v>
-      </c>
       <c r="G5" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H5">
         <v>11</v>
@@ -3611,22 +3671,22 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C6" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="D6" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="E6" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="G6" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="H6">
         <v>38</v>
@@ -3640,22 +3700,22 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E7" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="G7" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="H7">
         <v>13</v>
@@ -3681,22 +3741,22 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E8" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="G8" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="H8">
         <v>4</v>
@@ -3713,22 +3773,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E9" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="G9" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="H9">
         <v>9</v>
@@ -3748,22 +3808,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="C10" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="D10" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E10" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="G10" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -3780,22 +3840,22 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="C11" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="D11" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E11" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="G11" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="H11">
         <v>63</v>
@@ -3815,22 +3875,22 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="C12" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="D12" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E12" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="G12" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="H12">
         <v>65</v>
@@ -3844,22 +3904,22 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C13" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="D13" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E13" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="G13" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="H13">
         <v>14</v>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="215">
   <si>
     <t>ID</t>
   </si>
@@ -361,24 +361,36 @@
     <t>OnCardUsed</t>
   </si>
   <si>
+    <t>baji1</t>
+  </si>
+  <si>
     <t>游戏区大吧唧</t>
   </si>
   <si>
     <t>每使用两张卡，参数+4</t>
   </si>
   <si>
+    <t>baji2</t>
+  </si>
+  <si>
     <t>杂谈区大吧唧</t>
   </si>
   <si>
     <t>每使用两张卡，红温+3</t>
   </si>
   <si>
+    <t>baji3</t>
+  </si>
+  <si>
     <t>粉丝自制大吧唧</t>
   </si>
   <si>
     <t>每使用两张卡，获得20同接</t>
   </si>
   <si>
+    <t>baji4</t>
+  </si>
+  <si>
     <t>爱墨生的薯ki</t>
   </si>
   <si>
@@ -388,18 +400,27 @@
     <t>OnCardUpgraded</t>
   </si>
   <si>
+    <t>fan1</t>
+  </si>
+  <si>
     <t>爱墨生的结晶</t>
   </si>
   <si>
     <t>每当删除卡牌时，舰长+1</t>
   </si>
   <si>
-    <t>爱墨生的礼物</t>
+    <t>fan2</t>
+  </si>
+  <si>
+    <t>爱墨生的贡品</t>
   </si>
   <si>
     <t>每当获得卡牌时，沪币+30</t>
   </si>
   <si>
+    <t>fan3</t>
+  </si>
+  <si>
     <t>爱墨生的精气</t>
   </si>
   <si>
@@ -409,24 +430,36 @@
     <t>OnStaminaChanged</t>
   </si>
   <si>
+    <t>fan4</t>
+  </si>
+  <si>
     <t>应援棒-红</t>
   </si>
   <si>
     <t>当处于唱歌回合时，参数获得量+50%，直播中触发3次</t>
   </si>
   <si>
+    <t>call1</t>
+  </si>
+  <si>
     <t>应援棒-蓝</t>
   </si>
   <si>
     <t>当处于游戏回合时，参数获得量+50%，直播中触发3次</t>
   </si>
   <si>
+    <t>call2</t>
+  </si>
+  <si>
     <t>应援棒-黄</t>
   </si>
   <si>
     <t>当处于杂谈回合时，参数获得量+50%，直播中触发3次</t>
   </si>
   <si>
+    <t>call3</t>
+  </si>
+  <si>
     <t>百舰徽章-音乐区</t>
   </si>
   <si>
@@ -436,18 +469,27 @@
     <t>OnWeekEnd</t>
   </si>
   <si>
+    <t>jianzhang1</t>
+  </si>
+  <si>
     <t>百舰徽章-游戏区</t>
   </si>
   <si>
     <t>每周结束时，获得舰长数50%的游戏力</t>
   </si>
   <si>
+    <t>jianzhang2</t>
+  </si>
+  <si>
     <t>百舰徽章-电台区</t>
   </si>
   <si>
     <t>每周结束时，获得舰长数50%的杂谈力</t>
   </si>
   <si>
+    <t>jianzhang3</t>
+  </si>
+  <si>
     <t>粉丝徽章-音乐区</t>
   </si>
   <si>
@@ -457,16 +499,25 @@
     <t>OnPhaseEndingSelected</t>
   </si>
   <si>
+    <t>fans1</t>
+  </si>
+  <si>
     <t>粉丝徽章-游戏区</t>
   </si>
   <si>
     <t>每阶段结束时，获得粉丝数1%的游戏力</t>
   </si>
   <si>
+    <t>fans2</t>
+  </si>
+  <si>
     <t>粉丝徽章-电台区</t>
   </si>
   <si>
     <t>每阶段结束时，获得粉丝数1%的杂谈力</t>
+  </si>
+  <si>
+    <t>fans3</t>
   </si>
   <si>
     <t>收益徽章-音乐区</t>
@@ -2729,6 +2780,9 @@
       <c r="F24" t="s">
         <v>109</v>
       </c>
+      <c r="G24" t="s">
+        <v>110</v>
+      </c>
       <c r="H24">
         <v>13</v>
       </c>
@@ -2747,10 +2801,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s">
         <v>72</v>
@@ -2760,6 +2814,9 @@
       </c>
       <c r="F25" t="s">
         <v>109</v>
+      </c>
+      <c r="G25" t="s">
+        <v>113</v>
       </c>
       <c r="H25">
         <v>13</v>
@@ -2779,10 +2836,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
         <v>72</v>
@@ -2792,6 +2849,9 @@
       </c>
       <c r="F26" t="s">
         <v>109</v>
+      </c>
+      <c r="G26" t="s">
+        <v>116</v>
       </c>
       <c r="H26">
         <v>13</v>
@@ -2811,10 +2871,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s">
         <v>72</v>
@@ -2824,6 +2884,9 @@
       </c>
       <c r="F27" t="s">
         <v>109</v>
+      </c>
+      <c r="G27" t="s">
+        <v>119</v>
       </c>
       <c r="H27">
         <v>13</v>
@@ -2843,10 +2906,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s">
         <v>45</v>
@@ -2855,8 +2918,12 @@
         <v>-1</v>
       </c>
       <c r="F28" t="s">
-        <v>118</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="G28" t="s">
+        <v>123</v>
+      </c>
+      <c r="H28"/>
       <c r="I28">
         <v>15</v>
       </c>
@@ -2872,10 +2939,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D29" t="s">
         <v>45</v>
@@ -2886,6 +2953,10 @@
       <c r="F29" t="s">
         <v>76</v>
       </c>
+      <c r="G29" t="s">
+        <v>126</v>
+      </c>
+      <c r="H29"/>
       <c r="I29">
         <v>16</v>
       </c>
@@ -2901,10 +2972,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D30" t="s">
         <v>45</v>
@@ -2915,6 +2986,10 @@
       <c r="F30" t="s">
         <v>96</v>
       </c>
+      <c r="G30" t="s">
+        <v>129</v>
+      </c>
+      <c r="H30"/>
       <c r="I30">
         <v>5</v>
       </c>
@@ -2930,10 +3005,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D31" t="s">
         <v>45</v>
@@ -2942,7 +3017,10 @@
         <v>-1</v>
       </c>
       <c r="F31" t="s">
-        <v>125</v>
+        <v>132</v>
+      </c>
+      <c r="G31" t="s">
+        <v>133</v>
       </c>
       <c r="H31">
         <v>12</v>
@@ -2962,10 +3040,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C32" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D32" t="s">
         <v>72</v>
@@ -2975,6 +3053,9 @@
       </c>
       <c r="F32" t="s">
         <v>73</v>
+      </c>
+      <c r="G32" t="s">
+        <v>136</v>
       </c>
       <c r="H32">
         <v>10</v>
@@ -2994,10 +3075,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C33" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D33" t="s">
         <v>72</v>
@@ -3007,6 +3088,9 @@
       </c>
       <c r="F33" t="s">
         <v>73</v>
+      </c>
+      <c r="G33" t="s">
+        <v>139</v>
       </c>
       <c r="H33">
         <v>11</v>
@@ -3026,10 +3110,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C34" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="D34" t="s">
         <v>72</v>
@@ -3039,6 +3123,9 @@
       </c>
       <c r="F34" t="s">
         <v>73</v>
+      </c>
+      <c r="G34" t="s">
+        <v>142</v>
       </c>
       <c r="H34">
         <v>12</v>
@@ -3058,10 +3145,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="C35" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="D35" t="s">
         <v>45</v>
@@ -3070,7 +3157,10 @@
         <v>-1</v>
       </c>
       <c r="F35" t="s">
-        <v>134</v>
+        <v>145</v>
+      </c>
+      <c r="G35" t="s">
+        <v>146</v>
       </c>
       <c r="I35">
         <v>57</v>
@@ -3087,10 +3177,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="C36" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="D36" t="s">
         <v>45</v>
@@ -3099,7 +3189,10 @@
         <v>-1</v>
       </c>
       <c r="F36" t="s">
-        <v>134</v>
+        <v>145</v>
+      </c>
+      <c r="G36" t="s">
+        <v>149</v>
       </c>
       <c r="I36">
         <v>58</v>
@@ -3116,10 +3209,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="C37" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="D37" t="s">
         <v>45</v>
@@ -3128,7 +3221,10 @@
         <v>-1</v>
       </c>
       <c r="F37" t="s">
-        <v>134</v>
+        <v>145</v>
+      </c>
+      <c r="G37" t="s">
+        <v>152</v>
       </c>
       <c r="I37">
         <v>59</v>
@@ -3145,10 +3241,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="C38" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="D38" t="s">
         <v>45</v>
@@ -3157,7 +3253,10 @@
         <v>-1</v>
       </c>
       <c r="F38" t="s">
-        <v>141</v>
+        <v>155</v>
+      </c>
+      <c r="G38" t="s">
+        <v>156</v>
       </c>
       <c r="I38">
         <v>60</v>
@@ -3174,10 +3273,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="C39" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="D39" t="s">
         <v>45</v>
@@ -3186,7 +3285,10 @@
         <v>-1</v>
       </c>
       <c r="F39" t="s">
-        <v>141</v>
+        <v>155</v>
+      </c>
+      <c r="G39" t="s">
+        <v>159</v>
       </c>
       <c r="I39">
         <v>61</v>
@@ -3203,10 +3305,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C40" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="D40" t="s">
         <v>45</v>
@@ -3215,7 +3317,10 @@
         <v>-1</v>
       </c>
       <c r="F40" t="s">
-        <v>141</v>
+        <v>155</v>
+      </c>
+      <c r="G40" t="s">
+        <v>162</v>
       </c>
       <c r="I40">
         <v>62</v>
@@ -3232,10 +3337,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="C41" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="D41" t="s">
         <v>45</v>
@@ -3244,7 +3349,7 @@
         <v>-1</v>
       </c>
       <c r="F41" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="H41">
         <v>12</v>
@@ -3264,10 +3369,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="C42" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="D42" t="s">
         <v>45</v>
@@ -3276,7 +3381,7 @@
         <v>-1</v>
       </c>
       <c r="F42" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="H42">
         <v>12</v>
@@ -3296,10 +3401,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="C43" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="D43" t="s">
         <v>45</v>
@@ -3308,7 +3413,7 @@
         <v>-1</v>
       </c>
       <c r="F43" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="H43">
         <v>12</v>
@@ -3360,10 +3465,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="F1" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="G1" t="s">
         <v>42</v>
@@ -3392,22 +3497,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="C2" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="D2" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="E2" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="F2" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="G2" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -3421,22 +3526,22 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="C3" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="D3" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="E3" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="F3" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="G3" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="H3">
         <v>15</v>
@@ -3450,22 +3555,22 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="C4" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="E4" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="F4" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="G4" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="H4">
         <v>45</v>
@@ -3479,22 +3584,22 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="E5" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="F5" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="G5" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="H5">
         <v>11</v>
@@ -3508,22 +3613,22 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="C6" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="D6" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="E6" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="G6" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="H6">
         <v>38</v>
@@ -3537,22 +3642,22 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="E7" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="G7" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="H7">
         <v>13</v>
@@ -3578,22 +3683,22 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="E8" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="G8" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="H8">
         <v>4</v>
@@ -3610,22 +3715,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="E9" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="G9" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="H9">
         <v>9</v>
@@ -3645,22 +3750,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="C10" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="D10" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="E10" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="G10" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -3677,22 +3782,22 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="C11" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="D11" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="E11" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="G11" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="H11">
         <v>63</v>
@@ -3712,22 +3817,22 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C12" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="D12" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="E12" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="G12" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="H12">
         <v>65</v>
@@ -3741,22 +3846,22 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="C13" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="D13" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="E13" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="G13" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="H13">
         <v>14</v>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="218">
   <si>
     <t>ID</t>
   </si>
@@ -529,16 +529,25 @@
     <t>OnMoneyChanged</t>
   </si>
   <si>
+    <t>coin1</t>
+  </si>
+  <si>
     <t>收益徽章-游戏区</t>
   </si>
   <si>
     <t>每当消耗沪币时，游戏力+5</t>
   </si>
   <si>
+    <t>coin2</t>
+  </si>
+  <si>
     <t>收益徽章-电台区</t>
   </si>
   <si>
     <t>每当消耗沪币时，杂谈力+5</t>
+  </si>
+  <si>
+    <t>coin3</t>
   </si>
   <si>
     <t>LiveType</t>
@@ -3351,6 +3360,9 @@
       <c r="F41" t="s">
         <v>165</v>
       </c>
+      <c r="G41" t="s">
+        <v>166</v>
+      </c>
       <c r="H41">
         <v>12</v>
       </c>
@@ -3369,10 +3381,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C42" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D42" t="s">
         <v>45</v>
@@ -3382,6 +3394,9 @@
       </c>
       <c r="F42" t="s">
         <v>165</v>
+      </c>
+      <c r="G42" t="s">
+        <v>169</v>
       </c>
       <c r="H42">
         <v>12</v>
@@ -3401,10 +3416,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C43" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D43" t="s">
         <v>45</v>
@@ -3414,6 +3429,9 @@
       </c>
       <c r="F43" t="s">
         <v>165</v>
+      </c>
+      <c r="G43" t="s">
+        <v>172</v>
       </c>
       <c r="H43">
         <v>12</v>
@@ -3465,10 +3483,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G1" t="s">
         <v>42</v>
@@ -3497,22 +3515,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -3526,22 +3544,22 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F3" t="s">
         <v>179</v>
       </c>
-      <c r="D3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E3" t="s">
-        <v>180</v>
-      </c>
-      <c r="F3" t="s">
-        <v>176</v>
-      </c>
       <c r="G3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H3">
         <v>15</v>
@@ -3555,22 +3573,22 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E4" t="s">
         <v>183</v>
       </c>
-      <c r="D4" t="s">
-        <v>174</v>
-      </c>
-      <c r="E4" t="s">
-        <v>180</v>
-      </c>
       <c r="F4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H4">
         <v>45</v>
@@ -3584,22 +3602,22 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H5">
         <v>11</v>
@@ -3613,22 +3631,22 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C6" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D6" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E6" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H6">
         <v>38</v>
@@ -3642,22 +3660,22 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D7" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" t="s">
+        <v>178</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="D7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E7" t="s">
-        <v>175</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="G7" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H7">
         <v>13</v>
@@ -3683,22 +3701,22 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G8" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H8">
         <v>4</v>
@@ -3715,22 +3733,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D9" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E9" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G9" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H9">
         <v>9</v>
@@ -3750,22 +3768,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C10" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D10" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G10" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -3782,22 +3800,22 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C11" t="s">
+        <v>210</v>
+      </c>
+      <c r="D11" t="s">
+        <v>177</v>
+      </c>
+      <c r="E11" t="s">
+        <v>183</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D11" t="s">
-        <v>174</v>
-      </c>
-      <c r="E11" t="s">
-        <v>180</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="G11" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="H11">
         <v>63</v>
@@ -3817,22 +3835,22 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C12" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E12" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G12" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H12">
         <v>65</v>
@@ -3846,22 +3864,22 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C13" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E13" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G13" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H13">
         <v>14</v>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380" activeTab="1"/>
+    <workbookView windowWidth="24750" windowHeight="10030" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -1635,15 +1635,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="3.13888888888889" customWidth="1"/>
-    <col min="2" max="2" width="11.712962962963" customWidth="1"/>
-    <col min="3" max="3" width="15.4259259259259" customWidth="1"/>
-    <col min="4" max="4" width="28.712962962963" customWidth="1"/>
-    <col min="5" max="5" width="14.712962962963" customWidth="1"/>
-    <col min="6" max="6" width="13.4259259259259" customWidth="1"/>
-    <col min="7" max="7" width="10.4259259259259" customWidth="1"/>
+    <col min="1" max="1" width="3.14166666666667" customWidth="1"/>
+    <col min="2" max="2" width="11.7166666666667" customWidth="1"/>
+    <col min="3" max="3" width="15.425" customWidth="1"/>
+    <col min="4" max="4" width="28.7166666666667" customWidth="1"/>
+    <col min="5" max="5" width="14.7166666666667" customWidth="1"/>
+    <col min="6" max="6" width="13.425" customWidth="1"/>
+    <col min="7" max="7" width="10.425" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1959,25 +1959,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="3.42592592592593" customWidth="1"/>
-    <col min="2" max="2" width="13.5740740740741" customWidth="1"/>
-    <col min="3" max="3" width="39.1388888888889" customWidth="1"/>
-    <col min="4" max="4" width="12.1388888888889" customWidth="1"/>
-    <col min="5" max="5" width="5.42592592592593" customWidth="1"/>
-    <col min="6" max="6" width="20.1388888888889" customWidth="1"/>
-    <col min="7" max="7" width="15.2962962962963" customWidth="1"/>
-    <col min="8" max="8" width="7.42592592592593" customWidth="1"/>
-    <col min="9" max="9" width="10.287037037037" customWidth="1"/>
-    <col min="10" max="10" width="13.1388888888889" customWidth="1"/>
-    <col min="11" max="11" width="17.1388888888889" customWidth="1"/>
-    <col min="12" max="12" width="14.1388888888889" customWidth="1"/>
-    <col min="13" max="13" width="12.4259259259259" customWidth="1"/>
+    <col min="1" max="1" width="3.425" customWidth="1"/>
+    <col min="2" max="2" width="13.575" customWidth="1"/>
+    <col min="3" max="3" width="39.1416666666667" customWidth="1"/>
+    <col min="4" max="4" width="12.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="5.425" customWidth="1"/>
+    <col min="6" max="6" width="20.1416666666667" customWidth="1"/>
+    <col min="7" max="7" width="15.3" customWidth="1"/>
+    <col min="8" max="8" width="7.425" customWidth="1"/>
+    <col min="9" max="9" width="10.2833333333333" customWidth="1"/>
+    <col min="10" max="10" width="13.1416666666667" customWidth="1"/>
+    <col min="11" max="11" width="17.1416666666667" customWidth="1"/>
+    <col min="12" max="12" width="14.1416666666667" customWidth="1"/>
+    <col min="13" max="13" width="12.425" customWidth="1"/>
     <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="11.8518518518519" customWidth="1"/>
-    <col min="16" max="16" width="11.5740740740741" customWidth="1"/>
-    <col min="17" max="17" width="17.1388888888889" customWidth="1"/>
+    <col min="15" max="15" width="11.85" customWidth="1"/>
+    <col min="16" max="16" width="11.575" customWidth="1"/>
+    <col min="17" max="17" width="17.1416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -2036,7 +2036,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2246,7 +2246,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>67</v>
       </c>
       <c r="I12">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="J12">
         <v>0.25</v>
@@ -2418,7 +2418,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:18">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2450,7 +2450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:18">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:18">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2932,7 +2932,6 @@
       <c r="G28" t="s">
         <v>123</v>
       </c>
-      <c r="H28"/>
       <c r="I28">
         <v>15</v>
       </c>
@@ -2965,7 +2964,6 @@
       <c r="G29" t="s">
         <v>126</v>
       </c>
-      <c r="H29"/>
       <c r="I29">
         <v>16</v>
       </c>
@@ -2998,7 +2996,6 @@
       <c r="G30" t="s">
         <v>129</v>
       </c>
-      <c r="H30"/>
       <c r="I30">
         <v>5</v>
       </c>
@@ -3457,16 +3454,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:M14"/>
-  <sheetFormatPr defaultColWidth="8.71296296296296" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.71666666666667" defaultRowHeight="14"/>
   <cols>
-    <col min="3" max="3" width="23.5740740740741" customWidth="1"/>
-    <col min="4" max="7" width="18.1388888888889" customWidth="1"/>
-    <col min="8" max="8" width="10.5740740740741" customWidth="1"/>
+    <col min="3" max="3" width="23.575" customWidth="1"/>
+    <col min="4" max="7" width="18.1416666666667" customWidth="1"/>
+    <col min="8" max="8" width="10.575" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="12.8518518518519" customWidth="1"/>
+    <col min="10" max="10" width="12.85" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="11.287037037037" customWidth="1"/>
-    <col min="13" max="13" width="10.712962962963" customWidth="1"/>
+    <col min="12" max="12" width="11.2833333333333" customWidth="1"/>
+    <col min="13" max="13" width="10.7166666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -3510,7 +3507,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>0</v>
       </c>
@@ -3539,7 +3536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3568,7 +3565,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>2</v>
       </c>
@@ -3597,7 +3594,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>3</v>
       </c>
@@ -3626,7 +3623,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>4</v>
       </c>
@@ -3655,7 +3652,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" ht="41.4" spans="1:13">
+    <row r="7" ht="42" spans="1:13">
       <c r="A7">
         <v>5</v>
       </c>
@@ -3696,7 +3693,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="27.6" spans="1:11">
+    <row r="8" ht="28" spans="1:13">
       <c r="A8">
         <v>6</v>
       </c>
@@ -3728,7 +3725,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="41.4" spans="1:11">
+    <row r="9" ht="42" spans="1:13">
       <c r="A9">
         <v>7</v>
       </c>
@@ -3763,7 +3760,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>8</v>
       </c>
@@ -3795,7 +3792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3830,7 +3827,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:13">
       <c r="A12">
         <v>10</v>
       </c>
@@ -3859,7 +3856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:13">
       <c r="A13">
         <v>11</v>
       </c>
@@ -3888,7 +3885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="6:6">
+    <row r="14" spans="1:13">
       <c r="F14" s="1"/>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -496,7 +496,7 @@
     <t>每阶段结束时，获得粉丝数1%的歌力</t>
   </si>
   <si>
-    <t>OnPhaseEndingSelected</t>
+    <t>OnPhaseEnd</t>
   </si>
   <si>
     <t>fans1</t>

--- a/Assets/StreamingAssets/Configurations/Relics.xlsx
+++ b/Assets/StreamingAssets/Configurations/Relics.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D3A414D-8DCA-40C7-AEE8-05D9F95EE802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10030" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingRelicConditions" sheetId="1" r:id="rId1"/>
@@ -20,8 +26,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -496,9 +500,6 @@
     <t>每阶段结束时，获得粉丝数1%的歌力</t>
   </si>
   <si>
-    <t>OnPhaseEndingSelected</t>
-  </si>
-  <si>
     <t>fans1</t>
   </si>
   <si>
@@ -687,366 +688,33 @@
   </si>
   <si>
     <t>drink11</t>
+  </si>
+  <si>
+    <t>OnPhaseEnd</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1063,251 +731,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1316,61 +742,17 @@
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1628,22 +1010,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.14166666666667" customWidth="1"/>
-    <col min="2" max="2" width="11.7166666666667" customWidth="1"/>
-    <col min="3" max="3" width="15.425" customWidth="1"/>
-    <col min="4" max="4" width="28.7166666666667" customWidth="1"/>
-    <col min="5" max="5" width="14.7166666666667" customWidth="1"/>
-    <col min="6" max="6" width="13.425" customWidth="1"/>
-    <col min="7" max="7" width="10.425" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1951,33 +1333,31 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="13.575" customWidth="1"/>
-    <col min="3" max="3" width="39.1416666666667" customWidth="1"/>
-    <col min="4" max="4" width="12.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="5.425" customWidth="1"/>
-    <col min="6" max="6" width="20.1416666666667" customWidth="1"/>
-    <col min="7" max="7" width="15.3" customWidth="1"/>
-    <col min="8" max="8" width="7.425" customWidth="1"/>
-    <col min="9" max="9" width="10.2833333333333" customWidth="1"/>
-    <col min="10" max="10" width="13.1416666666667" customWidth="1"/>
-    <col min="11" max="11" width="17.1416666666667" customWidth="1"/>
-    <col min="12" max="12" width="14.1416666666667" customWidth="1"/>
-    <col min="13" max="13" width="12.425" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="39.140625" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" customWidth="1"/>
+    <col min="8" max="8" width="7.42578125" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="11" max="11" width="17.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
     <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="11.85" customWidth="1"/>
-    <col min="16" max="16" width="11.575" customWidth="1"/>
-    <col min="17" max="17" width="17.1416666666667" customWidth="1"/>
+    <col min="15" max="15" width="11.85546875" customWidth="1"/>
+    <col min="16" max="16" width="11.5703125" customWidth="1"/>
+    <col min="17" max="17" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -3259,10 +2639,10 @@
         <v>-1</v>
       </c>
       <c r="F38" t="s">
+        <v>217</v>
+      </c>
+      <c r="G38" t="s">
         <v>155</v>
-      </c>
-      <c r="G38" t="s">
-        <v>156</v>
       </c>
       <c r="I38">
         <v>60</v>
@@ -3279,10 +2659,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
+        <v>156</v>
+      </c>
+      <c r="C39" t="s">
         <v>157</v>
-      </c>
-      <c r="C39" t="s">
-        <v>158</v>
       </c>
       <c r="D39" t="s">
         <v>45</v>
@@ -3291,10 +2671,10 @@
         <v>-1</v>
       </c>
       <c r="F39" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="G39" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I39">
         <v>61</v>
@@ -3311,10 +2691,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
+        <v>159</v>
+      </c>
+      <c r="C40" t="s">
         <v>160</v>
-      </c>
-      <c r="C40" t="s">
-        <v>161</v>
       </c>
       <c r="D40" t="s">
         <v>45</v>
@@ -3323,10 +2703,10 @@
         <v>-1</v>
       </c>
       <c r="F40" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="G40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I40">
         <v>62</v>
@@ -3343,10 +2723,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
+        <v>162</v>
+      </c>
+      <c r="C41" t="s">
         <v>163</v>
-      </c>
-      <c r="C41" t="s">
-        <v>164</v>
       </c>
       <c r="D41" t="s">
         <v>45</v>
@@ -3355,10 +2735,10 @@
         <v>-1</v>
       </c>
       <c r="F41" t="s">
+        <v>164</v>
+      </c>
+      <c r="G41" t="s">
         <v>165</v>
-      </c>
-      <c r="G41" t="s">
-        <v>166</v>
       </c>
       <c r="H41">
         <v>12</v>
@@ -3378,10 +2758,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
+        <v>166</v>
+      </c>
+      <c r="C42" t="s">
         <v>167</v>
-      </c>
-      <c r="C42" t="s">
-        <v>168</v>
       </c>
       <c r="D42" t="s">
         <v>45</v>
@@ -3390,10 +2770,10 @@
         <v>-1</v>
       </c>
       <c r="F42" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G42" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H42">
         <v>12</v>
@@ -3413,10 +2793,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
+        <v>169</v>
+      </c>
+      <c r="C43" t="s">
         <v>170</v>
-      </c>
-      <c r="C43" t="s">
-        <v>171</v>
       </c>
       <c r="D43" t="s">
         <v>45</v>
@@ -3425,10 +2805,10 @@
         <v>-1</v>
       </c>
       <c r="F43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H43">
         <v>12</v>
@@ -3443,27 +2823,25 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" ht="17" customHeight="1"/>
+    <row r="47" spans="1:11" ht="17.100000000000001" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M14"/>
-  <sheetFormatPr defaultColWidth="8.71666666666667" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="23.575" customWidth="1"/>
-    <col min="4" max="7" width="18.1416666666667" customWidth="1"/>
-    <col min="8" max="8" width="10.575" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" customWidth="1"/>
+    <col min="4" max="7" width="18.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="12.85" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="11.2833333333333" customWidth="1"/>
-    <col min="13" max="13" width="10.7166666666667" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -3480,10 +2858,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1" t="s">
         <v>173</v>
-      </c>
-      <c r="F1" t="s">
-        <v>174</v>
       </c>
       <c r="G1" t="s">
         <v>42</v>
@@ -3512,22 +2890,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" t="s">
         <v>175</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>176</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>177</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>178</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>179</v>
-      </c>
-      <c r="G2" t="s">
-        <v>180</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -3541,22 +2919,22 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" t="s">
         <v>181</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E3" t="s">
         <v>182</v>
       </c>
-      <c r="D3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G3" t="s">
         <v>183</v>
-      </c>
-      <c r="F3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G3" t="s">
-        <v>184</v>
       </c>
       <c r="H3">
         <v>15</v>
@@ -3570,22 +2948,22 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" t="s">
         <v>185</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G4" t="s">
         <v>186</v>
-      </c>
-      <c r="D4" t="s">
-        <v>177</v>
-      </c>
-      <c r="E4" t="s">
-        <v>183</v>
-      </c>
-      <c r="F4" t="s">
-        <v>179</v>
-      </c>
-      <c r="G4" t="s">
-        <v>187</v>
       </c>
       <c r="H4">
         <v>45</v>
@@ -3599,22 +2977,22 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" t="s">
         <v>188</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E5" t="s">
+        <v>177</v>
+      </c>
+      <c r="F5" t="s">
+        <v>178</v>
+      </c>
+      <c r="G5" t="s">
         <v>189</v>
-      </c>
-      <c r="D5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F5" t="s">
-        <v>179</v>
-      </c>
-      <c r="G5" t="s">
-        <v>190</v>
       </c>
       <c r="H5">
         <v>11</v>
@@ -3628,22 +3006,22 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" t="s">
         <v>191</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>192</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="E6" t="s">
-        <v>178</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" t="s">
         <v>194</v>
-      </c>
-      <c r="G6" t="s">
-        <v>195</v>
       </c>
       <c r="H6">
         <v>38</v>
@@ -3652,27 +3030,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" ht="42" spans="1:13">
+    <row r="7" spans="1:13" ht="60">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" t="s">
+        <v>176</v>
+      </c>
+      <c r="E7" t="s">
+        <v>177</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G7" t="s">
         <v>197</v>
-      </c>
-      <c r="D7" t="s">
-        <v>177</v>
-      </c>
-      <c r="E7" t="s">
-        <v>178</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="G7" t="s">
-        <v>198</v>
       </c>
       <c r="H7">
         <v>13</v>
@@ -3693,27 +3071,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="28" spans="1:13">
+    <row r="8" spans="1:13" ht="30">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" t="s">
+        <v>176</v>
+      </c>
+      <c r="E8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G8" t="s">
         <v>200</v>
-      </c>
-      <c r="D8" t="s">
-        <v>177</v>
-      </c>
-      <c r="E8" t="s">
-        <v>178</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="G8" t="s">
-        <v>201</v>
       </c>
       <c r="H8">
         <v>4</v>
@@ -3725,27 +3103,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="42" spans="1:13">
+    <row r="9" spans="1:13" ht="45">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" t="s">
+        <v>176</v>
+      </c>
+      <c r="E9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G9" t="s">
         <v>203</v>
-      </c>
-      <c r="D9" t="s">
-        <v>177</v>
-      </c>
-      <c r="E9" t="s">
-        <v>178</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="G9" t="s">
-        <v>204</v>
       </c>
       <c r="H9">
         <v>9</v>
@@ -3765,22 +3143,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>204</v>
+      </c>
+      <c r="C10" t="s">
         <v>205</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>176</v>
+      </c>
+      <c r="E10" t="s">
+        <v>177</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="D10" t="s">
-        <v>177</v>
-      </c>
-      <c r="E10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" t="s">
         <v>207</v>
-      </c>
-      <c r="G10" t="s">
-        <v>208</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -3797,22 +3175,22 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>208</v>
+      </c>
+      <c r="C11" t="s">
         <v>209</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E11" t="s">
+        <v>182</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G11" t="s">
         <v>210</v>
-      </c>
-      <c r="D11" t="s">
-        <v>177</v>
-      </c>
-      <c r="E11" t="s">
-        <v>183</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="G11" t="s">
-        <v>211</v>
       </c>
       <c r="H11">
         <v>63</v>
@@ -3832,22 +3210,22 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>211</v>
+      </c>
+      <c r="C12" t="s">
         <v>212</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>176</v>
+      </c>
+      <c r="E12" t="s">
+        <v>182</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G12" t="s">
         <v>213</v>
-      </c>
-      <c r="D12" t="s">
-        <v>177</v>
-      </c>
-      <c r="E12" t="s">
-        <v>183</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="G12" t="s">
-        <v>214</v>
       </c>
       <c r="H12">
         <v>65</v>
@@ -3861,22 +3239,22 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>214</v>
+      </c>
+      <c r="C13" t="s">
         <v>215</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>176</v>
+      </c>
+      <c r="E13" t="s">
+        <v>177</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G13" t="s">
         <v>216</v>
-      </c>
-      <c r="D13" t="s">
-        <v>177</v>
-      </c>
-      <c r="E13" t="s">
-        <v>178</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="G13" t="s">
-        <v>217</v>
       </c>
       <c r="H13">
         <v>14</v>
@@ -3890,6 +3268,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>